--- a/Claudevala.xlsx
+++ b/Claudevala.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karol\Desktop\new_github\claudevala\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9080200-C293-4CEF-826C-53BF42DAE1C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A835B9DB-0FF3-4AEF-B462-6362E36462BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10725" uniqueCount="8430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11870" uniqueCount="9255">
   <si>
     <t>Mieleni minun tekevi,</t>
   </si>
@@ -25310,6 +25310,2481 @@
   </si>
   <si>
     <t>from dark/foggy, Sariola</t>
+  </si>
+  <si>
+    <t>Tuo oli kaunis Pohjan neiti,</t>
+  </si>
+  <si>
+    <t>tuo, olla, kaunis, Pohja, neito</t>
+  </si>
+  <si>
+    <t>that, to be, beautiful, North's, maiden</t>
+  </si>
+  <si>
+    <t>maan kuulu, ve'en valio.</t>
+  </si>
+  <si>
+    <t>maan kuulu, veden valio.</t>
+  </si>
+  <si>
+    <t>maa, kuulu, vesi, valio</t>
+  </si>
+  <si>
+    <t>land's, famous/renowned, water's, finest/choice</t>
+  </si>
+  <si>
+    <t>Istui ilman vempelellä,</t>
+  </si>
+  <si>
+    <t>istua, ilma, vempele</t>
+  </si>
+  <si>
+    <t>to sit, sky/air, swingletree/bar</t>
+  </si>
+  <si>
+    <t>The Pohjan neiti sitting on a rainbow weaving gold and silver cloth is a mythological image of the cosmic weaver — a maiden beyond ordinary reach, positioned between sky and earth, fitting for the prize in a trickster's quest.</t>
+  </si>
+  <si>
+    <t>taivon kaarella kajotti</t>
+  </si>
+  <si>
+    <t>taivaan kaarella kajotti</t>
+  </si>
+  <si>
+    <t>taivas, kaari, kajahtaa</t>
+  </si>
+  <si>
+    <t>sky/heaven, arc/rainbow, to gleam/shimmer</t>
+  </si>
+  <si>
+    <t>pukehissa puhta'issa,</t>
+  </si>
+  <si>
+    <t>pukuissa puhtaissa,</t>
+  </si>
+  <si>
+    <t>puku, puhdas</t>
+  </si>
+  <si>
+    <t>clothes, clean/pure</t>
+  </si>
+  <si>
+    <t>valke'issa vaattehissa;</t>
+  </si>
+  <si>
+    <t>valkeissa vaatteissa;</t>
+  </si>
+  <si>
+    <t>valkea, vaate</t>
+  </si>
+  <si>
+    <t>white/bright, clothes</t>
+  </si>
+  <si>
+    <t>kultakangasta kutovi,</t>
+  </si>
+  <si>
+    <t>kultakangasta kutoo,</t>
+  </si>
+  <si>
+    <t>kulta, kangas, kutoa</t>
+  </si>
+  <si>
+    <t>gold, cloth/fabric, to weave</t>
+  </si>
+  <si>
+    <t>hope'ista huolittavi</t>
+  </si>
+  <si>
+    <t>hopeaista huolittaa</t>
+  </si>
+  <si>
+    <t>kultaisesta sukkulasta,</t>
+  </si>
+  <si>
+    <t>kultainen, sukkula</t>
+  </si>
+  <si>
+    <t>golden, shuttle (weaving)</t>
+  </si>
+  <si>
+    <t>pirralla hope'isella.</t>
+  </si>
+  <si>
+    <t>pirralla hopeaisella.</t>
+  </si>
+  <si>
+    <t>pirta, hopea</t>
+  </si>
+  <si>
+    <t>with a reed (weaving tool), silver</t>
+  </si>
+  <si>
+    <t>Suihki sukkula piossa,</t>
+  </si>
+  <si>
+    <t>Suihki sukkula kädessä,</t>
+  </si>
+  <si>
+    <t>suikata, sukkula, käsi</t>
+  </si>
+  <si>
+    <t>to whizz/hiss, shuttle, hand</t>
+  </si>
+  <si>
+    <t>käämi käessä kääperöitsi,</t>
+  </si>
+  <si>
+    <t>käämi kädessä kääperöitsi,</t>
+  </si>
+  <si>
+    <t>käämi, käsi, kääperöidä</t>
+  </si>
+  <si>
+    <t>spool/bobbin, hand, to wind/roll</t>
+  </si>
+  <si>
+    <t>niiet vaskiset vatisi,</t>
+  </si>
+  <si>
+    <t>nie, vaskinen, vatista</t>
+  </si>
+  <si>
+    <t>heddles, copper/bronze, to vibrate/hum</t>
+  </si>
+  <si>
+    <t>hope'inen pirta piukki</t>
+  </si>
+  <si>
+    <t>hopeinen pirta piukki</t>
+  </si>
+  <si>
+    <t>hopea, pirta, piukata</t>
+  </si>
+  <si>
+    <t>silver, reed (weaving), to twang/snap</t>
+  </si>
+  <si>
+    <t>neien kangasta kutoissa,</t>
+  </si>
+  <si>
+    <t>neidon kangasta kutoessa,</t>
+  </si>
+  <si>
+    <t>neito, kangas, kutoa</t>
+  </si>
+  <si>
+    <t>maiden's, cloth, to weave</t>
+  </si>
+  <si>
+    <t>hope'ista huolittaissa.</t>
+  </si>
+  <si>
+    <t>hopeaista huolittaessa.</t>
+  </si>
+  <si>
+    <t>silver, to finish/trim</t>
+  </si>
+  <si>
+    <t>ajoa karittelevi</t>
+  </si>
+  <si>
+    <t>ajoa karittelee</t>
+  </si>
+  <si>
+    <t>Ajoi matkoa palasen,</t>
+  </si>
+  <si>
+    <t>Ajoi matkaa palasen,</t>
+  </si>
+  <si>
+    <t>ajaa, matka, palanen</t>
+  </si>
+  <si>
+    <t>to drive, journey, a piece/bit</t>
+  </si>
+  <si>
+    <t>pikkaraisen piirrätteli:</t>
+  </si>
+  <si>
+    <t>pikkuinen, piirrättää</t>
+  </si>
+  <si>
+    <t>a little, to trace/glide along</t>
+  </si>
+  <si>
+    <t>kuuli sukkulan surinan</t>
+  </si>
+  <si>
+    <t>kuulla, sukkula, surina</t>
+  </si>
+  <si>
+    <t>to hear, shuttle, humming/buzzing</t>
+  </si>
+  <si>
+    <t>ylähältä päänsä päältä.</t>
+  </si>
+  <si>
+    <t>ylhäältä, pää, päältä</t>
+  </si>
+  <si>
+    <t>from above, head, from atop</t>
+  </si>
+  <si>
+    <t>Tuossa päätänsä kohotti,</t>
+  </si>
+  <si>
+    <t>tuossa, pää, kohottaa</t>
+  </si>
+  <si>
+    <t>there, head, to raise/lift</t>
+  </si>
+  <si>
+    <t>Väinämöinen raising his head despite Louhi's prohibition — the very thing he was warned not to do — leads to his encounter with the maiden. This is the trickster breaking a rule and being rewarded rather than punished, inverting the usual formula.</t>
+  </si>
+  <si>
+    <t>katsahtavi taivahalle:</t>
+  </si>
+  <si>
+    <t>katsahtaa taivaalle:</t>
+  </si>
+  <si>
+    <t>katsahtaa, taivas</t>
+  </si>
+  <si>
+    <t>to glance, sky/heaven</t>
+  </si>
+  <si>
+    <t>kaari on kaunis taivahalla,</t>
+  </si>
+  <si>
+    <t>kaari on kaunis taivaalla,</t>
+  </si>
+  <si>
+    <t>kaari, kaunis, taivas</t>
+  </si>
+  <si>
+    <t>arc/rainbow, beautiful, sky/heaven</t>
+  </si>
+  <si>
+    <t>neiti kaaren kannikalla,</t>
+  </si>
+  <si>
+    <t>neito, kaari, kannikka</t>
+  </si>
+  <si>
+    <t>maiden, arc/rainbow, crust/edge</t>
+  </si>
+  <si>
+    <t>gold, cloth, to weave</t>
+  </si>
+  <si>
+    <t>hope'ista helkyttävi.</t>
+  </si>
+  <si>
+    <t>hopeaista helkyttää.</t>
+  </si>
+  <si>
+    <t>hopea, helkyttää</t>
+  </si>
+  <si>
+    <t>silver, to jingle/ring out</t>
+  </si>
+  <si>
+    <t>heti seisatti hevosen.</t>
+  </si>
+  <si>
+    <t>heti, seisattaa, hevonen</t>
+  </si>
+  <si>
+    <t>immediately, to halt, horse</t>
+  </si>
+  <si>
+    <t>Tuossa tuon sanoiksi virkki,</t>
+  </si>
+  <si>
+    <t>Tuossa tuon sanoiksi sanoi,</t>
+  </si>
+  <si>
+    <t>tuossa, tuo, sana, virkkoa</t>
+  </si>
+  <si>
+    <t>there, those, words, to say</t>
+  </si>
+  <si>
+    <t>"Tule, neiti, korjahani,</t>
+  </si>
+  <si>
+    <t>"Tule, neiti, korjaani,</t>
+  </si>
+  <si>
+    <t>tulla, neito, korja</t>
+  </si>
+  <si>
+    <t>to come, maiden, sleigh/carriage</t>
+  </si>
+  <si>
+    <t>Väinämöinen's immediate proposal — 'come into my sleigh, maiden' — is the trickster's characteristic directness in courtship, repeating the same presumptuous claim he made to Aino.</t>
+  </si>
+  <si>
+    <t>laskeite rekoseheni!"</t>
+  </si>
+  <si>
+    <t>laskeite rekoseen!"</t>
+  </si>
+  <si>
+    <t>laskea, reki</t>
+  </si>
+  <si>
+    <t>to lower/come down, sled</t>
+  </si>
+  <si>
+    <t>Neiti tuon sanoiksi virkki,</t>
+  </si>
+  <si>
+    <t>Neito tuon sanoiksi sanoi,</t>
+  </si>
+  <si>
+    <t>itse lausui ja kysyvi:</t>
+  </si>
+  <si>
+    <t>itse lausui ja kysyi:</t>
+  </si>
+  <si>
+    <t>itse, lausua, kysyä</t>
+  </si>
+  <si>
+    <t>herself, to utter, to ask</t>
+  </si>
+  <si>
+    <t>"Miksi neittä korjahasi,</t>
+  </si>
+  <si>
+    <t>"Miksi neittä korjaasi,</t>
+  </si>
+  <si>
+    <t>miksi, neito, korja</t>
+  </si>
+  <si>
+    <t>why, maiden, into your sleigh</t>
+  </si>
+  <si>
+    <t>tyttöä rekosehesi?"</t>
+  </si>
+  <si>
+    <t>tyttöä rekoseen?"</t>
+  </si>
+  <si>
+    <t>tyttö, reki</t>
+  </si>
+  <si>
+    <t>girl, into your sled</t>
+  </si>
+  <si>
+    <t>tuop' on tuohon vastaeli:</t>
+  </si>
+  <si>
+    <t>tuopa tuohon vastasi:</t>
+  </si>
+  <si>
+    <t>tuo, vastata</t>
+  </si>
+  <si>
+    <t>that one, to answer</t>
+  </si>
+  <si>
+    <t>"Siksi neittä korjahani,</t>
+  </si>
+  <si>
+    <t>"Siksi neittä korjaani,</t>
+  </si>
+  <si>
+    <t>siksi, neito, korja</t>
+  </si>
+  <si>
+    <t>for that reason, maiden, into my sleigh</t>
+  </si>
+  <si>
+    <t>tyttöä rekoseheni:</t>
+  </si>
+  <si>
+    <t>tyttöä rekoseen:</t>
+  </si>
+  <si>
+    <t>girl, into my sled</t>
+  </si>
+  <si>
+    <t>oluen osoajaksi,</t>
+  </si>
+  <si>
+    <t>olut, osoaja</t>
+  </si>
+  <si>
+    <t>beer/ale, brewer/server</t>
+  </si>
+  <si>
+    <t>joka lautsan laulajaksi,</t>
+  </si>
+  <si>
+    <t>joka, lauto, laulaja</t>
+  </si>
+  <si>
+    <t>every, bench/platform, singer</t>
+  </si>
+  <si>
+    <t>ikkunan iloitsijaksi</t>
+  </si>
+  <si>
+    <t>ikkuna, iloitsija</t>
+  </si>
+  <si>
+    <t>window's, rejoicer/entertainer</t>
+  </si>
+  <si>
+    <t>noilla Väinölän tiloilla,</t>
+  </si>
+  <si>
+    <t>tuo, Väinölä, tila</t>
+  </si>
+  <si>
+    <t>those, Väinölä, spaces/rooms</t>
+  </si>
+  <si>
+    <t>Kalevalan kartanoilla."</t>
+  </si>
+  <si>
+    <t>Kalevala, kartano</t>
+  </si>
+  <si>
+    <t>Kalevala, estate/yard</t>
+  </si>
+  <si>
+    <t>herself, to utter, to speak</t>
+  </si>
+  <si>
+    <t>"Kun kävin mataramaalla,</t>
+  </si>
+  <si>
+    <t>kun, käydä, mataramaa</t>
+  </si>
+  <si>
+    <t>when, to go, clover/madder field</t>
+  </si>
+  <si>
+    <t>keikuin keltakankahalla</t>
+  </si>
+  <si>
+    <t>keikkua, kelta, kangas</t>
+  </si>
+  <si>
+    <t>to sway/walk, yellow, heath/plain</t>
+  </si>
+  <si>
+    <t>eilen iltamyöhäsellä,</t>
+  </si>
+  <si>
+    <t>eilen iltamyöhäisellä,</t>
+  </si>
+  <si>
+    <t>eilen, iltamyöhäinen</t>
+  </si>
+  <si>
+    <t>yesterday, late evening</t>
+  </si>
+  <si>
+    <t>aletessa aurinkoisen,</t>
+  </si>
+  <si>
+    <t>aleta, aurinko</t>
+  </si>
+  <si>
+    <t>at the setting, sun</t>
+  </si>
+  <si>
+    <t>lintu lauleli lehossa,</t>
+  </si>
+  <si>
+    <t>lintu, laulella, lehto</t>
+  </si>
+  <si>
+    <t>bird, to sing, grove</t>
+  </si>
+  <si>
+    <t>kyntörastas raksutteli:</t>
+  </si>
+  <si>
+    <t>kyntörastas, raksuttaa</t>
+  </si>
+  <si>
+    <t>fieldfare/thrush, to rattle/chatter</t>
+  </si>
+  <si>
+    <t>The maiden's story of asking the fieldfare thrush whether it's better to be a daughter at home or a daughter-in-law at a husband's — and the bird's sharp answer — is a trickster-test within a trickster-test: she tests Väinämöinen by recounting how she has already been advised against marriage.</t>
+  </si>
+  <si>
+    <t>lauleli tytärten mielen</t>
+  </si>
+  <si>
+    <t>laulella, tytär, mieli</t>
+  </si>
+  <si>
+    <t>to sing, daughters', mind/mood</t>
+  </si>
+  <si>
+    <t>ja lauloi miniän mielen.</t>
+  </si>
+  <si>
+    <t>laulaa, miniä, mieli</t>
+  </si>
+  <si>
+    <t>to sing, daughter-in-law's, mood</t>
+  </si>
+  <si>
+    <t>"Mie tuota sanelemahan,</t>
+  </si>
+  <si>
+    <t>"Minä tuota sanelemaan,</t>
+  </si>
+  <si>
+    <t>minä, tuo, sanella</t>
+  </si>
+  <si>
+    <t>I, that, to recite/tell</t>
+  </si>
+  <si>
+    <t>linnulta kyselemähän:</t>
+  </si>
+  <si>
+    <t>linnulta kyselemään:</t>
+  </si>
+  <si>
+    <t>lintu, kyseleminen</t>
+  </si>
+  <si>
+    <t>from bird, to ask</t>
+  </si>
+  <si>
+    <t>'Oi sie kyntörastahainen!</t>
+  </si>
+  <si>
+    <t>'Oi sinä kyntörastaseni!</t>
+  </si>
+  <si>
+    <t>oi, sinä, kyntörastas</t>
+  </si>
+  <si>
+    <t>oh, you, fieldfare/thrush (dear)</t>
+  </si>
+  <si>
+    <t>Laula korvin kuullakseni:</t>
+  </si>
+  <si>
+    <t>laulaa, korva, kuulla</t>
+  </si>
+  <si>
+    <t>to sing, ears, to hear</t>
+  </si>
+  <si>
+    <t>kumman on parempi olla,</t>
+  </si>
+  <si>
+    <t>kumpi, parempi, olla</t>
+  </si>
+  <si>
+    <t>which of the two, better, to be</t>
+  </si>
+  <si>
+    <t>kumman olla kuuluisampi,</t>
+  </si>
+  <si>
+    <t>kumpi, olla, kuuluisa</t>
+  </si>
+  <si>
+    <t>which, to be, more famous/renowned</t>
+  </si>
+  <si>
+    <t>tyttärenkö taattolassa</t>
+  </si>
+  <si>
+    <t>tyttärenkö isässä</t>
+  </si>
+  <si>
+    <t>tytär, isä</t>
+  </si>
+  <si>
+    <t>daughter's, at father's (home)</t>
+  </si>
+  <si>
+    <t>vai miniän miehelässä?'</t>
+  </si>
+  <si>
+    <t>vai miniän miehen kotona?'</t>
+  </si>
+  <si>
+    <t>vai, miniä, mies, koti</t>
+  </si>
+  <si>
+    <t>or, daughter-in-law's, husband's, home</t>
+  </si>
+  <si>
+    <t>"Tiainenpa tieon antoi,</t>
+  </si>
+  <si>
+    <t>"Tiainen tiedon antoi,</t>
+  </si>
+  <si>
+    <t>tiainen, tieto, antaa</t>
+  </si>
+  <si>
+    <t>tit (bird), knowledge/information, to give</t>
+  </si>
+  <si>
+    <t>kyntörastas raksahutti:</t>
+  </si>
+  <si>
+    <t>kyntörastas raksahti:</t>
+  </si>
+  <si>
+    <t>kyntörastas, raksahtaa</t>
+  </si>
+  <si>
+    <t>fieldfare/thrush, to rattle/snap</t>
+  </si>
+  <si>
+    <t>'Valkea kesäinen päivä,</t>
+  </si>
+  <si>
+    <t>valkea, kesäinen, päivä</t>
+  </si>
+  <si>
+    <t>bright, summer, day</t>
+  </si>
+  <si>
+    <t>neitivalta valkeampi;</t>
+  </si>
+  <si>
+    <t>neitivalta, valkea</t>
+  </si>
+  <si>
+    <t>maiden's power/status, brighter</t>
+  </si>
+  <si>
+    <t>vilu on rauta pakkasessa,</t>
+  </si>
+  <si>
+    <t>kylmä on rauta pakkasessa,</t>
+  </si>
+  <si>
+    <t>vilu, rauta, pakkanen</t>
+  </si>
+  <si>
+    <t>cold, iron, frost</t>
+  </si>
+  <si>
+    <t>vilumpi miniävalta.</t>
+  </si>
+  <si>
+    <t>kylmempi miniävalta.</t>
+  </si>
+  <si>
+    <t>vilumpi, miniä, valta</t>
+  </si>
+  <si>
+    <t>colder, daughter-in-law's, power/status</t>
+  </si>
+  <si>
+    <t>The tit's verdict — a daughter at home is like a berry on good soil; a daughter-in-law in a husband's house is like a dog in chains — is one of the sharpest social critiques in the Kalevala, delivered through the trickster medium of a bird-oracle.</t>
+  </si>
+  <si>
+    <t>Niin on neiti taattolassa,</t>
+  </si>
+  <si>
+    <t>Niin on neiti isässä,</t>
+  </si>
+  <si>
+    <t>niin, neito, isä</t>
+  </si>
+  <si>
+    <t>so, maiden, at father's</t>
+  </si>
+  <si>
+    <t>kuin marja hyvällä maalla,</t>
+  </si>
+  <si>
+    <t>kuin, marja, hyvä, maa</t>
+  </si>
+  <si>
+    <t>like, berry, good, land</t>
+  </si>
+  <si>
+    <t>niin miniä miehelässä,</t>
+  </si>
+  <si>
+    <t>niin, miniä, miehelä</t>
+  </si>
+  <si>
+    <t>so, daughter-in-law, at husband's</t>
+  </si>
+  <si>
+    <t>kuin on koira kahlehissa.</t>
+  </si>
+  <si>
+    <t>kuin on koira kahleissa.</t>
+  </si>
+  <si>
+    <t>kuin, koira, kahle</t>
+  </si>
+  <si>
+    <t>like, dog, chains</t>
+  </si>
+  <si>
+    <t>Harvoin saapi orja lemmen,</t>
+  </si>
+  <si>
+    <t>harvoin, saada, orja, lempi</t>
+  </si>
+  <si>
+    <t>seldom, to get, slave/serf, love</t>
+  </si>
+  <si>
+    <t>ei miniä milloinkana.'"</t>
+  </si>
+  <si>
+    <t>ei miniä milloinkaan.'"</t>
+  </si>
+  <si>
+    <t>ei, miniä, milloinkaan</t>
+  </si>
+  <si>
+    <t>not, daughter-in-law, ever</t>
+  </si>
+  <si>
+    <t>"Tyhjiä tiaisen virret,</t>
+  </si>
+  <si>
+    <t>tyhjä, tiainen, virsi</t>
+  </si>
+  <si>
+    <t>empty/hollow, tit's, songs</t>
+  </si>
+  <si>
+    <t>Väinämöinen's dismissal of the bird's wisdom as empty verses — 'a girl is still a girl once married' — is the trickster refusing to hear what doesn't suit him, the blind spot that will cost him.</t>
+  </si>
+  <si>
+    <t>rastahaisen raksutukset!</t>
+  </si>
+  <si>
+    <t>rastas, raksuttaa</t>
+  </si>
+  <si>
+    <t>thrush's, chatterings</t>
+  </si>
+  <si>
+    <t>Lapsi on tytär kotona,</t>
+  </si>
+  <si>
+    <t>lapsi, tytär, koti</t>
+  </si>
+  <si>
+    <t>child, daughter, at home</t>
+  </si>
+  <si>
+    <t>vasta on neiti naituansa.</t>
+  </si>
+  <si>
+    <t>vasta on neiti naituna.</t>
+  </si>
+  <si>
+    <t>vasta, neito, naida</t>
+  </si>
+  <si>
+    <t>only then, maiden, married</t>
+  </si>
+  <si>
+    <t>Tule, neiti, korjahani,</t>
+  </si>
+  <si>
+    <t>Tule, neiti, korjaani,</t>
+  </si>
+  <si>
+    <t>to come, maiden, into my sleigh</t>
+  </si>
+  <si>
+    <t>laskeite rekoseheni!</t>
+  </si>
+  <si>
+    <t>laskeite rekoseen!</t>
+  </si>
+  <si>
+    <t>En ole mitätön miesi,</t>
+  </si>
+  <si>
+    <t>En ole mitätön mies,</t>
+  </si>
+  <si>
+    <t>ei, olla, mitätön, mies</t>
+  </si>
+  <si>
+    <t>not, to be, worthless/nothing, man</t>
+  </si>
+  <si>
+    <t>uros muita untelompi."</t>
+  </si>
+  <si>
+    <t>uros, muu, untelo</t>
+  </si>
+  <si>
+    <t>hero/man, others, more clumsy/dull</t>
+  </si>
+  <si>
+    <t>Neiti taiten vastaeli,</t>
+  </si>
+  <si>
+    <t>Neito taitavasti vastasi,</t>
+  </si>
+  <si>
+    <t>neito, taitavasti, vastata</t>
+  </si>
+  <si>
+    <t>maiden, skillfully, to answer</t>
+  </si>
+  <si>
+    <t>The Pohjan neiti's series of impossible tasks is the classic trickster-test sequence: she sets riddles that seem impossible to prove worthy suitors from unworthy ones, each task harder than the last.</t>
+  </si>
+  <si>
+    <t>"Sitte sun mieheksi sanoisin,</t>
+  </si>
+  <si>
+    <t>"Silloin sinua mieheksi sanoisin,</t>
+  </si>
+  <si>
+    <t>silloin, sinä, mies, sanoa</t>
+  </si>
+  <si>
+    <t>then, you, man, to call</t>
+  </si>
+  <si>
+    <t>urohoksi arveleisin,</t>
+  </si>
+  <si>
+    <t>uros, arvella</t>
+  </si>
+  <si>
+    <t>hero/man, to consider/think</t>
+  </si>
+  <si>
+    <t>jospa jouhen halkaiseisit</t>
+  </si>
+  <si>
+    <t>jos jouhen halkaiseisit</t>
+  </si>
+  <si>
+    <t>jos, jouhi, halkoa</t>
+  </si>
+  <si>
+    <t>if, horsehair, to split</t>
+  </si>
+  <si>
+    <t>veitsellä kärettömällä,</t>
+  </si>
+  <si>
+    <t>veitsi, käretön</t>
+  </si>
+  <si>
+    <t>knife, bladeless/edgeless</t>
+  </si>
+  <si>
+    <t>munan solmuhun vetäisit</t>
+  </si>
+  <si>
+    <t>munan solmuun vetäisit</t>
+  </si>
+  <si>
+    <t>muna, solmu, vetää</t>
+  </si>
+  <si>
+    <t>egg, knot, to pull/draw</t>
+  </si>
+  <si>
+    <t>solmun tuntumattomaksi."</t>
+  </si>
+  <si>
+    <t>solmu, tuntumaton</t>
+  </si>
+  <si>
+    <t>knot, unfelt/imperceptible</t>
+  </si>
+  <si>
+    <t>jouhen halki halkaisevi</t>
+  </si>
+  <si>
+    <t>jouhen halki halkaisee</t>
+  </si>
+  <si>
+    <t>jouhi, halki, halkoa</t>
+  </si>
+  <si>
+    <t>horsehair, in half, to split</t>
+  </si>
+  <si>
+    <t>Väinämöinen splitting a horsehair with a bladeless knife and tying an egg in an invisible knot are classic shamanic-trickster feats: impossible tasks accomplished through magical skill rather than physical means.</t>
+  </si>
+  <si>
+    <t>aivan tutkaimettomalla;</t>
+  </si>
+  <si>
+    <t>aivan, tutkain</t>
+  </si>
+  <si>
+    <t>quite, without a point/probe</t>
+  </si>
+  <si>
+    <t>munan solmuhun vetävi</t>
+  </si>
+  <si>
+    <t>munan solmuun vetää</t>
+  </si>
+  <si>
+    <t>solmun tuntumattomaksi.</t>
+  </si>
+  <si>
+    <t>Käski neittä korjahansa,</t>
+  </si>
+  <si>
+    <t>Käski neittä korjaansa,</t>
+  </si>
+  <si>
+    <t>käskeä, neito, korja</t>
+  </si>
+  <si>
+    <t>to bid/invite, maiden, into his sleigh</t>
+  </si>
+  <si>
+    <t>tyttöä rekosehensa.</t>
+  </si>
+  <si>
+    <t>tyttöä rekoseen.</t>
+  </si>
+  <si>
+    <t>girl, into his sled</t>
+  </si>
+  <si>
+    <t>Neiti taiten vastaeli:</t>
+  </si>
+  <si>
+    <t>Neito taitavasti vastasi:</t>
+  </si>
+  <si>
+    <t>"Ehkäpä tulen sinulle,</t>
+  </si>
+  <si>
+    <t>ehkä, tulla, sinä</t>
+  </si>
+  <si>
+    <t>perhaps, to come, you</t>
+  </si>
+  <si>
+    <t>kun kiskot kivestä tuohta,</t>
+  </si>
+  <si>
+    <t>kun, kiskoa, kivi, tuohi</t>
+  </si>
+  <si>
+    <t>when, to strip/peel, stone, birch bark</t>
+  </si>
+  <si>
+    <t>säret jäästä aiaksia</t>
+  </si>
+  <si>
+    <t>säret jäästä aitaksia</t>
+  </si>
+  <si>
+    <t>särkeä, jää, aita</t>
+  </si>
+  <si>
+    <t>to break, ice, fencing/stakes</t>
+  </si>
+  <si>
+    <t>ilman palan pakkumatta,</t>
+  </si>
+  <si>
+    <t>ilman, pala, pakkua</t>
+  </si>
+  <si>
+    <t>without, piece, to crack/snap off</t>
+  </si>
+  <si>
+    <t>pilkkehen pirahtamatta."</t>
+  </si>
+  <si>
+    <t>pilkkeen pirahtamatta."</t>
+  </si>
+  <si>
+    <t>pilkke, pirahtaa</t>
+  </si>
+  <si>
+    <t>chip/splinter, to fly off</t>
+  </si>
+  <si>
+    <t>ei tuosta kovin hätäile:</t>
+  </si>
+  <si>
+    <t>ei, tuo, kovin, hätäillä</t>
+  </si>
+  <si>
+    <t>not, that, greatly, to panic/rush</t>
+  </si>
+  <si>
+    <t>kiskoipa kivestä tuohta,</t>
+  </si>
+  <si>
+    <t>kiskoa, kivi, tuohi</t>
+  </si>
+  <si>
+    <t>to strip/peel, stone, birch bark</t>
+  </si>
+  <si>
+    <t>särki jäästä aiaksia</t>
+  </si>
+  <si>
+    <t>särki jäästä aitaksia</t>
+  </si>
+  <si>
+    <t>pilkkehen pirahtamatta.</t>
+  </si>
+  <si>
+    <t>pilkkeen pirahtamatta.</t>
+  </si>
+  <si>
+    <t>Kutsui neittä korjahansa,</t>
+  </si>
+  <si>
+    <t>Kutsui neittä korjaansa,</t>
+  </si>
+  <si>
+    <t>kutsua, neito, korja</t>
+  </si>
+  <si>
+    <t>to call/invite, maiden, into his sleigh</t>
+  </si>
+  <si>
+    <t>Neiti taiten vastoavi,</t>
+  </si>
+  <si>
+    <t>Neito taitavasti vastaa,</t>
+  </si>
+  <si>
+    <t>sanovi sanalla tuolla:</t>
+  </si>
+  <si>
+    <t>sanoo sanalla tuolla:</t>
+  </si>
+  <si>
+    <t>"Sillenpä minä menisin,</t>
+  </si>
+  <si>
+    <t>"Silloin minä menisin,</t>
+  </si>
+  <si>
+    <t>silloin, minä, mennä</t>
+  </si>
+  <si>
+    <t>then, I, to go</t>
+  </si>
+  <si>
+    <t>kenp' on veistäisi venosen</t>
+  </si>
+  <si>
+    <t>joka veistäisi venosen</t>
+  </si>
+  <si>
+    <t>joka, veistää, vene</t>
+  </si>
+  <si>
+    <t>whoever, to carve/build, boat</t>
+  </si>
+  <si>
+    <t>kehrävarteni muruista,</t>
+  </si>
+  <si>
+    <t>kehrä, varsi, muru</t>
+  </si>
+  <si>
+    <t>spindle, shaft, crumb/fragment</t>
+  </si>
+  <si>
+    <t>kalpimeni kappaleista,</t>
+  </si>
+  <si>
+    <t>kalpime, kappale</t>
+  </si>
+  <si>
+    <t>my distaff, pieces</t>
+  </si>
+  <si>
+    <t>työntäisi venon vesille,</t>
+  </si>
+  <si>
+    <t>uuen laivan lainehille</t>
+  </si>
+  <si>
+    <t>uuden laivan laineille</t>
+  </si>
+  <si>
+    <t>uusi, laiva, laine</t>
+  </si>
+  <si>
+    <t>new, ship, waves</t>
+  </si>
+  <si>
+    <t>ilman polven polkematta,</t>
+  </si>
+  <si>
+    <t>ilman, polvi, polkea</t>
+  </si>
+  <si>
+    <t>without, knee, to trample/press</t>
+  </si>
+  <si>
+    <t>ilman kouran koskematta,</t>
+  </si>
+  <si>
+    <t>ilman, koura, koskea</t>
+  </si>
+  <si>
+    <t>without, fist/hand, to touch</t>
+  </si>
+  <si>
+    <t>käsivarren kääntämättä,</t>
+  </si>
+  <si>
+    <t>käsivarsi, kääntää</t>
+  </si>
+  <si>
+    <t>forearm, to turn</t>
+  </si>
+  <si>
+    <t>olkapään ojentamatta."</t>
+  </si>
+  <si>
+    <t>olkapää, ojentaa</t>
+  </si>
+  <si>
+    <t>shoulder, to stretch/extend</t>
+  </si>
+  <si>
+    <t>The third impossible task — building a boat from her spinning implements without using hands, knees, or shoulders — raises the stakes maximally. Väinämöinen attempts it and is injured, which drives the rest of the runo.</t>
+  </si>
+  <si>
+    <t>"Liene ei maassa, maailmassa,</t>
+  </si>
+  <si>
+    <t>"Lienee ei maassa, maailmassa,</t>
+  </si>
+  <si>
+    <t>lieneä, ei, maa, maailma</t>
+  </si>
+  <si>
+    <t>to be perhaps, not, earth, world</t>
+  </si>
+  <si>
+    <t>koko ilman kannen alla</t>
+  </si>
+  <si>
+    <t>koko, ilma, kansi, alla</t>
+  </si>
+  <si>
+    <t>whole, sky/air, lid/cover, under</t>
+  </si>
+  <si>
+    <t>mointa laivan laatijata,</t>
+  </si>
+  <si>
+    <t>moista laivan rakentajaa,</t>
+  </si>
+  <si>
+    <t>moiset, laiva, rakentaja</t>
+  </si>
+  <si>
+    <t>such, ship, builder</t>
+  </si>
+  <si>
+    <t>vertoani veistäjätä."</t>
+  </si>
+  <si>
+    <t>vertoani veistäjää."</t>
+  </si>
+  <si>
+    <t>vero, veistäjä</t>
+  </si>
+  <si>
+    <t>my equal, carver/builder</t>
+  </si>
+  <si>
+    <t>Väinämöinen's boast — there is no ship-builder in the world my equal — is the trickster's fatal overconfidence that precedes his injury.</t>
+  </si>
+  <si>
+    <t>Otti värttinän muruja,</t>
+  </si>
+  <si>
+    <t>ottaa, värttinä, muru</t>
+  </si>
+  <si>
+    <t>to take, spindle, crumb/fragment</t>
+  </si>
+  <si>
+    <t>kehrävarren kiertimiä;</t>
+  </si>
+  <si>
+    <t>kehrä, varsi, kiertäminen</t>
+  </si>
+  <si>
+    <t>spindle, shaft, windings/turnings</t>
+  </si>
+  <si>
+    <t>läksi veistohon venosen,</t>
+  </si>
+  <si>
+    <t>läksi veistämään venettä,</t>
+  </si>
+  <si>
+    <t>lähteä, veistää, vene</t>
+  </si>
+  <si>
+    <t>to set out, to carve/build, boat</t>
+  </si>
+  <si>
+    <t>satalauan laittelohon</t>
+  </si>
+  <si>
+    <t>satalaidan laitteloon</t>
+  </si>
+  <si>
+    <t>sata, laita, laittaa</t>
+  </si>
+  <si>
+    <t>hundred-planked, arranging/building</t>
+  </si>
+  <si>
+    <t>vuorelle teräksiselle,</t>
+  </si>
+  <si>
+    <t>vuori, teräksinen</t>
+  </si>
+  <si>
+    <t>mountain, steel/iron</t>
+  </si>
+  <si>
+    <t>rautaiselle kalliolle.</t>
+  </si>
+  <si>
+    <t>rautainen, kallio</t>
+  </si>
+  <si>
+    <t>iron, cliff/rock</t>
+  </si>
+  <si>
+    <t>Veikaten venettä veisti,</t>
+  </si>
+  <si>
+    <t>veikata, vene, veistää</t>
+  </si>
+  <si>
+    <t>chanting/singing, boat, to carve/build</t>
+  </si>
+  <si>
+    <t>purtta puista uhkaellen.</t>
+  </si>
+  <si>
+    <t>pursi, puu, uhkaella</t>
+  </si>
+  <si>
+    <t>boat, wood, to threaten/force</t>
+  </si>
+  <si>
+    <t>Väinämöinen's boat-building through song — 'chanting and threatening the wood' — is the trickster-shaman's method: magical speech used to compel matter into shape.</t>
+  </si>
+  <si>
+    <t>Veisti päivän, veisti toisen,</t>
+  </si>
+  <si>
+    <t>veistää, päivä, toinen</t>
+  </si>
+  <si>
+    <t>to carve/build, day, second</t>
+  </si>
+  <si>
+    <t>veisti kohta kolmannenki:</t>
+  </si>
+  <si>
+    <t>veisti kohta kolmannenkin:</t>
+  </si>
+  <si>
+    <t>veistää, kohta, kolmas</t>
+  </si>
+  <si>
+    <t>to carve/build, soon, third</t>
+  </si>
+  <si>
+    <t>ei kirves kivehen koske,</t>
+  </si>
+  <si>
+    <t>ei kirves kiveen koske,</t>
+  </si>
+  <si>
+    <t>ei, kirves, kivi, koskea</t>
+  </si>
+  <si>
+    <t>not, axe, stone, to touch</t>
+  </si>
+  <si>
+    <t>kasa ei kalka kalliohon.</t>
+  </si>
+  <si>
+    <t>kasa ei kalka kallioon.</t>
+  </si>
+  <si>
+    <t>kasa, kalkahtaa, kallio</t>
+  </si>
+  <si>
+    <t>chip, to clang/strike, cliff</t>
+  </si>
+  <si>
+    <t>Niin päivällä kolmannella</t>
+  </si>
+  <si>
+    <t>niin, päivä, kolmas</t>
+  </si>
+  <si>
+    <t>so, day, third</t>
+  </si>
+  <si>
+    <t>Hiisi pontta pyörähytti,</t>
+  </si>
+  <si>
+    <t>Hiisi, pontta, pyörähyttää</t>
+  </si>
+  <si>
+    <t>Hiisi (evil spirit), notch/block, to whirl/spin</t>
+  </si>
+  <si>
+    <t>Hiisi (the malevolent spirit) and Lempo (the demon) intervening to spoil Väinämöinen's axe-work is the trickster being out-tricked by supernatural forces — the darker trickster powers of Hiisi subverting his creation.</t>
+  </si>
+  <si>
+    <t>Lempo tempasi tereä,</t>
+  </si>
+  <si>
+    <t>Lempo tempasi terän,</t>
+  </si>
+  <si>
+    <t>Lempo, tempoa, terä</t>
+  </si>
+  <si>
+    <t>Lempo (demon), to snatch/jerk, blade/edge</t>
+  </si>
+  <si>
+    <t>Paha vartta vaapahutti.</t>
+  </si>
+  <si>
+    <t>paha, varsi, vaapahtaa</t>
+  </si>
+  <si>
+    <t>evil/bad one, handle/shaft, to jerk/yank</t>
+  </si>
+  <si>
+    <t>Kävipä kivehen kirves,</t>
+  </si>
+  <si>
+    <t>Kävipä kiveen kirves,</t>
+  </si>
+  <si>
+    <t>käydä, kivi, kirves</t>
+  </si>
+  <si>
+    <t>to go/strike, stone, axe</t>
+  </si>
+  <si>
+    <t>kasa kalkkoi kalliohon;</t>
+  </si>
+  <si>
+    <t>kasa kalkkoi kallioon;</t>
+  </si>
+  <si>
+    <t>kasa, kalkkahtaa, kallio</t>
+  </si>
+  <si>
+    <t>chip, to clang, cliff</t>
+  </si>
+  <si>
+    <t>kirves kilpistyi kivestä,</t>
+  </si>
+  <si>
+    <t>kirves, kilpistyä, kivi</t>
+  </si>
+  <si>
+    <t>axe, to glance off, stone</t>
+  </si>
+  <si>
+    <t>terä liuskahti liha'an,</t>
+  </si>
+  <si>
+    <t>terä liuskahti lihaan,</t>
+  </si>
+  <si>
+    <t>terä, liuskahtaa, liha</t>
+  </si>
+  <si>
+    <t>blade, to slip/glance, flesh</t>
+  </si>
+  <si>
+    <t>polvehen pojan pätöisen,</t>
+  </si>
+  <si>
+    <t>polveen pojan pätöisen,</t>
+  </si>
+  <si>
+    <t>polvi, poika, pätöinen</t>
+  </si>
+  <si>
+    <t>into knee, son's, capable/worthy</t>
+  </si>
+  <si>
+    <t>varpahasen Väinämöisen.</t>
+  </si>
+  <si>
+    <t>varpaaseen Väinämöisen.</t>
+  </si>
+  <si>
+    <t>varvas, Väinämöinen</t>
+  </si>
+  <si>
+    <t>into toe, Väinämöinen's</t>
+  </si>
+  <si>
+    <t>Sen Lempo lihoille liitti,</t>
+  </si>
+  <si>
+    <t>Sen Lempo lihaan liitti,</t>
+  </si>
+  <si>
+    <t>se, Lempo, liha, liittää</t>
+  </si>
+  <si>
+    <t>that, Lempo, flesh, to attach/join</t>
+  </si>
+  <si>
+    <t>Hiisi suonille sovitti:</t>
+  </si>
+  <si>
+    <t>Hiisi, suoni, sovittaa</t>
+  </si>
+  <si>
+    <t>Hiisi, sinews, to fit/settle</t>
+  </si>
+  <si>
+    <t>Lempo driving the cut deeper into flesh and Hiisi fitting it to the sinews — the demons actively worsening the wound — confirms that supernatural trickster-forces are at work against Väinämöinen.</t>
+  </si>
+  <si>
+    <t>veri pääsi vuotamahan,</t>
+  </si>
+  <si>
+    <t>veri pääsi vuotamaan,</t>
+  </si>
+  <si>
+    <t>veri, päästä, vuotaa</t>
+  </si>
+  <si>
+    <t>blood, to get free, to flow</t>
+  </si>
+  <si>
+    <t>hurme huppelehtamahan.</t>
+  </si>
+  <si>
+    <t>hurme huppelehtamaan.</t>
+  </si>
+  <si>
+    <t>hurme, huppelehtaa</t>
+  </si>
+  <si>
+    <t>blood, to gush/flow freely</t>
+  </si>
+  <si>
+    <t>tuossa tuon sanoiksi virkki,</t>
+  </si>
+  <si>
+    <t>tuossa tuon sanoiksi sanoi,</t>
+  </si>
+  <si>
+    <t>noin on lausui ja pakisi:</t>
+  </si>
+  <si>
+    <t>niin lausui ja puhui:</t>
+  </si>
+  <si>
+    <t>niin, lausua, puhua</t>
+  </si>
+  <si>
+    <t>so, to utter, to speak</t>
+  </si>
+  <si>
+    <t>"Oi sie kirves kikkanokka,</t>
+  </si>
+  <si>
+    <t>"Oi sinä kirves kikkanokka,</t>
+  </si>
+  <si>
+    <t>oi, sinä, kirves, kikkanokka</t>
+  </si>
+  <si>
+    <t>oh, you, axe, hook-beaked/crooked-nosed</t>
+  </si>
+  <si>
+    <t>tasaterä tapparainen!</t>
+  </si>
+  <si>
+    <t>tasaterä, tappara</t>
+  </si>
+  <si>
+    <t>even-bladed, battle-axe</t>
+  </si>
+  <si>
+    <t>Luulitko puuta purrehesi,</t>
+  </si>
+  <si>
+    <t>luulla, puu, purra</t>
+  </si>
+  <si>
+    <t>to think, wood, to bite/gnaw</t>
+  </si>
+  <si>
+    <t>Väinämöinen's reproach to his axe — 'did you think I was wood? why did you bite flesh?' — is the shaman speaking to his tools as living agents, a characteristic trickster personification of objects.</t>
+  </si>
+  <si>
+    <t>honkoa hotaisnehesi,</t>
+  </si>
+  <si>
+    <t>honka, hotaista</t>
+  </si>
+  <si>
+    <t>pine, to snap at/lunge</t>
+  </si>
+  <si>
+    <t>petäjätä pannehesi,</t>
+  </si>
+  <si>
+    <t>petäjää pannehesi,</t>
+  </si>
+  <si>
+    <t>petäjä, panna</t>
+  </si>
+  <si>
+    <t>pine tree, to put/treat as</t>
+  </si>
+  <si>
+    <t>koivua kohannehesi,</t>
+  </si>
+  <si>
+    <t>koivu, kohdata</t>
+  </si>
+  <si>
+    <t>birch, to encounter/meet</t>
+  </si>
+  <si>
+    <t>kun sa lipsahit liha'an,</t>
+  </si>
+  <si>
+    <t>kun sinä lipsahit lihaan,</t>
+  </si>
+  <si>
+    <t>kun, sinä, lipsahtaa, liha</t>
+  </si>
+  <si>
+    <t>when, you, to slip/slide, flesh</t>
+  </si>
+  <si>
+    <t>solahutit suonilleni?"</t>
+  </si>
+  <si>
+    <t>solahtaa, suoni</t>
+  </si>
+  <si>
+    <t>to glide/sink, into my sinews</t>
+  </si>
+  <si>
+    <t>Loihe siitä loitsimahan,</t>
+  </si>
+  <si>
+    <t>Lähti siitä loitsimaan,</t>
+  </si>
+  <si>
+    <t>lähteä, loitsia</t>
+  </si>
+  <si>
+    <t>to set out, to chant/incant</t>
+  </si>
+  <si>
+    <t>sai itse sanelemahan.</t>
+  </si>
+  <si>
+    <t>sai itse sanelemaan.</t>
+  </si>
+  <si>
+    <t>to begin, himself, to recite/chant</t>
+  </si>
+  <si>
+    <t>Luki synnyt syitä myöten,</t>
+  </si>
+  <si>
+    <t>lukea, synty, syy</t>
+  </si>
+  <si>
+    <t>to read/recite, origins/births, reasons</t>
+  </si>
+  <si>
+    <t>luottehet lomia myöten,</t>
+  </si>
+  <si>
+    <t>luote, lomi</t>
+  </si>
+  <si>
+    <t>charms/spells, through the gaps/intervals</t>
+  </si>
+  <si>
+    <t>mutt' ei muista muutamia</t>
+  </si>
+  <si>
+    <t>mutta ei muistanut muutamia</t>
+  </si>
+  <si>
+    <t>mutta, ei, muistaa, muutama</t>
+  </si>
+  <si>
+    <t>but, not, to remember, some/certain</t>
+  </si>
+  <si>
+    <t>rauan suuria sanoja,</t>
+  </si>
+  <si>
+    <t>raudan suuria sanoja,</t>
+  </si>
+  <si>
+    <t>rauta, suuri, sana</t>
+  </si>
+  <si>
+    <t>iron's, great, words</t>
+  </si>
+  <si>
+    <t>Väinämöinen's failure to remember the iron-words — the specific magical formulas needed to stop the bleeding — is a rare gap in the master trickster-shaman's knowledge, driving him on a humiliating quest through three households.</t>
+  </si>
+  <si>
+    <t>joista salpa saataisihin,</t>
+  </si>
+  <si>
+    <t>joista, salpa, saada</t>
+  </si>
+  <si>
+    <t>from which, bolt/bar, to get</t>
+  </si>
+  <si>
+    <t>luja lukko tuotaisihin</t>
+  </si>
+  <si>
+    <t>luja, lukko, tuoda</t>
+  </si>
+  <si>
+    <t>firm, lock, to bring</t>
+  </si>
+  <si>
+    <t>noille rauan ratkomille,</t>
+  </si>
+  <si>
+    <t>noille raudan ratkomille,</t>
+  </si>
+  <si>
+    <t>tuo, rauta, ratkoa</t>
+  </si>
+  <si>
+    <t>those, iron's, unravellings/cuts</t>
+  </si>
+  <si>
+    <t>suu sinervän silpomille.</t>
+  </si>
+  <si>
+    <t>suu, sinervä, silpoa</t>
+  </si>
+  <si>
+    <t>mouth, bluish-grey, to hack/slash</t>
+  </si>
+  <si>
+    <t>Jo veri jokena juoksi,</t>
+  </si>
+  <si>
+    <t>jo, veri, joki, juosta</t>
+  </si>
+  <si>
+    <t>already, blood, as a river, to run</t>
+  </si>
+  <si>
+    <t>hurme koskena kohisi:</t>
+  </si>
+  <si>
+    <t>hurme, koski, kohista</t>
+  </si>
+  <si>
+    <t>blood, as rapids, to roar/surge</t>
+  </si>
+  <si>
+    <t>peitti maassa marjan varret,</t>
+  </si>
+  <si>
+    <t>peittää, maa, marja, varsi</t>
+  </si>
+  <si>
+    <t>to cover, earth, berry, plant/stalk</t>
+  </si>
+  <si>
+    <t>kanervaiset kankahalla.</t>
+  </si>
+  <si>
+    <t>kanervainen, kangas</t>
+  </si>
+  <si>
+    <t>heathery, heath/plain</t>
+  </si>
+  <si>
+    <t>Eik' ollut sitä mätästä,</t>
+  </si>
+  <si>
+    <t>Eikä ollut sitä mätästä,</t>
+  </si>
+  <si>
+    <t>ei, olla, se, mätäs</t>
+  </si>
+  <si>
+    <t>not, to be, that, tussock/mound</t>
+  </si>
+  <si>
+    <t>jok' ei tullut tulvillehen</t>
+  </si>
+  <si>
+    <t>joka ei tullut tulvillaan</t>
+  </si>
+  <si>
+    <t>joka, ei, tulla, tulvilla</t>
+  </si>
+  <si>
+    <t>which, not, to come, flooded</t>
+  </si>
+  <si>
+    <t>noita liikoja veriä,</t>
+  </si>
+  <si>
+    <t>tuo, liika, veri</t>
+  </si>
+  <si>
+    <t>those, excessive, blood</t>
+  </si>
+  <si>
+    <t>hurmehia huurovia</t>
+  </si>
+  <si>
+    <t>hurme, huuroa</t>
+  </si>
+  <si>
+    <t>blood, steaming/reeking</t>
+  </si>
+  <si>
+    <t>polvesta pojan totisen,</t>
+  </si>
+  <si>
+    <t>polvi, poika, totinen</t>
+  </si>
+  <si>
+    <t>from knee, son's, serious/earnest</t>
+  </si>
+  <si>
+    <t>varpahasta Väinämöisen.</t>
+  </si>
+  <si>
+    <t>from toe, Väinämöinen's</t>
+  </si>
+  <si>
+    <t>ketti villoja kiveltä,</t>
+  </si>
+  <si>
+    <t>kettoa, villa, kivi</t>
+  </si>
+  <si>
+    <t>to gather/pick, wools/fibres, stone</t>
+  </si>
+  <si>
+    <t>otti suolta sammalia,</t>
+  </si>
+  <si>
+    <t>ottaa, suo, sammal</t>
+  </si>
+  <si>
+    <t>to take, swamp, moss</t>
+  </si>
+  <si>
+    <t>maasta mättähän repäisi</t>
+  </si>
+  <si>
+    <t>maa, mätäs, repiä</t>
+  </si>
+  <si>
+    <t>earth, tussock, to tear/pull</t>
+  </si>
+  <si>
+    <t>tukkeheksi tuiman reiän,</t>
+  </si>
+  <si>
+    <t>tukki, tuima, reikä</t>
+  </si>
+  <si>
+    <t>as a plug, fierce/harsh, hole</t>
+  </si>
+  <si>
+    <t>paikaksi pahan veräjän;</t>
+  </si>
+  <si>
+    <t>paikka, paha, veräjä</t>
+  </si>
+  <si>
+    <t>as a patch, bad, gate/opening</t>
+  </si>
+  <si>
+    <t>ei vääjä vähäistäkänä,</t>
+  </si>
+  <si>
+    <t>ei vääjää vähäistäkään,</t>
+  </si>
+  <si>
+    <t>ei, vääjätä, vähäinen</t>
+  </si>
+  <si>
+    <t>not, to slow/stop, even a little</t>
+  </si>
+  <si>
+    <t>pikkuistakana piätä.</t>
+  </si>
+  <si>
+    <t>pikkuistakaan piätä.</t>
+  </si>
+  <si>
+    <t>pikkuinen, piätä</t>
+  </si>
+  <si>
+    <t>even a little, to stop/dam</t>
+  </si>
+  <si>
+    <t>Jopa tuskaksi tulevi,</t>
+  </si>
+  <si>
+    <t>Jo tuskaksi tulee,</t>
+  </si>
+  <si>
+    <t>itse itkuhun hyräytyi;</t>
+  </si>
+  <si>
+    <t>itse itkuun hyräytyi;</t>
+  </si>
+  <si>
+    <t>itse, itku, hyräyttää</t>
+  </si>
+  <si>
+    <t>himself, crying, to hum/murmur into</t>
+  </si>
+  <si>
+    <t>pani varsan valjahisin,</t>
+  </si>
+  <si>
+    <t>pani varsan valjaisiin,</t>
+  </si>
+  <si>
+    <t>ruskean re'en etehen,</t>
+  </si>
+  <si>
+    <t>ruskean reen eteen,</t>
+  </si>
+  <si>
+    <t>siitä reuoikse rekehen,</t>
+  </si>
+  <si>
+    <t>siitä reuoikse rekeen,</t>
+  </si>
+  <si>
+    <t>siitä, reutaista, reki</t>
+  </si>
+  <si>
+    <t>from that, to leap into, sled</t>
+  </si>
+  <si>
+    <t>kohennaikse korjahansa.</t>
+  </si>
+  <si>
+    <t>kohentautui korjaansa.</t>
+  </si>
+  <si>
+    <t>to settle/adjust, sleigh</t>
+  </si>
+  <si>
+    <t>Laski virkkua vitsalla,</t>
+  </si>
+  <si>
+    <t>laskea, virkku, vitsa</t>
+  </si>
+  <si>
+    <t>to let go/strike, lively, switch/whip</t>
+  </si>
+  <si>
+    <t>helähytti helmisvyöllä;</t>
+  </si>
+  <si>
+    <t>heläyttää, helmisvyö</t>
+  </si>
+  <si>
+    <t>to crack/snap, pearl-belt</t>
+  </si>
+  <si>
+    <t>virkku juoksi, matka joutui,</t>
+  </si>
+  <si>
+    <t>virkku, juosta, matka, joutua</t>
+  </si>
+  <si>
+    <t>lively (horse), to run, journey, to progress</t>
+  </si>
+  <si>
+    <t>reki vieri, tie lyheni.</t>
+  </si>
+  <si>
+    <t>reki, vierähtää, tie, lyhentyä</t>
+  </si>
+  <si>
+    <t>sled, to roll/glide, road, to shorten</t>
+  </si>
+  <si>
+    <t>Jo kohta kylä tulevi:</t>
+  </si>
+  <si>
+    <t>Jo kohta kylä tulee:</t>
+  </si>
+  <si>
+    <t>jo, kohta, kylä, tulla</t>
+  </si>
+  <si>
+    <t>already, soon, village, to come</t>
+  </si>
+  <si>
+    <t>kolme tietä kohtoavi.</t>
+  </si>
+  <si>
+    <t>kolme tietä kohtaa.</t>
+  </si>
+  <si>
+    <t>kolme, tie, kohdata</t>
+  </si>
+  <si>
+    <t>three, roads, to meet/encounter</t>
+  </si>
+  <si>
+    <t>The three crossroads and three houses Väinämöinen tries in search of a healer — each time refused — is a folktale formula, the trickster-hero humbled and dependent, forced to beg for help from strangers.</t>
+  </si>
+  <si>
+    <t>ajavi alinta tietä</t>
+  </si>
+  <si>
+    <t>ajaa alinta tietä</t>
+  </si>
+  <si>
+    <t>ajaa, alin, tie</t>
+  </si>
+  <si>
+    <t>to drive, lowest, road</t>
+  </si>
+  <si>
+    <t>alimaisehen talohon.</t>
+  </si>
+  <si>
+    <t>alimmaiseen taloon.</t>
+  </si>
+  <si>
+    <t>alin, talo</t>
+  </si>
+  <si>
+    <t>lowest, house</t>
+  </si>
+  <si>
+    <t>Yli kynnyksen kysyvi:</t>
+  </si>
+  <si>
+    <t>Yli kynnyksen kysyy:</t>
+  </si>
+  <si>
+    <t>yli, kynnys, kysyä</t>
+  </si>
+  <si>
+    <t>over, threshold, to ask</t>
+  </si>
+  <si>
+    <t>"Oisiko talossa tässä</t>
+  </si>
+  <si>
+    <t>"Olisiko talossa tässä</t>
+  </si>
+  <si>
+    <t>olla, talo, tässä</t>
+  </si>
+  <si>
+    <t>to be, house, here</t>
+  </si>
+  <si>
+    <t>rauan raannan katsojata,</t>
+  </si>
+  <si>
+    <t>raudan raannan katsojaa,</t>
+  </si>
+  <si>
+    <t>rauta, raanta, katsoja</t>
+  </si>
+  <si>
+    <t>iron's, wound/cut, looker/examiner</t>
+  </si>
+  <si>
+    <t>uron tuskan tuntijata,</t>
+  </si>
+  <si>
+    <t>uron tuskan tuntijaa,</t>
+  </si>
+  <si>
+    <t>uros, tuska, tuntija</t>
+  </si>
+  <si>
+    <t>hero's, anguish/pain, knower</t>
+  </si>
+  <si>
+    <t>vammojen vakittajata?"</t>
+  </si>
+  <si>
+    <t>vammojen vakittajaa?"</t>
+  </si>
+  <si>
+    <t>vamma, vakittaja</t>
+  </si>
+  <si>
+    <t>wounds, fixer/binder</t>
+  </si>
+  <si>
+    <t>Olipa lapsi lattialla,</t>
+  </si>
+  <si>
+    <t>olla, lapsi, lattia</t>
+  </si>
+  <si>
+    <t>to be, child, floor</t>
+  </si>
+  <si>
+    <t>poika pieni pankon päässä.</t>
+  </si>
+  <si>
+    <t>poika, pieni, pankko</t>
+  </si>
+  <si>
+    <t>boy, small, shelf/bench end</t>
+  </si>
+  <si>
+    <t>Tuop' on tuohon vastoavi:</t>
+  </si>
+  <si>
+    <t>Tuopa tuohon vastaa:</t>
+  </si>
+  <si>
+    <t>"Ei ole talossa tässä</t>
+  </si>
+  <si>
+    <t>ei, olla, talo, tässä</t>
+  </si>
+  <si>
+    <t>not, to be, house, here</t>
+  </si>
+  <si>
+    <t>iron's, wound, looker/examiner</t>
+  </si>
+  <si>
+    <t>hero's, anguish, knower</t>
+  </si>
+  <si>
+    <t>kivun kiinniottajata,</t>
+  </si>
+  <si>
+    <t>kivun kiinniottajaa,</t>
+  </si>
+  <si>
+    <t>kipu, kiinniottaja</t>
+  </si>
+  <si>
+    <t>pain, catcher/stopper</t>
+  </si>
+  <si>
+    <t>vammojen vakittajata;</t>
+  </si>
+  <si>
+    <t>vammojen vakittajaa;</t>
+  </si>
+  <si>
+    <t>wounds, fixer</t>
+  </si>
+  <si>
+    <t>onpi toisessa talossa:</t>
+  </si>
+  <si>
+    <t>onpa toisessa talossa:</t>
+  </si>
+  <si>
+    <t>olla, toinen, talo</t>
+  </si>
+  <si>
+    <t>to be, another, house</t>
+  </si>
+  <si>
+    <t>aja toisehen talohon!"</t>
+  </si>
+  <si>
+    <t>aja toiseen taloon!"</t>
+  </si>
+  <si>
+    <t>ajaa, toinen, talo</t>
+  </si>
+  <si>
+    <t>to drive, another, house</t>
+  </si>
+  <si>
+    <t>laski virkkua vitsalla,</t>
+  </si>
+  <si>
+    <t>ajoa suhuttelevi.</t>
+  </si>
+  <si>
+    <t>ajoa suhuttelee.</t>
+  </si>
+  <si>
+    <t>to drive, journey, a piece</t>
+  </si>
+  <si>
+    <t>keskimäistä tietä myöten</t>
+  </si>
+  <si>
+    <t>keski, tie, myöten</t>
+  </si>
+  <si>
+    <t>middle, road, along</t>
+  </si>
+  <si>
+    <t>keskimäisehen talohon.</t>
+  </si>
+  <si>
+    <t>keskimmäiseen taloon.</t>
+  </si>
+  <si>
+    <t>keski, talo</t>
+  </si>
+  <si>
+    <t>middle, house</t>
+  </si>
+  <si>
+    <t>Kysyi kynnyksen takoa,</t>
+  </si>
+  <si>
+    <t>Kysyi kynnyksen takaa,</t>
+  </si>
+  <si>
+    <t>kysyä, kynnys, takaa</t>
+  </si>
+  <si>
+    <t>to ask, threshold, from behind</t>
+  </si>
+  <si>
+    <t>anoi alta ikkunaisen:</t>
+  </si>
+  <si>
+    <t>anoi alta ikkunan:</t>
+  </si>
+  <si>
+    <t>anoa, alta, ikkuna</t>
+  </si>
+  <si>
+    <t>to beg/ask, from under, window</t>
+  </si>
+  <si>
+    <t>salpoa verisatehen,</t>
+  </si>
+  <si>
+    <t>salata, veri, sade</t>
+  </si>
+  <si>
+    <t>to dam/stop, blood, rain/shower</t>
+  </si>
+  <si>
+    <t>suonikosken sortajata?"</t>
+  </si>
+  <si>
+    <t>suonivirran sortajaa?"</t>
+  </si>
+  <si>
+    <t>suoni, koski/virta, sortaa</t>
+  </si>
+  <si>
+    <t>sinew/vein, rapids/stream, to topple/dam</t>
+  </si>
+  <si>
+    <t>Akka oli vanha vaipan alla,</t>
+  </si>
+  <si>
+    <t>akka, vanha, vaippa, alla</t>
+  </si>
+  <si>
+    <t>old woman, old, cloak/wrap, under</t>
+  </si>
+  <si>
+    <t>kielipalku pankon päässä.</t>
+  </si>
+  <si>
+    <t>kielipalku, pankko</t>
+  </si>
+  <si>
+    <t>tongue-beam (talkative one), shelf/bench end</t>
+  </si>
+  <si>
+    <t>Akka varsin vastaeli,</t>
+  </si>
+  <si>
+    <t>Akka varsin vastasi,</t>
+  </si>
+  <si>
+    <t>akka, varsin, vastata</t>
+  </si>
+  <si>
+    <t>old woman, quite/truly, to answer</t>
+  </si>
+  <si>
+    <t>hammas kolmi kolkkaeli:</t>
+  </si>
+  <si>
+    <t>hammas kolme kolkkaeli:</t>
+  </si>
+  <si>
+    <t>hammas, kolme, kolkahtaa</t>
+  </si>
+  <si>
+    <t>tooth, three, to clatter/knock</t>
+  </si>
+  <si>
+    <t>iron's, wound, looker</t>
+  </si>
+  <si>
+    <t>verisynnyn tietäjätä,</t>
+  </si>
+  <si>
+    <t>verisynnyn tietäjää,</t>
+  </si>
+  <si>
+    <t>veri, synty, tietäjä</t>
+  </si>
+  <si>
+    <t>blood's, origin/birth, wise man/knower</t>
+  </si>
+  <si>
+    <t>kivun kiinniottajata;</t>
+  </si>
+  <si>
+    <t>kivun kiinniottajaa;</t>
+  </si>
+  <si>
+    <t>ylimäistä tietä myöten</t>
+  </si>
+  <si>
+    <t>ylimmäistä tietä myöten</t>
+  </si>
+  <si>
+    <t>ylin, tie, myöten</t>
+  </si>
+  <si>
+    <t>highest/upper, road, along</t>
+  </si>
+  <si>
+    <t>ylimäisehen talohon.</t>
+  </si>
+  <si>
+    <t>ylimmäiseen taloon.</t>
+  </si>
+  <si>
+    <t>ylin, talo</t>
+  </si>
+  <si>
+    <t>highest/upper, house</t>
+  </si>
+  <si>
+    <t>Yli kynnyksen kysyvi,</t>
+  </si>
+  <si>
+    <t>Yli kynnyksen kysyy,</t>
+  </si>
+  <si>
+    <t>lausui lakkapuun takoa:</t>
+  </si>
+  <si>
+    <t>lausui lakkapuun takaa:</t>
+  </si>
+  <si>
+    <t>lausua, lakkapuu</t>
+  </si>
+  <si>
+    <t>to utter, from behind the ridge-post</t>
+  </si>
+  <si>
+    <t>tämän tulvan tukkijata,</t>
+  </si>
+  <si>
+    <t>tämän tulvan tukkijaa,</t>
+  </si>
+  <si>
+    <t>tämä, tulva, tukkia</t>
+  </si>
+  <si>
+    <t>this, flood/surge, stopper</t>
+  </si>
+  <si>
+    <t>veren summan sulkijata?"</t>
+  </si>
+  <si>
+    <t>veren summan sulkijaa?"</t>
+  </si>
+  <si>
+    <t>veri, summa, sulkea</t>
+  </si>
+  <si>
+    <t>blood's, great amount/sum, stopper/closer</t>
+  </si>
+  <si>
+    <t>Ukko oli uunilla asuva,</t>
+  </si>
+  <si>
+    <t>ukko, olla, uuni, asua</t>
+  </si>
+  <si>
+    <t>old man, to be, stove/oven, to live/sit</t>
+  </si>
+  <si>
+    <t>halliparta harjun alla.</t>
+  </si>
+  <si>
+    <t>halliparta, harju</t>
+  </si>
+  <si>
+    <t>grey-beard, esker/ridge</t>
+  </si>
+  <si>
+    <t>Ukko uunilta urahti,</t>
+  </si>
+  <si>
+    <t>ukko, uuni, urata</t>
+  </si>
+  <si>
+    <t>old man, from stove, to grunt/growl</t>
+  </si>
+  <si>
+    <t>halliparta paukutteli:</t>
+  </si>
+  <si>
+    <t>halliparta, paukuttaa</t>
+  </si>
+  <si>
+    <t>grey-beard, to bang/thump</t>
+  </si>
+  <si>
+    <t>"On sulettu suuremmatki,</t>
+  </si>
+  <si>
+    <t>"On suljettu suuremmatkin,</t>
+  </si>
+  <si>
+    <t>olla, sulkea, suuri</t>
+  </si>
+  <si>
+    <t>to be, closed/stopped, greater</t>
+  </si>
+  <si>
+    <t>The grey-bearded old man on the stove — the third and successful healer — claims that greater floods have been stopped with three words of the Creator and the deep origins formula: rivers from their mouths, lakes from their heads, angry currents from their necks. His confident boast sets up the healing to come in the next runo.</t>
+  </si>
+  <si>
+    <t>jalommatki jaksettuna</t>
+  </si>
+  <si>
+    <t>jalommatkin jaksettu</t>
+  </si>
+  <si>
+    <t>jalo, jaksaa</t>
+  </si>
+  <si>
+    <t>nobler/finer ones too, managed/accomplished</t>
+  </si>
+  <si>
+    <t>Luojan kolmella sanalla,</t>
+  </si>
+  <si>
+    <t>Luoja, kolme, sana</t>
+  </si>
+  <si>
+    <t>Creator's/God's, three, words</t>
+  </si>
+  <si>
+    <t>syvän synnyn säätämällä:</t>
+  </si>
+  <si>
+    <t>syvä, synty, säätää</t>
+  </si>
+  <si>
+    <t>deep, origin/birth, to regulate/ordain</t>
+  </si>
+  <si>
+    <t>joet suista, järvet päistä,</t>
+  </si>
+  <si>
+    <t>joki, suu, järvi, pää</t>
+  </si>
+  <si>
+    <t>rivers, from mouths, lakes, from heads</t>
+  </si>
+  <si>
+    <t>virrat niskalta vihaiset,</t>
+  </si>
+  <si>
+    <t>virta, niska, vihainen</t>
+  </si>
+  <si>
+    <t>streams/currents, from neck, angry/fierce</t>
+  </si>
+  <si>
+    <t>lahet niemien nenistä,</t>
+  </si>
+  <si>
+    <t>lahti, niemi, nenä</t>
+  </si>
+  <si>
+    <t>bays, headlands', tips</t>
+  </si>
+  <si>
+    <t>kannakset kape'immilta."</t>
+  </si>
+  <si>
+    <t>kannakset kapeimmilta."</t>
+  </si>
+  <si>
+    <t>kannas, kapea</t>
+  </si>
+  <si>
+    <t>isthmuses/necks, narrowest</t>
   </si>
 </sst>
 </file>
@@ -25657,7 +28132,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7BF64756-3F7A-4FC1-A800-775B3843C6BA}" name="Table1" displayName="Table1" ref="A1:G2646" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7BF64756-3F7A-4FC1-A800-775B3843C6BA}" name="Table1" displayName="Table1" ref="A1:G2928" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{076FBF39-E03A-429D-B22F-E97723D41E45}" name="Runo" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{12FCAC6C-E61E-453B-B9A4-0B45BEB02CA4}" name="Rivi" dataDxfId="5"/>
@@ -25956,7 +28431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2646"/>
+  <dimension ref="A1:G2928"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.5703125" style="7" bestFit="1" customWidth="1"/>
@@ -81813,6 +84288,5962 @@
       </c>
       <c r="G2646" s="6"/>
     </row>
+    <row r="2647" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2647" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2647" s="8">
+        <v>1</v>
+      </c>
+      <c r="C2647" s="3" t="s">
+        <v>8430</v>
+      </c>
+      <c r="D2647" s="3" t="s">
+        <v>8430</v>
+      </c>
+      <c r="E2647" s="3" t="s">
+        <v>8431</v>
+      </c>
+      <c r="F2647" s="3" t="s">
+        <v>8432</v>
+      </c>
+      <c r="G2647" s="4"/>
+    </row>
+    <row r="2648" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2648" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2648" s="8">
+        <v>2</v>
+      </c>
+      <c r="C2648" s="3" t="s">
+        <v>8433</v>
+      </c>
+      <c r="D2648" s="3" t="s">
+        <v>8434</v>
+      </c>
+      <c r="E2648" s="3" t="s">
+        <v>8435</v>
+      </c>
+      <c r="F2648" s="3" t="s">
+        <v>8436</v>
+      </c>
+      <c r="G2648" s="4"/>
+    </row>
+    <row r="2649" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2649" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2649" s="8">
+        <v>3</v>
+      </c>
+      <c r="C2649" s="3" t="s">
+        <v>8437</v>
+      </c>
+      <c r="D2649" s="3" t="s">
+        <v>8437</v>
+      </c>
+      <c r="E2649" s="3" t="s">
+        <v>8438</v>
+      </c>
+      <c r="F2649" s="3" t="s">
+        <v>8439</v>
+      </c>
+      <c r="G2649" s="4" t="s">
+        <v>8440</v>
+      </c>
+    </row>
+    <row r="2650" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2650" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2650" s="8">
+        <v>4</v>
+      </c>
+      <c r="C2650" s="3" t="s">
+        <v>8441</v>
+      </c>
+      <c r="D2650" s="3" t="s">
+        <v>8442</v>
+      </c>
+      <c r="E2650" s="3" t="s">
+        <v>8443</v>
+      </c>
+      <c r="F2650" s="3" t="s">
+        <v>8444</v>
+      </c>
+      <c r="G2650" s="4"/>
+    </row>
+    <row r="2651" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2651" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2651" s="8">
+        <v>5</v>
+      </c>
+      <c r="C2651" s="3" t="s">
+        <v>8445</v>
+      </c>
+      <c r="D2651" s="3" t="s">
+        <v>8446</v>
+      </c>
+      <c r="E2651" s="3" t="s">
+        <v>8447</v>
+      </c>
+      <c r="F2651" s="3" t="s">
+        <v>8448</v>
+      </c>
+      <c r="G2651" s="4"/>
+    </row>
+    <row r="2652" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2652" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2652" s="8">
+        <v>6</v>
+      </c>
+      <c r="C2652" s="3" t="s">
+        <v>8449</v>
+      </c>
+      <c r="D2652" s="3" t="s">
+        <v>8450</v>
+      </c>
+      <c r="E2652" s="3" t="s">
+        <v>8451</v>
+      </c>
+      <c r="F2652" s="3" t="s">
+        <v>8452</v>
+      </c>
+      <c r="G2652" s="4"/>
+    </row>
+    <row r="2653" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2653" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2653" s="8">
+        <v>7</v>
+      </c>
+      <c r="C2653" s="3" t="s">
+        <v>8453</v>
+      </c>
+      <c r="D2653" s="3" t="s">
+        <v>8454</v>
+      </c>
+      <c r="E2653" s="3" t="s">
+        <v>8455</v>
+      </c>
+      <c r="F2653" s="3" t="s">
+        <v>8456</v>
+      </c>
+      <c r="G2653" s="4"/>
+    </row>
+    <row r="2654" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2654" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2654" s="8">
+        <v>8</v>
+      </c>
+      <c r="C2654" s="3" t="s">
+        <v>8457</v>
+      </c>
+      <c r="D2654" s="3" t="s">
+        <v>8458</v>
+      </c>
+      <c r="E2654" s="3" t="s">
+        <v>6744</v>
+      </c>
+      <c r="F2654" s="3" t="s">
+        <v>6745</v>
+      </c>
+      <c r="G2654" s="4"/>
+    </row>
+    <row r="2655" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2655" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2655" s="8">
+        <v>9</v>
+      </c>
+      <c r="C2655" s="3" t="s">
+        <v>8459</v>
+      </c>
+      <c r="D2655" s="3" t="s">
+        <v>8459</v>
+      </c>
+      <c r="E2655" s="3" t="s">
+        <v>8460</v>
+      </c>
+      <c r="F2655" s="3" t="s">
+        <v>8461</v>
+      </c>
+      <c r="G2655" s="4"/>
+    </row>
+    <row r="2656" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2656" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2656" s="8">
+        <v>10</v>
+      </c>
+      <c r="C2656" s="3" t="s">
+        <v>8462</v>
+      </c>
+      <c r="D2656" s="3" t="s">
+        <v>8463</v>
+      </c>
+      <c r="E2656" s="3" t="s">
+        <v>8464</v>
+      </c>
+      <c r="F2656" s="3" t="s">
+        <v>8465</v>
+      </c>
+      <c r="G2656" s="4"/>
+    </row>
+    <row r="2657" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2657" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2657" s="8">
+        <v>11</v>
+      </c>
+      <c r="C2657" s="3" t="s">
+        <v>8466</v>
+      </c>
+      <c r="D2657" s="3" t="s">
+        <v>8467</v>
+      </c>
+      <c r="E2657" s="3" t="s">
+        <v>8468</v>
+      </c>
+      <c r="F2657" s="3" t="s">
+        <v>8469</v>
+      </c>
+      <c r="G2657" s="4"/>
+    </row>
+    <row r="2658" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2658" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2658" s="8">
+        <v>12</v>
+      </c>
+      <c r="C2658" s="3" t="s">
+        <v>8470</v>
+      </c>
+      <c r="D2658" s="3" t="s">
+        <v>8471</v>
+      </c>
+      <c r="E2658" s="3" t="s">
+        <v>8472</v>
+      </c>
+      <c r="F2658" s="3" t="s">
+        <v>8473</v>
+      </c>
+      <c r="G2658" s="4"/>
+    </row>
+    <row r="2659" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2659" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2659" s="8">
+        <v>13</v>
+      </c>
+      <c r="C2659" s="3" t="s">
+        <v>8474</v>
+      </c>
+      <c r="D2659" s="3" t="s">
+        <v>8474</v>
+      </c>
+      <c r="E2659" s="3" t="s">
+        <v>8475</v>
+      </c>
+      <c r="F2659" s="3" t="s">
+        <v>8476</v>
+      </c>
+      <c r="G2659" s="4"/>
+    </row>
+    <row r="2660" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2660" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2660" s="8">
+        <v>14</v>
+      </c>
+      <c r="C2660" s="3" t="s">
+        <v>8477</v>
+      </c>
+      <c r="D2660" s="3" t="s">
+        <v>8478</v>
+      </c>
+      <c r="E2660" s="3" t="s">
+        <v>8479</v>
+      </c>
+      <c r="F2660" s="3" t="s">
+        <v>8480</v>
+      </c>
+      <c r="G2660" s="4"/>
+    </row>
+    <row r="2661" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2661" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2661" s="8">
+        <v>15</v>
+      </c>
+      <c r="C2661" s="3" t="s">
+        <v>8481</v>
+      </c>
+      <c r="D2661" s="3" t="s">
+        <v>8482</v>
+      </c>
+      <c r="E2661" s="3" t="s">
+        <v>8483</v>
+      </c>
+      <c r="F2661" s="3" t="s">
+        <v>8484</v>
+      </c>
+      <c r="G2661" s="4"/>
+    </row>
+    <row r="2662" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2662" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2662" s="8">
+        <v>16</v>
+      </c>
+      <c r="C2662" s="3" t="s">
+        <v>8485</v>
+      </c>
+      <c r="D2662" s="3" t="s">
+        <v>8486</v>
+      </c>
+      <c r="E2662" s="3" t="s">
+        <v>6744</v>
+      </c>
+      <c r="F2662" s="3" t="s">
+        <v>8487</v>
+      </c>
+      <c r="G2662" s="4"/>
+    </row>
+    <row r="2663" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2663" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2663" s="8">
+        <v>17</v>
+      </c>
+      <c r="C2663" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D2663" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E2663" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F2663" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G2663" s="4"/>
+    </row>
+    <row r="2664" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2664" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2664" s="8">
+        <v>18</v>
+      </c>
+      <c r="C2664" s="3" t="s">
+        <v>8488</v>
+      </c>
+      <c r="D2664" s="3" t="s">
+        <v>8489</v>
+      </c>
+      <c r="E2664" s="3" t="s">
+        <v>4004</v>
+      </c>
+      <c r="F2664" s="3" t="s">
+        <v>4005</v>
+      </c>
+      <c r="G2664" s="4"/>
+    </row>
+    <row r="2665" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2665" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2665" s="8">
+        <v>19</v>
+      </c>
+      <c r="C2665" s="3" t="s">
+        <v>8426</v>
+      </c>
+      <c r="D2665" s="3" t="s">
+        <v>8426</v>
+      </c>
+      <c r="E2665" s="3" t="s">
+        <v>6649</v>
+      </c>
+      <c r="F2665" s="3" t="s">
+        <v>8427</v>
+      </c>
+      <c r="G2665" s="4"/>
+    </row>
+    <row r="2666" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2666" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2666" s="8">
+        <v>20</v>
+      </c>
+      <c r="C2666" s="3" t="s">
+        <v>8428</v>
+      </c>
+      <c r="D2666" s="3" t="s">
+        <v>8428</v>
+      </c>
+      <c r="E2666" s="3" t="s">
+        <v>7690</v>
+      </c>
+      <c r="F2666" s="3" t="s">
+        <v>8429</v>
+      </c>
+      <c r="G2666" s="4"/>
+    </row>
+    <row r="2667" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2667" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2667" s="8">
+        <v>21</v>
+      </c>
+      <c r="C2667" s="3" t="s">
+        <v>8490</v>
+      </c>
+      <c r="D2667" s="3" t="s">
+        <v>8491</v>
+      </c>
+      <c r="E2667" s="3" t="s">
+        <v>8492</v>
+      </c>
+      <c r="F2667" s="3" t="s">
+        <v>8493</v>
+      </c>
+      <c r="G2667" s="4"/>
+    </row>
+    <row r="2668" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2668" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2668" s="8">
+        <v>22</v>
+      </c>
+      <c r="C2668" s="3" t="s">
+        <v>8494</v>
+      </c>
+      <c r="D2668" s="3" t="s">
+        <v>8494</v>
+      </c>
+      <c r="E2668" s="3" t="s">
+        <v>8495</v>
+      </c>
+      <c r="F2668" s="3" t="s">
+        <v>8496</v>
+      </c>
+      <c r="G2668" s="4"/>
+    </row>
+    <row r="2669" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2669" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2669" s="8">
+        <v>23</v>
+      </c>
+      <c r="C2669" s="3" t="s">
+        <v>8497</v>
+      </c>
+      <c r="D2669" s="3" t="s">
+        <v>8497</v>
+      </c>
+      <c r="E2669" s="3" t="s">
+        <v>8498</v>
+      </c>
+      <c r="F2669" s="3" t="s">
+        <v>8499</v>
+      </c>
+      <c r="G2669" s="4"/>
+    </row>
+    <row r="2670" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2670" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2670" s="8">
+        <v>24</v>
+      </c>
+      <c r="C2670" s="3" t="s">
+        <v>8500</v>
+      </c>
+      <c r="D2670" s="3" t="s">
+        <v>8500</v>
+      </c>
+      <c r="E2670" s="3" t="s">
+        <v>8501</v>
+      </c>
+      <c r="F2670" s="3" t="s">
+        <v>8502</v>
+      </c>
+      <c r="G2670" s="4"/>
+    </row>
+    <row r="2671" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2671" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2671" s="8">
+        <v>25</v>
+      </c>
+      <c r="C2671" s="3" t="s">
+        <v>8503</v>
+      </c>
+      <c r="D2671" s="3" t="s">
+        <v>8503</v>
+      </c>
+      <c r="E2671" s="3" t="s">
+        <v>8504</v>
+      </c>
+      <c r="F2671" s="3" t="s">
+        <v>8505</v>
+      </c>
+      <c r="G2671" s="4" t="s">
+        <v>8506</v>
+      </c>
+    </row>
+    <row r="2672" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2672" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2672" s="8">
+        <v>26</v>
+      </c>
+      <c r="C2672" s="3" t="s">
+        <v>8507</v>
+      </c>
+      <c r="D2672" s="3" t="s">
+        <v>8508</v>
+      </c>
+      <c r="E2672" s="3" t="s">
+        <v>8509</v>
+      </c>
+      <c r="F2672" s="3" t="s">
+        <v>8510</v>
+      </c>
+      <c r="G2672" s="4"/>
+    </row>
+    <row r="2673" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2673" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2673" s="8">
+        <v>27</v>
+      </c>
+      <c r="C2673" s="3" t="s">
+        <v>8511</v>
+      </c>
+      <c r="D2673" s="3" t="s">
+        <v>8512</v>
+      </c>
+      <c r="E2673" s="3" t="s">
+        <v>8513</v>
+      </c>
+      <c r="F2673" s="3" t="s">
+        <v>8514</v>
+      </c>
+      <c r="G2673" s="4"/>
+    </row>
+    <row r="2674" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2674" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2674" s="8">
+        <v>28</v>
+      </c>
+      <c r="C2674" s="3" t="s">
+        <v>8515</v>
+      </c>
+      <c r="D2674" s="3" t="s">
+        <v>8515</v>
+      </c>
+      <c r="E2674" s="3" t="s">
+        <v>8516</v>
+      </c>
+      <c r="F2674" s="3" t="s">
+        <v>8517</v>
+      </c>
+      <c r="G2674" s="4"/>
+    </row>
+    <row r="2675" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2675" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2675" s="8">
+        <v>29</v>
+      </c>
+      <c r="C2675" s="3" t="s">
+        <v>8453</v>
+      </c>
+      <c r="D2675" s="3" t="s">
+        <v>8454</v>
+      </c>
+      <c r="E2675" s="3" t="s">
+        <v>8455</v>
+      </c>
+      <c r="F2675" s="3" t="s">
+        <v>8518</v>
+      </c>
+      <c r="G2675" s="4"/>
+    </row>
+    <row r="2676" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2676" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2676" s="8">
+        <v>30</v>
+      </c>
+      <c r="C2676" s="3" t="s">
+        <v>8519</v>
+      </c>
+      <c r="D2676" s="3" t="s">
+        <v>8520</v>
+      </c>
+      <c r="E2676" s="3" t="s">
+        <v>8521</v>
+      </c>
+      <c r="F2676" s="3" t="s">
+        <v>8522</v>
+      </c>
+      <c r="G2676" s="4"/>
+    </row>
+    <row r="2677" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2677" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2677" s="8">
+        <v>31</v>
+      </c>
+      <c r="C2677" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D2677" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E2677" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F2677" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G2677" s="4"/>
+    </row>
+    <row r="2678" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2678" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2678" s="8">
+        <v>32</v>
+      </c>
+      <c r="C2678" s="3" t="s">
+        <v>8523</v>
+      </c>
+      <c r="D2678" s="3" t="s">
+        <v>8523</v>
+      </c>
+      <c r="E2678" s="3" t="s">
+        <v>8524</v>
+      </c>
+      <c r="F2678" s="3" t="s">
+        <v>8525</v>
+      </c>
+      <c r="G2678" s="4"/>
+    </row>
+    <row r="2679" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2679" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2679" s="8">
+        <v>33</v>
+      </c>
+      <c r="C2679" s="3" t="s">
+        <v>8526</v>
+      </c>
+      <c r="D2679" s="3" t="s">
+        <v>8527</v>
+      </c>
+      <c r="E2679" s="3" t="s">
+        <v>8528</v>
+      </c>
+      <c r="F2679" s="3" t="s">
+        <v>8529</v>
+      </c>
+      <c r="G2679" s="4"/>
+    </row>
+    <row r="2680" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2680" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2680" s="8">
+        <v>34</v>
+      </c>
+      <c r="C2680" s="3" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D2680" s="3" t="s">
+        <v>1706</v>
+      </c>
+      <c r="E2680" s="3" t="s">
+        <v>7070</v>
+      </c>
+      <c r="F2680" s="3" t="s">
+        <v>7071</v>
+      </c>
+      <c r="G2680" s="4"/>
+    </row>
+    <row r="2681" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2681" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2681" s="8">
+        <v>35</v>
+      </c>
+      <c r="C2681" s="3" t="s">
+        <v>8530</v>
+      </c>
+      <c r="D2681" s="3" t="s">
+        <v>8531</v>
+      </c>
+      <c r="E2681" s="3" t="s">
+        <v>8532</v>
+      </c>
+      <c r="F2681" s="3" t="s">
+        <v>8533</v>
+      </c>
+      <c r="G2681" s="4" t="s">
+        <v>8534</v>
+      </c>
+    </row>
+    <row r="2682" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2682" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2682" s="8">
+        <v>36</v>
+      </c>
+      <c r="C2682" s="3" t="s">
+        <v>8535</v>
+      </c>
+      <c r="D2682" s="3" t="s">
+        <v>8536</v>
+      </c>
+      <c r="E2682" s="3" t="s">
+        <v>8537</v>
+      </c>
+      <c r="F2682" s="3" t="s">
+        <v>8538</v>
+      </c>
+      <c r="G2682" s="4"/>
+    </row>
+    <row r="2683" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2683" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2683" s="8">
+        <v>37</v>
+      </c>
+      <c r="C2683" s="3" t="s">
+        <v>8539</v>
+      </c>
+      <c r="D2683" s="3" t="s">
+        <v>8540</v>
+      </c>
+      <c r="E2683" s="3" t="s">
+        <v>4382</v>
+      </c>
+      <c r="F2683" s="3" t="s">
+        <v>4383</v>
+      </c>
+      <c r="G2683" s="4"/>
+    </row>
+    <row r="2684" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2684" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2684" s="8">
+        <v>38</v>
+      </c>
+      <c r="C2684" s="3" t="s">
+        <v>8541</v>
+      </c>
+      <c r="D2684" s="3" t="s">
+        <v>8542</v>
+      </c>
+      <c r="E2684" s="3" t="s">
+        <v>8543</v>
+      </c>
+      <c r="F2684" s="3" t="s">
+        <v>8544</v>
+      </c>
+      <c r="G2684" s="4"/>
+    </row>
+    <row r="2685" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2685" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2685" s="8">
+        <v>39</v>
+      </c>
+      <c r="C2685" s="3" t="s">
+        <v>8545</v>
+      </c>
+      <c r="D2685" s="3" t="s">
+        <v>8546</v>
+      </c>
+      <c r="E2685" s="3" t="s">
+        <v>8547</v>
+      </c>
+      <c r="F2685" s="3" t="s">
+        <v>8548</v>
+      </c>
+      <c r="G2685" s="4"/>
+    </row>
+    <row r="2686" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2686" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2686" s="8">
+        <v>40</v>
+      </c>
+      <c r="C2686" s="3" t="s">
+        <v>8549</v>
+      </c>
+      <c r="D2686" s="3" t="s">
+        <v>8550</v>
+      </c>
+      <c r="E2686" s="3" t="s">
+        <v>8551</v>
+      </c>
+      <c r="F2686" s="3" t="s">
+        <v>8552</v>
+      </c>
+      <c r="G2686" s="4"/>
+    </row>
+    <row r="2687" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2687" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2687" s="8">
+        <v>41</v>
+      </c>
+      <c r="C2687" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D2687" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E2687" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F2687" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G2687" s="4"/>
+    </row>
+    <row r="2688" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2688" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2688" s="8">
+        <v>42</v>
+      </c>
+      <c r="C2688" s="3" t="s">
+        <v>8553</v>
+      </c>
+      <c r="D2688" s="3" t="s">
+        <v>8554</v>
+      </c>
+      <c r="E2688" s="3" t="s">
+        <v>8555</v>
+      </c>
+      <c r="F2688" s="3" t="s">
+        <v>8556</v>
+      </c>
+      <c r="G2688" s="4"/>
+    </row>
+    <row r="2689" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2689" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2689" s="8">
+        <v>43</v>
+      </c>
+      <c r="C2689" s="3" t="s">
+        <v>8557</v>
+      </c>
+      <c r="D2689" s="3" t="s">
+        <v>8558</v>
+      </c>
+      <c r="E2689" s="3" t="s">
+        <v>8559</v>
+      </c>
+      <c r="F2689" s="3" t="s">
+        <v>8560</v>
+      </c>
+      <c r="G2689" s="4"/>
+    </row>
+    <row r="2690" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2690" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2690" s="8">
+        <v>44</v>
+      </c>
+      <c r="C2690" s="3" t="s">
+        <v>8561</v>
+      </c>
+      <c r="D2690" s="3" t="s">
+        <v>8562</v>
+      </c>
+      <c r="E2690" s="3" t="s">
+        <v>8551</v>
+      </c>
+      <c r="F2690" s="3" t="s">
+        <v>8563</v>
+      </c>
+      <c r="G2690" s="4"/>
+    </row>
+    <row r="2691" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2691" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2691" s="8">
+        <v>45</v>
+      </c>
+      <c r="C2691" s="3" t="s">
+        <v>6276</v>
+      </c>
+      <c r="D2691" s="3" t="s">
+        <v>6276</v>
+      </c>
+      <c r="E2691" s="3" t="s">
+        <v>3928</v>
+      </c>
+      <c r="F2691" s="3" t="s">
+        <v>3929</v>
+      </c>
+      <c r="G2691" s="4"/>
+    </row>
+    <row r="2692" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2692" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2692" s="8">
+        <v>46</v>
+      </c>
+      <c r="C2692" s="3" t="s">
+        <v>8564</v>
+      </c>
+      <c r="D2692" s="3" t="s">
+        <v>8564</v>
+      </c>
+      <c r="E2692" s="3" t="s">
+        <v>8565</v>
+      </c>
+      <c r="F2692" s="3" t="s">
+        <v>8566</v>
+      </c>
+      <c r="G2692" s="4"/>
+    </row>
+    <row r="2693" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2693" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2693" s="8">
+        <v>47</v>
+      </c>
+      <c r="C2693" s="3" t="s">
+        <v>8567</v>
+      </c>
+      <c r="D2693" s="3" t="s">
+        <v>8567</v>
+      </c>
+      <c r="E2693" s="3" t="s">
+        <v>8568</v>
+      </c>
+      <c r="F2693" s="3" t="s">
+        <v>8569</v>
+      </c>
+      <c r="G2693" s="4"/>
+    </row>
+    <row r="2694" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2694" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2694" s="8">
+        <v>48</v>
+      </c>
+      <c r="C2694" s="3" t="s">
+        <v>8570</v>
+      </c>
+      <c r="D2694" s="3" t="s">
+        <v>8570</v>
+      </c>
+      <c r="E2694" s="3" t="s">
+        <v>8571</v>
+      </c>
+      <c r="F2694" s="3" t="s">
+        <v>8572</v>
+      </c>
+      <c r="G2694" s="4"/>
+    </row>
+    <row r="2695" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2695" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2695" s="8">
+        <v>49</v>
+      </c>
+      <c r="C2695" s="3" t="s">
+        <v>8573</v>
+      </c>
+      <c r="D2695" s="3" t="s">
+        <v>8573</v>
+      </c>
+      <c r="E2695" s="3" t="s">
+        <v>8574</v>
+      </c>
+      <c r="F2695" s="3" t="s">
+        <v>8575</v>
+      </c>
+      <c r="G2695" s="4"/>
+    </row>
+    <row r="2696" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2696" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2696" s="8">
+        <v>50</v>
+      </c>
+      <c r="C2696" s="3" t="s">
+        <v>8576</v>
+      </c>
+      <c r="D2696" s="3" t="s">
+        <v>8576</v>
+      </c>
+      <c r="E2696" s="3" t="s">
+        <v>8577</v>
+      </c>
+      <c r="F2696" s="3" t="s">
+        <v>8578</v>
+      </c>
+      <c r="G2696" s="4"/>
+    </row>
+    <row r="2697" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2697" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2697" s="8">
+        <v>51</v>
+      </c>
+      <c r="C2697" s="3" t="s">
+        <v>8539</v>
+      </c>
+      <c r="D2697" s="3" t="s">
+        <v>8540</v>
+      </c>
+      <c r="E2697" s="3" t="s">
+        <v>4382</v>
+      </c>
+      <c r="F2697" s="3" t="s">
+        <v>4383</v>
+      </c>
+      <c r="G2697" s="4"/>
+    </row>
+    <row r="2698" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2698" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2698" s="8">
+        <v>52</v>
+      </c>
+      <c r="C2698" s="3" t="s">
+        <v>6220</v>
+      </c>
+      <c r="D2698" s="3" t="s">
+        <v>6221</v>
+      </c>
+      <c r="E2698" s="3" t="s">
+        <v>6222</v>
+      </c>
+      <c r="F2698" s="3" t="s">
+        <v>8579</v>
+      </c>
+      <c r="G2698" s="4"/>
+    </row>
+    <row r="2699" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2699" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2699" s="8">
+        <v>53</v>
+      </c>
+      <c r="C2699" s="3" t="s">
+        <v>8580</v>
+      </c>
+      <c r="D2699" s="3" t="s">
+        <v>8580</v>
+      </c>
+      <c r="E2699" s="3" t="s">
+        <v>8581</v>
+      </c>
+      <c r="F2699" s="3" t="s">
+        <v>8582</v>
+      </c>
+      <c r="G2699" s="4"/>
+    </row>
+    <row r="2700" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2700" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2700" s="8">
+        <v>54</v>
+      </c>
+      <c r="C2700" s="3" t="s">
+        <v>8583</v>
+      </c>
+      <c r="D2700" s="3" t="s">
+        <v>8583</v>
+      </c>
+      <c r="E2700" s="3" t="s">
+        <v>8584</v>
+      </c>
+      <c r="F2700" s="3" t="s">
+        <v>8585</v>
+      </c>
+      <c r="G2700" s="4"/>
+    </row>
+    <row r="2701" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2701" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2701" s="8">
+        <v>55</v>
+      </c>
+      <c r="C2701" s="3" t="s">
+        <v>8586</v>
+      </c>
+      <c r="D2701" s="3" t="s">
+        <v>8587</v>
+      </c>
+      <c r="E2701" s="3" t="s">
+        <v>8588</v>
+      </c>
+      <c r="F2701" s="3" t="s">
+        <v>8589</v>
+      </c>
+      <c r="G2701" s="4"/>
+    </row>
+    <row r="2702" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2702" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2702" s="8">
+        <v>56</v>
+      </c>
+      <c r="C2702" s="3" t="s">
+        <v>8590</v>
+      </c>
+      <c r="D2702" s="3" t="s">
+        <v>8590</v>
+      </c>
+      <c r="E2702" s="3" t="s">
+        <v>8591</v>
+      </c>
+      <c r="F2702" s="3" t="s">
+        <v>8592</v>
+      </c>
+      <c r="G2702" s="4"/>
+    </row>
+    <row r="2703" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2703" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2703" s="8">
+        <v>57</v>
+      </c>
+      <c r="C2703" s="3" t="s">
+        <v>8593</v>
+      </c>
+      <c r="D2703" s="3" t="s">
+        <v>8593</v>
+      </c>
+      <c r="E2703" s="3" t="s">
+        <v>8594</v>
+      </c>
+      <c r="F2703" s="3" t="s">
+        <v>8595</v>
+      </c>
+      <c r="G2703" s="4"/>
+    </row>
+    <row r="2704" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2704" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2704" s="8">
+        <v>58</v>
+      </c>
+      <c r="C2704" s="3" t="s">
+        <v>8596</v>
+      </c>
+      <c r="D2704" s="3" t="s">
+        <v>8596</v>
+      </c>
+      <c r="E2704" s="3" t="s">
+        <v>8597</v>
+      </c>
+      <c r="F2704" s="3" t="s">
+        <v>8598</v>
+      </c>
+      <c r="G2704" s="4" t="s">
+        <v>8599</v>
+      </c>
+    </row>
+    <row r="2705" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2705" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2705" s="8">
+        <v>59</v>
+      </c>
+      <c r="C2705" s="3" t="s">
+        <v>8600</v>
+      </c>
+      <c r="D2705" s="3" t="s">
+        <v>8600</v>
+      </c>
+      <c r="E2705" s="3" t="s">
+        <v>8601</v>
+      </c>
+      <c r="F2705" s="3" t="s">
+        <v>8602</v>
+      </c>
+      <c r="G2705" s="4"/>
+    </row>
+    <row r="2706" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2706" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2706" s="8">
+        <v>60</v>
+      </c>
+      <c r="C2706" s="3" t="s">
+        <v>8603</v>
+      </c>
+      <c r="D2706" s="3" t="s">
+        <v>8603</v>
+      </c>
+      <c r="E2706" s="3" t="s">
+        <v>8604</v>
+      </c>
+      <c r="F2706" s="3" t="s">
+        <v>8605</v>
+      </c>
+      <c r="G2706" s="4"/>
+    </row>
+    <row r="2707" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2707" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2707" s="8">
+        <v>61</v>
+      </c>
+      <c r="C2707" s="3" t="s">
+        <v>8606</v>
+      </c>
+      <c r="D2707" s="3" t="s">
+        <v>8607</v>
+      </c>
+      <c r="E2707" s="3" t="s">
+        <v>8608</v>
+      </c>
+      <c r="F2707" s="3" t="s">
+        <v>8609</v>
+      </c>
+      <c r="G2707" s="4"/>
+    </row>
+    <row r="2708" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2708" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2708" s="8">
+        <v>62</v>
+      </c>
+      <c r="C2708" s="3" t="s">
+        <v>8610</v>
+      </c>
+      <c r="D2708" s="3" t="s">
+        <v>8611</v>
+      </c>
+      <c r="E2708" s="3" t="s">
+        <v>8612</v>
+      </c>
+      <c r="F2708" s="3" t="s">
+        <v>8613</v>
+      </c>
+      <c r="G2708" s="4"/>
+    </row>
+    <row r="2709" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2709" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2709" s="8">
+        <v>63</v>
+      </c>
+      <c r="C2709" s="3" t="s">
+        <v>8614</v>
+      </c>
+      <c r="D2709" s="3" t="s">
+        <v>8615</v>
+      </c>
+      <c r="E2709" s="3" t="s">
+        <v>8616</v>
+      </c>
+      <c r="F2709" s="3" t="s">
+        <v>8617</v>
+      </c>
+      <c r="G2709" s="4"/>
+    </row>
+    <row r="2710" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2710" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2710" s="8">
+        <v>64</v>
+      </c>
+      <c r="C2710" s="3" t="s">
+        <v>8618</v>
+      </c>
+      <c r="D2710" s="3" t="s">
+        <v>8618</v>
+      </c>
+      <c r="E2710" s="3" t="s">
+        <v>8619</v>
+      </c>
+      <c r="F2710" s="3" t="s">
+        <v>8620</v>
+      </c>
+      <c r="G2710" s="4"/>
+    </row>
+    <row r="2711" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2711" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2711" s="8">
+        <v>65</v>
+      </c>
+      <c r="C2711" s="3" t="s">
+        <v>8621</v>
+      </c>
+      <c r="D2711" s="3" t="s">
+        <v>8621</v>
+      </c>
+      <c r="E2711" s="3" t="s">
+        <v>8622</v>
+      </c>
+      <c r="F2711" s="3" t="s">
+        <v>8623</v>
+      </c>
+      <c r="G2711" s="4"/>
+    </row>
+    <row r="2712" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2712" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2712" s="8">
+        <v>66</v>
+      </c>
+      <c r="C2712" s="3" t="s">
+        <v>8624</v>
+      </c>
+      <c r="D2712" s="3" t="s">
+        <v>8624</v>
+      </c>
+      <c r="E2712" s="3" t="s">
+        <v>8625</v>
+      </c>
+      <c r="F2712" s="3" t="s">
+        <v>8626</v>
+      </c>
+      <c r="G2712" s="4"/>
+    </row>
+    <row r="2713" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2713" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2713" s="8">
+        <v>67</v>
+      </c>
+      <c r="C2713" s="3" t="s">
+        <v>8627</v>
+      </c>
+      <c r="D2713" s="3" t="s">
+        <v>8628</v>
+      </c>
+      <c r="E2713" s="3" t="s">
+        <v>8629</v>
+      </c>
+      <c r="F2713" s="3" t="s">
+        <v>8630</v>
+      </c>
+      <c r="G2713" s="4"/>
+    </row>
+    <row r="2714" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2714" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2714" s="8">
+        <v>68</v>
+      </c>
+      <c r="C2714" s="3" t="s">
+        <v>8631</v>
+      </c>
+      <c r="D2714" s="3" t="s">
+        <v>8632</v>
+      </c>
+      <c r="E2714" s="3" t="s">
+        <v>8633</v>
+      </c>
+      <c r="F2714" s="3" t="s">
+        <v>8634</v>
+      </c>
+      <c r="G2714" s="4"/>
+    </row>
+    <row r="2715" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2715" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2715" s="8">
+        <v>69</v>
+      </c>
+      <c r="C2715" s="3" t="s">
+        <v>8635</v>
+      </c>
+      <c r="D2715" s="3" t="s">
+        <v>8636</v>
+      </c>
+      <c r="E2715" s="3" t="s">
+        <v>8637</v>
+      </c>
+      <c r="F2715" s="3" t="s">
+        <v>8638</v>
+      </c>
+      <c r="G2715" s="4"/>
+    </row>
+    <row r="2716" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2716" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2716" s="8">
+        <v>70</v>
+      </c>
+      <c r="C2716" s="3" t="s">
+        <v>8639</v>
+      </c>
+      <c r="D2716" s="3" t="s">
+        <v>8640</v>
+      </c>
+      <c r="E2716" s="3" t="s">
+        <v>8641</v>
+      </c>
+      <c r="F2716" s="3" t="s">
+        <v>8642</v>
+      </c>
+      <c r="G2716" s="4"/>
+    </row>
+    <row r="2717" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2717" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2717" s="8">
+        <v>71</v>
+      </c>
+      <c r="C2717" s="3" t="s">
+        <v>8643</v>
+      </c>
+      <c r="D2717" s="3" t="s">
+        <v>8643</v>
+      </c>
+      <c r="E2717" s="3" t="s">
+        <v>8644</v>
+      </c>
+      <c r="F2717" s="3" t="s">
+        <v>8645</v>
+      </c>
+      <c r="G2717" s="4"/>
+    </row>
+    <row r="2718" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2718" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2718" s="8">
+        <v>72</v>
+      </c>
+      <c r="C2718" s="3" t="s">
+        <v>8646</v>
+      </c>
+      <c r="D2718" s="3" t="s">
+        <v>8646</v>
+      </c>
+      <c r="E2718" s="3" t="s">
+        <v>8647</v>
+      </c>
+      <c r="F2718" s="3" t="s">
+        <v>8648</v>
+      </c>
+      <c r="G2718" s="4"/>
+    </row>
+    <row r="2719" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2719" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2719" s="8">
+        <v>73</v>
+      </c>
+      <c r="C2719" s="3" t="s">
+        <v>8649</v>
+      </c>
+      <c r="D2719" s="3" t="s">
+        <v>8650</v>
+      </c>
+      <c r="E2719" s="3" t="s">
+        <v>8651</v>
+      </c>
+      <c r="F2719" s="3" t="s">
+        <v>8652</v>
+      </c>
+      <c r="G2719" s="4"/>
+    </row>
+    <row r="2720" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2720" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2720" s="8">
+        <v>74</v>
+      </c>
+      <c r="C2720" s="3" t="s">
+        <v>8653</v>
+      </c>
+      <c r="D2720" s="3" t="s">
+        <v>8654</v>
+      </c>
+      <c r="E2720" s="3" t="s">
+        <v>8655</v>
+      </c>
+      <c r="F2720" s="3" t="s">
+        <v>8656</v>
+      </c>
+      <c r="G2720" s="4" t="s">
+        <v>8657</v>
+      </c>
+    </row>
+    <row r="2721" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2721" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2721" s="8">
+        <v>75</v>
+      </c>
+      <c r="C2721" s="3" t="s">
+        <v>8658</v>
+      </c>
+      <c r="D2721" s="3" t="s">
+        <v>8659</v>
+      </c>
+      <c r="E2721" s="3" t="s">
+        <v>8660</v>
+      </c>
+      <c r="F2721" s="3" t="s">
+        <v>8661</v>
+      </c>
+      <c r="G2721" s="4"/>
+    </row>
+    <row r="2722" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2722" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2722" s="8">
+        <v>76</v>
+      </c>
+      <c r="C2722" s="3" t="s">
+        <v>8662</v>
+      </c>
+      <c r="D2722" s="3" t="s">
+        <v>8662</v>
+      </c>
+      <c r="E2722" s="3" t="s">
+        <v>8663</v>
+      </c>
+      <c r="F2722" s="3" t="s">
+        <v>8664</v>
+      </c>
+      <c r="G2722" s="4"/>
+    </row>
+    <row r="2723" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2723" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2723" s="8">
+        <v>77</v>
+      </c>
+      <c r="C2723" s="3" t="s">
+        <v>8665</v>
+      </c>
+      <c r="D2723" s="3" t="s">
+        <v>8665</v>
+      </c>
+      <c r="E2723" s="3" t="s">
+        <v>8666</v>
+      </c>
+      <c r="F2723" s="3" t="s">
+        <v>8667</v>
+      </c>
+      <c r="G2723" s="4"/>
+    </row>
+    <row r="2724" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2724" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2724" s="8">
+        <v>78</v>
+      </c>
+      <c r="C2724" s="3" t="s">
+        <v>8668</v>
+      </c>
+      <c r="D2724" s="3" t="s">
+        <v>8669</v>
+      </c>
+      <c r="E2724" s="3" t="s">
+        <v>8670</v>
+      </c>
+      <c r="F2724" s="3" t="s">
+        <v>8671</v>
+      </c>
+      <c r="G2724" s="4"/>
+    </row>
+    <row r="2725" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2725" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2725" s="8">
+        <v>79</v>
+      </c>
+      <c r="C2725" s="3" t="s">
+        <v>8672</v>
+      </c>
+      <c r="D2725" s="3" t="s">
+        <v>8672</v>
+      </c>
+      <c r="E2725" s="3" t="s">
+        <v>8673</v>
+      </c>
+      <c r="F2725" s="3" t="s">
+        <v>8674</v>
+      </c>
+      <c r="G2725" s="4"/>
+    </row>
+    <row r="2726" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2726" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2726" s="8">
+        <v>80</v>
+      </c>
+      <c r="C2726" s="3" t="s">
+        <v>8675</v>
+      </c>
+      <c r="D2726" s="3" t="s">
+        <v>8676</v>
+      </c>
+      <c r="E2726" s="3" t="s">
+        <v>8677</v>
+      </c>
+      <c r="F2726" s="3" t="s">
+        <v>8678</v>
+      </c>
+      <c r="G2726" s="4"/>
+    </row>
+    <row r="2727" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2727" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2727" s="8">
+        <v>81</v>
+      </c>
+      <c r="C2727" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D2727" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E2727" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F2727" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G2727" s="4"/>
+    </row>
+    <row r="2728" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2728" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2728" s="8">
+        <v>82</v>
+      </c>
+      <c r="C2728" s="3" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D2728" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E2728" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F2728" s="3" t="s">
+        <v>1748</v>
+      </c>
+      <c r="G2728" s="4"/>
+    </row>
+    <row r="2729" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2729" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2729" s="8">
+        <v>83</v>
+      </c>
+      <c r="C2729" s="3" t="s">
+        <v>8679</v>
+      </c>
+      <c r="D2729" s="3" t="s">
+        <v>8679</v>
+      </c>
+      <c r="E2729" s="3" t="s">
+        <v>8680</v>
+      </c>
+      <c r="F2729" s="3" t="s">
+        <v>8681</v>
+      </c>
+      <c r="G2729" s="4" t="s">
+        <v>8682</v>
+      </c>
+    </row>
+    <row r="2730" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2730" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2730" s="8">
+        <v>84</v>
+      </c>
+      <c r="C2730" s="3" t="s">
+        <v>8683</v>
+      </c>
+      <c r="D2730" s="3" t="s">
+        <v>8683</v>
+      </c>
+      <c r="E2730" s="3" t="s">
+        <v>8684</v>
+      </c>
+      <c r="F2730" s="3" t="s">
+        <v>8685</v>
+      </c>
+      <c r="G2730" s="4"/>
+    </row>
+    <row r="2731" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2731" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2731" s="8">
+        <v>85</v>
+      </c>
+      <c r="C2731" s="3" t="s">
+        <v>8686</v>
+      </c>
+      <c r="D2731" s="3" t="s">
+        <v>8686</v>
+      </c>
+      <c r="E2731" s="3" t="s">
+        <v>8687</v>
+      </c>
+      <c r="F2731" s="3" t="s">
+        <v>8688</v>
+      </c>
+      <c r="G2731" s="4"/>
+    </row>
+    <row r="2732" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2732" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2732" s="8">
+        <v>86</v>
+      </c>
+      <c r="C2732" s="3" t="s">
+        <v>8689</v>
+      </c>
+      <c r="D2732" s="3" t="s">
+        <v>8690</v>
+      </c>
+      <c r="E2732" s="3" t="s">
+        <v>8691</v>
+      </c>
+      <c r="F2732" s="3" t="s">
+        <v>8692</v>
+      </c>
+      <c r="G2732" s="4"/>
+    </row>
+    <row r="2733" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2733" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2733" s="8">
+        <v>87</v>
+      </c>
+      <c r="C2733" s="3" t="s">
+        <v>8693</v>
+      </c>
+      <c r="D2733" s="3" t="s">
+        <v>8694</v>
+      </c>
+      <c r="E2733" s="3" t="s">
+        <v>8532</v>
+      </c>
+      <c r="F2733" s="3" t="s">
+        <v>8695</v>
+      </c>
+      <c r="G2733" s="4"/>
+    </row>
+    <row r="2734" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2734" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2734" s="8">
+        <v>88</v>
+      </c>
+      <c r="C2734" s="3" t="s">
+        <v>8696</v>
+      </c>
+      <c r="D2734" s="3" t="s">
+        <v>8697</v>
+      </c>
+      <c r="E2734" s="3" t="s">
+        <v>8537</v>
+      </c>
+      <c r="F2734" s="3" t="s">
+        <v>8538</v>
+      </c>
+      <c r="G2734" s="4"/>
+    </row>
+    <row r="2735" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2735" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2735" s="8">
+        <v>89</v>
+      </c>
+      <c r="C2735" s="3" t="s">
+        <v>8698</v>
+      </c>
+      <c r="D2735" s="3" t="s">
+        <v>8699</v>
+      </c>
+      <c r="E2735" s="3" t="s">
+        <v>8700</v>
+      </c>
+      <c r="F2735" s="3" t="s">
+        <v>8701</v>
+      </c>
+      <c r="G2735" s="4"/>
+    </row>
+    <row r="2736" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2736" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2736" s="8">
+        <v>90</v>
+      </c>
+      <c r="C2736" s="3" t="s">
+        <v>8702</v>
+      </c>
+      <c r="D2736" s="3" t="s">
+        <v>8702</v>
+      </c>
+      <c r="E2736" s="3" t="s">
+        <v>8703</v>
+      </c>
+      <c r="F2736" s="3" t="s">
+        <v>8704</v>
+      </c>
+      <c r="G2736" s="4"/>
+    </row>
+    <row r="2737" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2737" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2737" s="8">
+        <v>91</v>
+      </c>
+      <c r="C2737" s="3" t="s">
+        <v>8705</v>
+      </c>
+      <c r="D2737" s="3" t="s">
+        <v>8706</v>
+      </c>
+      <c r="E2737" s="3" t="s">
+        <v>8707</v>
+      </c>
+      <c r="F2737" s="3" t="s">
+        <v>8708</v>
+      </c>
+      <c r="G2737" s="4" t="s">
+        <v>8709</v>
+      </c>
+    </row>
+    <row r="2738" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2738" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2738" s="8">
+        <v>92</v>
+      </c>
+      <c r="C2738" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="D2738" s="3" t="s">
+        <v>2890</v>
+      </c>
+      <c r="E2738" s="3" t="s">
+        <v>2973</v>
+      </c>
+      <c r="F2738" s="3" t="s">
+        <v>4356</v>
+      </c>
+      <c r="G2738" s="4"/>
+    </row>
+    <row r="2739" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2739" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2739" s="8">
+        <v>93</v>
+      </c>
+      <c r="C2739" s="3" t="s">
+        <v>8710</v>
+      </c>
+      <c r="D2739" s="3" t="s">
+        <v>8711</v>
+      </c>
+      <c r="E2739" s="3" t="s">
+        <v>8712</v>
+      </c>
+      <c r="F2739" s="3" t="s">
+        <v>8713</v>
+      </c>
+      <c r="G2739" s="4"/>
+    </row>
+    <row r="2740" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2740" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2740" s="8">
+        <v>94</v>
+      </c>
+      <c r="C2740" s="3" t="s">
+        <v>8714</v>
+      </c>
+      <c r="D2740" s="3" t="s">
+        <v>8714</v>
+      </c>
+      <c r="E2740" s="3" t="s">
+        <v>8715</v>
+      </c>
+      <c r="F2740" s="3" t="s">
+        <v>8716</v>
+      </c>
+      <c r="G2740" s="4"/>
+    </row>
+    <row r="2741" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2741" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2741" s="8">
+        <v>95</v>
+      </c>
+      <c r="C2741" s="3" t="s">
+        <v>8717</v>
+      </c>
+      <c r="D2741" s="3" t="s">
+        <v>8718</v>
+      </c>
+      <c r="E2741" s="3" t="s">
+        <v>8719</v>
+      </c>
+      <c r="F2741" s="3" t="s">
+        <v>8720</v>
+      </c>
+      <c r="G2741" s="4"/>
+    </row>
+    <row r="2742" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2742" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2742" s="8">
+        <v>96</v>
+      </c>
+      <c r="C2742" s="3" t="s">
+        <v>8721</v>
+      </c>
+      <c r="D2742" s="3" t="s">
+        <v>8721</v>
+      </c>
+      <c r="E2742" s="3" t="s">
+        <v>8722</v>
+      </c>
+      <c r="F2742" s="3" t="s">
+        <v>8723</v>
+      </c>
+      <c r="G2742" s="4"/>
+    </row>
+    <row r="2743" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2743" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2743" s="8">
+        <v>97</v>
+      </c>
+      <c r="C2743" s="3" t="s">
+        <v>8724</v>
+      </c>
+      <c r="D2743" s="3" t="s">
+        <v>8725</v>
+      </c>
+      <c r="E2743" s="3" t="s">
+        <v>8726</v>
+      </c>
+      <c r="F2743" s="3" t="s">
+        <v>8727</v>
+      </c>
+      <c r="G2743" s="4"/>
+    </row>
+    <row r="2744" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2744" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2744" s="8">
+        <v>98</v>
+      </c>
+      <c r="C2744" s="3" t="s">
+        <v>8728</v>
+      </c>
+      <c r="D2744" s="3" t="s">
+        <v>8728</v>
+      </c>
+      <c r="E2744" s="3" t="s">
+        <v>8729</v>
+      </c>
+      <c r="F2744" s="3" t="s">
+        <v>8730</v>
+      </c>
+      <c r="G2744" s="4"/>
+    </row>
+    <row r="2745" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2745" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2745" s="8">
+        <v>99</v>
+      </c>
+      <c r="C2745" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D2745" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E2745" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F2745" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G2745" s="4"/>
+    </row>
+    <row r="2746" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2746" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2746" s="8">
+        <v>100</v>
+      </c>
+      <c r="C2746" s="3" t="s">
+        <v>8731</v>
+      </c>
+      <c r="D2746" s="3" t="s">
+        <v>8732</v>
+      </c>
+      <c r="E2746" s="3" t="s">
+        <v>8733</v>
+      </c>
+      <c r="F2746" s="3" t="s">
+        <v>8734</v>
+      </c>
+      <c r="G2746" s="4" t="s">
+        <v>8735</v>
+      </c>
+    </row>
+    <row r="2747" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2747" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2747" s="8">
+        <v>101</v>
+      </c>
+      <c r="C2747" s="3" t="s">
+        <v>8721</v>
+      </c>
+      <c r="D2747" s="3" t="s">
+        <v>8721</v>
+      </c>
+      <c r="E2747" s="3" t="s">
+        <v>8722</v>
+      </c>
+      <c r="F2747" s="3" t="s">
+        <v>8723</v>
+      </c>
+      <c r="G2747" s="4"/>
+    </row>
+    <row r="2748" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2748" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2748" s="8">
+        <v>102</v>
+      </c>
+      <c r="C2748" s="3" t="s">
+        <v>8736</v>
+      </c>
+      <c r="D2748" s="3" t="s">
+        <v>8736</v>
+      </c>
+      <c r="E2748" s="3" t="s">
+        <v>8737</v>
+      </c>
+      <c r="F2748" s="3" t="s">
+        <v>8738</v>
+      </c>
+      <c r="G2748" s="4"/>
+    </row>
+    <row r="2749" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2749" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2749" s="8">
+        <v>103</v>
+      </c>
+      <c r="C2749" s="3" t="s">
+        <v>8739</v>
+      </c>
+      <c r="D2749" s="3" t="s">
+        <v>8740</v>
+      </c>
+      <c r="E2749" s="3" t="s">
+        <v>8726</v>
+      </c>
+      <c r="F2749" s="3" t="s">
+        <v>8727</v>
+      </c>
+      <c r="G2749" s="4"/>
+    </row>
+    <row r="2750" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2750" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2750" s="8">
+        <v>104</v>
+      </c>
+      <c r="C2750" s="3" t="s">
+        <v>8741</v>
+      </c>
+      <c r="D2750" s="3" t="s">
+        <v>8741</v>
+      </c>
+      <c r="E2750" s="3" t="s">
+        <v>8729</v>
+      </c>
+      <c r="F2750" s="3" t="s">
+        <v>8730</v>
+      </c>
+      <c r="G2750" s="4"/>
+    </row>
+    <row r="2751" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2751" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2751" s="8">
+        <v>105</v>
+      </c>
+      <c r="C2751" s="3" t="s">
+        <v>8742</v>
+      </c>
+      <c r="D2751" s="3" t="s">
+        <v>8743</v>
+      </c>
+      <c r="E2751" s="3" t="s">
+        <v>8744</v>
+      </c>
+      <c r="F2751" s="3" t="s">
+        <v>8745</v>
+      </c>
+      <c r="G2751" s="4"/>
+    </row>
+    <row r="2752" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2752" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2752" s="8">
+        <v>106</v>
+      </c>
+      <c r="C2752" s="3" t="s">
+        <v>8746</v>
+      </c>
+      <c r="D2752" s="3" t="s">
+        <v>8747</v>
+      </c>
+      <c r="E2752" s="3" t="s">
+        <v>8551</v>
+      </c>
+      <c r="F2752" s="3" t="s">
+        <v>8748</v>
+      </c>
+      <c r="G2752" s="4"/>
+    </row>
+    <row r="2753" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2753" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2753" s="8">
+        <v>107</v>
+      </c>
+      <c r="C2753" s="3" t="s">
+        <v>8749</v>
+      </c>
+      <c r="D2753" s="3" t="s">
+        <v>8750</v>
+      </c>
+      <c r="E2753" s="3" t="s">
+        <v>8707</v>
+      </c>
+      <c r="F2753" s="3" t="s">
+        <v>8708</v>
+      </c>
+      <c r="G2753" s="4"/>
+    </row>
+    <row r="2754" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2754" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2754" s="8">
+        <v>108</v>
+      </c>
+      <c r="C2754" s="3" t="s">
+        <v>8751</v>
+      </c>
+      <c r="D2754" s="3" t="s">
+        <v>8751</v>
+      </c>
+      <c r="E2754" s="3" t="s">
+        <v>8752</v>
+      </c>
+      <c r="F2754" s="3" t="s">
+        <v>8753</v>
+      </c>
+      <c r="G2754" s="4"/>
+    </row>
+    <row r="2755" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2755" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2755" s="8">
+        <v>109</v>
+      </c>
+      <c r="C2755" s="3" t="s">
+        <v>8754</v>
+      </c>
+      <c r="D2755" s="3" t="s">
+        <v>8754</v>
+      </c>
+      <c r="E2755" s="3" t="s">
+        <v>8755</v>
+      </c>
+      <c r="F2755" s="3" t="s">
+        <v>8756</v>
+      </c>
+      <c r="G2755" s="4"/>
+    </row>
+    <row r="2756" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2756" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2756" s="8">
+        <v>110</v>
+      </c>
+      <c r="C2756" s="3" t="s">
+        <v>8757</v>
+      </c>
+      <c r="D2756" s="3" t="s">
+        <v>8758</v>
+      </c>
+      <c r="E2756" s="3" t="s">
+        <v>8759</v>
+      </c>
+      <c r="F2756" s="3" t="s">
+        <v>8760</v>
+      </c>
+      <c r="G2756" s="4"/>
+    </row>
+    <row r="2757" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2757" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2757" s="8">
+        <v>111</v>
+      </c>
+      <c r="C2757" s="3" t="s">
+        <v>8761</v>
+      </c>
+      <c r="D2757" s="3" t="s">
+        <v>8761</v>
+      </c>
+      <c r="E2757" s="3" t="s">
+        <v>8762</v>
+      </c>
+      <c r="F2757" s="3" t="s">
+        <v>8763</v>
+      </c>
+      <c r="G2757" s="4"/>
+    </row>
+    <row r="2758" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2758" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2758" s="8">
+        <v>112</v>
+      </c>
+      <c r="C2758" s="3" t="s">
+        <v>8764</v>
+      </c>
+      <c r="D2758" s="3" t="s">
+        <v>8765</v>
+      </c>
+      <c r="E2758" s="3" t="s">
+        <v>8766</v>
+      </c>
+      <c r="F2758" s="3" t="s">
+        <v>8767</v>
+      </c>
+      <c r="G2758" s="4"/>
+    </row>
+    <row r="2759" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2759" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2759" s="8">
+        <v>113</v>
+      </c>
+      <c r="C2759" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D2759" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E2759" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F2759" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G2759" s="4"/>
+    </row>
+    <row r="2760" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2760" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2760" s="8">
+        <v>114</v>
+      </c>
+      <c r="C2760" s="3" t="s">
+        <v>8768</v>
+      </c>
+      <c r="D2760" s="3" t="s">
+        <v>8768</v>
+      </c>
+      <c r="E2760" s="3" t="s">
+        <v>8769</v>
+      </c>
+      <c r="F2760" s="3" t="s">
+        <v>8770</v>
+      </c>
+      <c r="G2760" s="4"/>
+    </row>
+    <row r="2761" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2761" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2761" s="8">
+        <v>115</v>
+      </c>
+      <c r="C2761" s="3" t="s">
+        <v>8771</v>
+      </c>
+      <c r="D2761" s="3" t="s">
+        <v>8771</v>
+      </c>
+      <c r="E2761" s="3" t="s">
+        <v>8772</v>
+      </c>
+      <c r="F2761" s="3" t="s">
+        <v>8773</v>
+      </c>
+      <c r="G2761" s="4"/>
+    </row>
+    <row r="2762" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2762" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2762" s="8">
+        <v>116</v>
+      </c>
+      <c r="C2762" s="3" t="s">
+        <v>8774</v>
+      </c>
+      <c r="D2762" s="3" t="s">
+        <v>8775</v>
+      </c>
+      <c r="E2762" s="3" t="s">
+        <v>8759</v>
+      </c>
+      <c r="F2762" s="3" t="s">
+        <v>8760</v>
+      </c>
+      <c r="G2762" s="4"/>
+    </row>
+    <row r="2763" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2763" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2763" s="8">
+        <v>117</v>
+      </c>
+      <c r="C2763" s="3" t="s">
+        <v>8761</v>
+      </c>
+      <c r="D2763" s="3" t="s">
+        <v>8761</v>
+      </c>
+      <c r="E2763" s="3" t="s">
+        <v>8762</v>
+      </c>
+      <c r="F2763" s="3" t="s">
+        <v>8763</v>
+      </c>
+      <c r="G2763" s="4"/>
+    </row>
+    <row r="2764" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2764" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2764" s="8">
+        <v>118</v>
+      </c>
+      <c r="C2764" s="3" t="s">
+        <v>8776</v>
+      </c>
+      <c r="D2764" s="3" t="s">
+        <v>8777</v>
+      </c>
+      <c r="E2764" s="3" t="s">
+        <v>8766</v>
+      </c>
+      <c r="F2764" s="3" t="s">
+        <v>8767</v>
+      </c>
+      <c r="G2764" s="4"/>
+    </row>
+    <row r="2765" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2765" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2765" s="8">
+        <v>119</v>
+      </c>
+      <c r="C2765" s="3" t="s">
+        <v>8778</v>
+      </c>
+      <c r="D2765" s="3" t="s">
+        <v>8779</v>
+      </c>
+      <c r="E2765" s="3" t="s">
+        <v>8780</v>
+      </c>
+      <c r="F2765" s="3" t="s">
+        <v>8781</v>
+      </c>
+      <c r="G2765" s="4"/>
+    </row>
+    <row r="2766" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2766" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2766" s="8">
+        <v>120</v>
+      </c>
+      <c r="C2766" s="3" t="s">
+        <v>8746</v>
+      </c>
+      <c r="D2766" s="3" t="s">
+        <v>8747</v>
+      </c>
+      <c r="E2766" s="3" t="s">
+        <v>8551</v>
+      </c>
+      <c r="F2766" s="3" t="s">
+        <v>8748</v>
+      </c>
+      <c r="G2766" s="4"/>
+    </row>
+    <row r="2767" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2767" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2767" s="8">
+        <v>121</v>
+      </c>
+      <c r="C2767" s="3" t="s">
+        <v>8782</v>
+      </c>
+      <c r="D2767" s="3" t="s">
+        <v>8783</v>
+      </c>
+      <c r="E2767" s="3" t="s">
+        <v>8707</v>
+      </c>
+      <c r="F2767" s="3" t="s">
+        <v>8708</v>
+      </c>
+      <c r="G2767" s="4"/>
+    </row>
+    <row r="2768" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2768" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2768" s="8">
+        <v>122</v>
+      </c>
+      <c r="C2768" s="3" t="s">
+        <v>8784</v>
+      </c>
+      <c r="D2768" s="3" t="s">
+        <v>8785</v>
+      </c>
+      <c r="E2768" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F2768" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G2768" s="4"/>
+    </row>
+    <row r="2769" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2769" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2769" s="8">
+        <v>123</v>
+      </c>
+      <c r="C2769" s="3" t="s">
+        <v>8786</v>
+      </c>
+      <c r="D2769" s="3" t="s">
+        <v>8787</v>
+      </c>
+      <c r="E2769" s="3" t="s">
+        <v>8788</v>
+      </c>
+      <c r="F2769" s="3" t="s">
+        <v>8789</v>
+      </c>
+      <c r="G2769" s="4"/>
+    </row>
+    <row r="2770" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2770" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2770" s="8">
+        <v>124</v>
+      </c>
+      <c r="C2770" s="3" t="s">
+        <v>8790</v>
+      </c>
+      <c r="D2770" s="3" t="s">
+        <v>8791</v>
+      </c>
+      <c r="E2770" s="3" t="s">
+        <v>8792</v>
+      </c>
+      <c r="F2770" s="3" t="s">
+        <v>8793</v>
+      </c>
+      <c r="G2770" s="4"/>
+    </row>
+    <row r="2771" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2771" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2771" s="8">
+        <v>125</v>
+      </c>
+      <c r="C2771" s="3" t="s">
+        <v>8794</v>
+      </c>
+      <c r="D2771" s="3" t="s">
+        <v>8794</v>
+      </c>
+      <c r="E2771" s="3" t="s">
+        <v>8795</v>
+      </c>
+      <c r="F2771" s="3" t="s">
+        <v>8796</v>
+      </c>
+      <c r="G2771" s="4"/>
+    </row>
+    <row r="2772" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2772" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2772" s="8">
+        <v>126</v>
+      </c>
+      <c r="C2772" s="3" t="s">
+        <v>8797</v>
+      </c>
+      <c r="D2772" s="3" t="s">
+        <v>8797</v>
+      </c>
+      <c r="E2772" s="3" t="s">
+        <v>8798</v>
+      </c>
+      <c r="F2772" s="3" t="s">
+        <v>8799</v>
+      </c>
+      <c r="G2772" s="4"/>
+    </row>
+    <row r="2773" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2773" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2773" s="8">
+        <v>127</v>
+      </c>
+      <c r="C2773" s="3" t="s">
+        <v>8800</v>
+      </c>
+      <c r="D2773" s="3" t="s">
+        <v>8800</v>
+      </c>
+      <c r="E2773" s="3" t="s">
+        <v>7907</v>
+      </c>
+      <c r="F2773" s="3" t="s">
+        <v>7908</v>
+      </c>
+      <c r="G2773" s="4"/>
+    </row>
+    <row r="2774" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2774" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2774" s="8">
+        <v>128</v>
+      </c>
+      <c r="C2774" s="3" t="s">
+        <v>8801</v>
+      </c>
+      <c r="D2774" s="3" t="s">
+        <v>8802</v>
+      </c>
+      <c r="E2774" s="3" t="s">
+        <v>8803</v>
+      </c>
+      <c r="F2774" s="3" t="s">
+        <v>8804</v>
+      </c>
+      <c r="G2774" s="4"/>
+    </row>
+    <row r="2775" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2775" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2775" s="8">
+        <v>129</v>
+      </c>
+      <c r="C2775" s="3" t="s">
+        <v>8805</v>
+      </c>
+      <c r="D2775" s="3" t="s">
+        <v>8805</v>
+      </c>
+      <c r="E2775" s="3" t="s">
+        <v>8806</v>
+      </c>
+      <c r="F2775" s="3" t="s">
+        <v>8807</v>
+      </c>
+      <c r="G2775" s="4"/>
+    </row>
+    <row r="2776" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2776" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2776" s="8">
+        <v>130</v>
+      </c>
+      <c r="C2776" s="3" t="s">
+        <v>8808</v>
+      </c>
+      <c r="D2776" s="3" t="s">
+        <v>8808</v>
+      </c>
+      <c r="E2776" s="3" t="s">
+        <v>8809</v>
+      </c>
+      <c r="F2776" s="3" t="s">
+        <v>8810</v>
+      </c>
+      <c r="G2776" s="4"/>
+    </row>
+    <row r="2777" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2777" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2777" s="8">
+        <v>131</v>
+      </c>
+      <c r="C2777" s="3" t="s">
+        <v>8811</v>
+      </c>
+      <c r="D2777" s="3" t="s">
+        <v>8811</v>
+      </c>
+      <c r="E2777" s="3" t="s">
+        <v>8812</v>
+      </c>
+      <c r="F2777" s="3" t="s">
+        <v>8813</v>
+      </c>
+      <c r="G2777" s="4"/>
+    </row>
+    <row r="2778" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2778" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2778" s="8">
+        <v>132</v>
+      </c>
+      <c r="C2778" s="3" t="s">
+        <v>8814</v>
+      </c>
+      <c r="D2778" s="3" t="s">
+        <v>8814</v>
+      </c>
+      <c r="E2778" s="3" t="s">
+        <v>8815</v>
+      </c>
+      <c r="F2778" s="3" t="s">
+        <v>8816</v>
+      </c>
+      <c r="G2778" s="4" t="s">
+        <v>8817</v>
+      </c>
+    </row>
+    <row r="2779" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2779" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2779" s="8">
+        <v>133</v>
+      </c>
+      <c r="C2779" s="3" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D2779" s="3" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E2779" s="3" t="s">
+        <v>1601</v>
+      </c>
+      <c r="F2779" s="3" t="s">
+        <v>1602</v>
+      </c>
+      <c r="G2779" s="4"/>
+    </row>
+    <row r="2780" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2780" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2780" s="8">
+        <v>134</v>
+      </c>
+      <c r="C2780" s="3" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D2780" s="3" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E2780" s="3" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F2780" s="3" t="s">
+        <v>1748</v>
+      </c>
+      <c r="G2780" s="4"/>
+    </row>
+    <row r="2781" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2781" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2781" s="8">
+        <v>135</v>
+      </c>
+      <c r="C2781" s="3" t="s">
+        <v>8818</v>
+      </c>
+      <c r="D2781" s="3" t="s">
+        <v>8819</v>
+      </c>
+      <c r="E2781" s="3" t="s">
+        <v>8820</v>
+      </c>
+      <c r="F2781" s="3" t="s">
+        <v>8821</v>
+      </c>
+      <c r="G2781" s="4"/>
+    </row>
+    <row r="2782" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2782" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2782" s="8">
+        <v>136</v>
+      </c>
+      <c r="C2782" s="3" t="s">
+        <v>8822</v>
+      </c>
+      <c r="D2782" s="3" t="s">
+        <v>8822</v>
+      </c>
+      <c r="E2782" s="3" t="s">
+        <v>8823</v>
+      </c>
+      <c r="F2782" s="3" t="s">
+        <v>8824</v>
+      </c>
+      <c r="G2782" s="4"/>
+    </row>
+    <row r="2783" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2783" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2783" s="8">
+        <v>137</v>
+      </c>
+      <c r="C2783" s="3" t="s">
+        <v>8825</v>
+      </c>
+      <c r="D2783" s="3" t="s">
+        <v>8826</v>
+      </c>
+      <c r="E2783" s="3" t="s">
+        <v>8827</v>
+      </c>
+      <c r="F2783" s="3" t="s">
+        <v>8828</v>
+      </c>
+      <c r="G2783" s="4"/>
+    </row>
+    <row r="2784" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2784" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2784" s="8">
+        <v>138</v>
+      </c>
+      <c r="C2784" s="3" t="s">
+        <v>8829</v>
+      </c>
+      <c r="D2784" s="3" t="s">
+        <v>8830</v>
+      </c>
+      <c r="E2784" s="3" t="s">
+        <v>8831</v>
+      </c>
+      <c r="F2784" s="3" t="s">
+        <v>8832</v>
+      </c>
+      <c r="G2784" s="4" t="s">
+        <v>8833</v>
+      </c>
+    </row>
+    <row r="2785" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2785" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2785" s="8">
+        <v>139</v>
+      </c>
+      <c r="C2785" s="3" t="s">
+        <v>8834</v>
+      </c>
+      <c r="D2785" s="3" t="s">
+        <v>8834</v>
+      </c>
+      <c r="E2785" s="3" t="s">
+        <v>8835</v>
+      </c>
+      <c r="F2785" s="3" t="s">
+        <v>8836</v>
+      </c>
+      <c r="G2785" s="4"/>
+    </row>
+    <row r="2786" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2786" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2786" s="8">
+        <v>140</v>
+      </c>
+      <c r="C2786" s="3" t="s">
+        <v>8837</v>
+      </c>
+      <c r="D2786" s="3" t="s">
+        <v>8837</v>
+      </c>
+      <c r="E2786" s="3" t="s">
+        <v>8838</v>
+      </c>
+      <c r="F2786" s="3" t="s">
+        <v>8839</v>
+      </c>
+      <c r="G2786" s="4"/>
+    </row>
+    <row r="2787" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2787" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2787" s="8">
+        <v>141</v>
+      </c>
+      <c r="C2787" s="3" t="s">
+        <v>8840</v>
+      </c>
+      <c r="D2787" s="3" t="s">
+        <v>8841</v>
+      </c>
+      <c r="E2787" s="3" t="s">
+        <v>8842</v>
+      </c>
+      <c r="F2787" s="3" t="s">
+        <v>8843</v>
+      </c>
+      <c r="G2787" s="4"/>
+    </row>
+    <row r="2788" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2788" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2788" s="8">
+        <v>142</v>
+      </c>
+      <c r="C2788" s="3" t="s">
+        <v>8844</v>
+      </c>
+      <c r="D2788" s="3" t="s">
+        <v>8845</v>
+      </c>
+      <c r="E2788" s="3" t="s">
+        <v>8846</v>
+      </c>
+      <c r="F2788" s="3" t="s">
+        <v>8847</v>
+      </c>
+      <c r="G2788" s="4"/>
+    </row>
+    <row r="2789" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2789" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2789" s="8">
+        <v>143</v>
+      </c>
+      <c r="C2789" s="3" t="s">
+        <v>8848</v>
+      </c>
+      <c r="D2789" s="3" t="s">
+        <v>8848</v>
+      </c>
+      <c r="E2789" s="3" t="s">
+        <v>8849</v>
+      </c>
+      <c r="F2789" s="3" t="s">
+        <v>8850</v>
+      </c>
+      <c r="G2789" s="4"/>
+    </row>
+    <row r="2790" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2790" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2790" s="8">
+        <v>144</v>
+      </c>
+      <c r="C2790" s="3" t="s">
+        <v>8851</v>
+      </c>
+      <c r="D2790" s="3" t="s">
+        <v>8851</v>
+      </c>
+      <c r="E2790" s="3" t="s">
+        <v>8852</v>
+      </c>
+      <c r="F2790" s="3" t="s">
+        <v>8853</v>
+      </c>
+      <c r="G2790" s="4"/>
+    </row>
+    <row r="2791" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2791" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2791" s="8">
+        <v>145</v>
+      </c>
+      <c r="C2791" s="3" t="s">
+        <v>8854</v>
+      </c>
+      <c r="D2791" s="3" t="s">
+        <v>8854</v>
+      </c>
+      <c r="E2791" s="3" t="s">
+        <v>8855</v>
+      </c>
+      <c r="F2791" s="3" t="s">
+        <v>8856</v>
+      </c>
+      <c r="G2791" s="4"/>
+    </row>
+    <row r="2792" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2792" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2792" s="8">
+        <v>146</v>
+      </c>
+      <c r="C2792" s="3" t="s">
+        <v>8857</v>
+      </c>
+      <c r="D2792" s="3" t="s">
+        <v>8857</v>
+      </c>
+      <c r="E2792" s="3" t="s">
+        <v>8858</v>
+      </c>
+      <c r="F2792" s="3" t="s">
+        <v>8859</v>
+      </c>
+      <c r="G2792" s="4" t="s">
+        <v>8860</v>
+      </c>
+    </row>
+    <row r="2793" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2793" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2793" s="8">
+        <v>147</v>
+      </c>
+      <c r="C2793" s="3" t="s">
+        <v>8861</v>
+      </c>
+      <c r="D2793" s="3" t="s">
+        <v>8861</v>
+      </c>
+      <c r="E2793" s="3" t="s">
+        <v>8862</v>
+      </c>
+      <c r="F2793" s="3" t="s">
+        <v>8863</v>
+      </c>
+      <c r="G2793" s="4"/>
+    </row>
+    <row r="2794" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2794" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2794" s="8">
+        <v>148</v>
+      </c>
+      <c r="C2794" s="3" t="s">
+        <v>8864</v>
+      </c>
+      <c r="D2794" s="3" t="s">
+        <v>8865</v>
+      </c>
+      <c r="E2794" s="3" t="s">
+        <v>8866</v>
+      </c>
+      <c r="F2794" s="3" t="s">
+        <v>8867</v>
+      </c>
+      <c r="G2794" s="4"/>
+    </row>
+    <row r="2795" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2795" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2795" s="8">
+        <v>149</v>
+      </c>
+      <c r="C2795" s="3" t="s">
+        <v>8868</v>
+      </c>
+      <c r="D2795" s="3" t="s">
+        <v>8869</v>
+      </c>
+      <c r="E2795" s="3" t="s">
+        <v>8870</v>
+      </c>
+      <c r="F2795" s="3" t="s">
+        <v>8871</v>
+      </c>
+      <c r="G2795" s="4"/>
+    </row>
+    <row r="2796" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2796" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2796" s="8">
+        <v>150</v>
+      </c>
+      <c r="C2796" s="3" t="s">
+        <v>8872</v>
+      </c>
+      <c r="D2796" s="3" t="s">
+        <v>8873</v>
+      </c>
+      <c r="E2796" s="3" t="s">
+        <v>8874</v>
+      </c>
+      <c r="F2796" s="3" t="s">
+        <v>8875</v>
+      </c>
+      <c r="G2796" s="4"/>
+    </row>
+    <row r="2797" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2797" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2797" s="8">
+        <v>151</v>
+      </c>
+      <c r="C2797" s="3" t="s">
+        <v>8876</v>
+      </c>
+      <c r="D2797" s="3" t="s">
+        <v>8876</v>
+      </c>
+      <c r="E2797" s="3" t="s">
+        <v>8877</v>
+      </c>
+      <c r="F2797" s="3" t="s">
+        <v>8878</v>
+      </c>
+      <c r="G2797" s="4"/>
+    </row>
+    <row r="2798" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2798" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2798" s="8">
+        <v>152</v>
+      </c>
+      <c r="C2798" s="3" t="s">
+        <v>8879</v>
+      </c>
+      <c r="D2798" s="3" t="s">
+        <v>8879</v>
+      </c>
+      <c r="E2798" s="3" t="s">
+        <v>8880</v>
+      </c>
+      <c r="F2798" s="3" t="s">
+        <v>8881</v>
+      </c>
+      <c r="G2798" s="4" t="s">
+        <v>8882</v>
+      </c>
+    </row>
+    <row r="2799" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2799" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2799" s="8">
+        <v>153</v>
+      </c>
+      <c r="C2799" s="3" t="s">
+        <v>8883</v>
+      </c>
+      <c r="D2799" s="3" t="s">
+        <v>8884</v>
+      </c>
+      <c r="E2799" s="3" t="s">
+        <v>8885</v>
+      </c>
+      <c r="F2799" s="3" t="s">
+        <v>8886</v>
+      </c>
+      <c r="G2799" s="4"/>
+    </row>
+    <row r="2800" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2800" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2800" s="8">
+        <v>154</v>
+      </c>
+      <c r="C2800" s="3" t="s">
+        <v>8887</v>
+      </c>
+      <c r="D2800" s="3" t="s">
+        <v>8887</v>
+      </c>
+      <c r="E2800" s="3" t="s">
+        <v>8888</v>
+      </c>
+      <c r="F2800" s="3" t="s">
+        <v>8889</v>
+      </c>
+      <c r="G2800" s="4"/>
+    </row>
+    <row r="2801" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2801" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2801" s="8">
+        <v>155</v>
+      </c>
+      <c r="C2801" s="3" t="s">
+        <v>8890</v>
+      </c>
+      <c r="D2801" s="3" t="s">
+        <v>8891</v>
+      </c>
+      <c r="E2801" s="3" t="s">
+        <v>8892</v>
+      </c>
+      <c r="F2801" s="3" t="s">
+        <v>8893</v>
+      </c>
+      <c r="G2801" s="4"/>
+    </row>
+    <row r="2802" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2802" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2802" s="8">
+        <v>156</v>
+      </c>
+      <c r="C2802" s="3" t="s">
+        <v>8894</v>
+      </c>
+      <c r="D2802" s="3" t="s">
+        <v>8895</v>
+      </c>
+      <c r="E2802" s="3" t="s">
+        <v>8896</v>
+      </c>
+      <c r="F2802" s="3" t="s">
+        <v>8897</v>
+      </c>
+      <c r="G2802" s="4"/>
+    </row>
+    <row r="2803" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2803" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2803" s="8">
+        <v>157</v>
+      </c>
+      <c r="C2803" s="3" t="s">
+        <v>8898</v>
+      </c>
+      <c r="D2803" s="3" t="s">
+        <v>8898</v>
+      </c>
+      <c r="E2803" s="3" t="s">
+        <v>8899</v>
+      </c>
+      <c r="F2803" s="3" t="s">
+        <v>8900</v>
+      </c>
+      <c r="G2803" s="4"/>
+    </row>
+    <row r="2804" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2804" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2804" s="8">
+        <v>158</v>
+      </c>
+      <c r="C2804" s="3" t="s">
+        <v>8901</v>
+      </c>
+      <c r="D2804" s="3" t="s">
+        <v>8902</v>
+      </c>
+      <c r="E2804" s="3" t="s">
+        <v>8903</v>
+      </c>
+      <c r="F2804" s="3" t="s">
+        <v>8904</v>
+      </c>
+      <c r="G2804" s="4"/>
+    </row>
+    <row r="2805" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2805" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2805" s="8">
+        <v>159</v>
+      </c>
+      <c r="C2805" s="3" t="s">
+        <v>8905</v>
+      </c>
+      <c r="D2805" s="3" t="s">
+        <v>8906</v>
+      </c>
+      <c r="E2805" s="3" t="s">
+        <v>8907</v>
+      </c>
+      <c r="F2805" s="3" t="s">
+        <v>8908</v>
+      </c>
+      <c r="G2805" s="4"/>
+    </row>
+    <row r="2806" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2806" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2806" s="8">
+        <v>160</v>
+      </c>
+      <c r="C2806" s="3" t="s">
+        <v>8909</v>
+      </c>
+      <c r="D2806" s="3" t="s">
+        <v>8910</v>
+      </c>
+      <c r="E2806" s="3" t="s">
+        <v>8911</v>
+      </c>
+      <c r="F2806" s="3" t="s">
+        <v>8912</v>
+      </c>
+      <c r="G2806" s="4"/>
+    </row>
+    <row r="2807" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2807" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2807" s="8">
+        <v>161</v>
+      </c>
+      <c r="C2807" s="3" t="s">
+        <v>8913</v>
+      </c>
+      <c r="D2807" s="3" t="s">
+        <v>8914</v>
+      </c>
+      <c r="E2807" s="3" t="s">
+        <v>8915</v>
+      </c>
+      <c r="F2807" s="3" t="s">
+        <v>8916</v>
+      </c>
+      <c r="G2807" s="4"/>
+    </row>
+    <row r="2808" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2808" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2808" s="8">
+        <v>162</v>
+      </c>
+      <c r="C2808" s="3" t="s">
+        <v>8917</v>
+      </c>
+      <c r="D2808" s="3" t="s">
+        <v>8917</v>
+      </c>
+      <c r="E2808" s="3" t="s">
+        <v>8918</v>
+      </c>
+      <c r="F2808" s="3" t="s">
+        <v>8919</v>
+      </c>
+      <c r="G2808" s="4" t="s">
+        <v>8920</v>
+      </c>
+    </row>
+    <row r="2809" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2809" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2809" s="8">
+        <v>163</v>
+      </c>
+      <c r="C2809" s="3" t="s">
+        <v>8921</v>
+      </c>
+      <c r="D2809" s="3" t="s">
+        <v>8922</v>
+      </c>
+      <c r="E2809" s="3" t="s">
+        <v>8923</v>
+      </c>
+      <c r="F2809" s="3" t="s">
+        <v>8924</v>
+      </c>
+      <c r="G2809" s="4"/>
+    </row>
+    <row r="2810" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2810" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2810" s="8">
+        <v>164</v>
+      </c>
+      <c r="C2810" s="3" t="s">
+        <v>8925</v>
+      </c>
+      <c r="D2810" s="3" t="s">
+        <v>8926</v>
+      </c>
+      <c r="E2810" s="3" t="s">
+        <v>8927</v>
+      </c>
+      <c r="F2810" s="3" t="s">
+        <v>8928</v>
+      </c>
+      <c r="G2810" s="4"/>
+    </row>
+    <row r="2811" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2811" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2811" s="8">
+        <v>165</v>
+      </c>
+      <c r="C2811" s="3" t="s">
+        <v>2810</v>
+      </c>
+      <c r="D2811" s="3" t="s">
+        <v>2811</v>
+      </c>
+      <c r="E2811" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F2811" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G2811" s="4"/>
+    </row>
+    <row r="2812" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2812" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2812" s="8">
+        <v>166</v>
+      </c>
+      <c r="C2812" s="3" t="s">
+        <v>2812</v>
+      </c>
+      <c r="D2812" s="3" t="s">
+        <v>2812</v>
+      </c>
+      <c r="E2812" s="3" t="s">
+        <v>3654</v>
+      </c>
+      <c r="F2812" s="3" t="s">
+        <v>2814</v>
+      </c>
+      <c r="G2812" s="4"/>
+    </row>
+    <row r="2813" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2813" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2813" s="8">
+        <v>167</v>
+      </c>
+      <c r="C2813" s="3" t="s">
+        <v>8929</v>
+      </c>
+      <c r="D2813" s="3" t="s">
+        <v>8930</v>
+      </c>
+      <c r="E2813" s="3" t="s">
+        <v>8528</v>
+      </c>
+      <c r="F2813" s="3" t="s">
+        <v>8529</v>
+      </c>
+      <c r="G2813" s="4"/>
+    </row>
+    <row r="2814" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2814" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2814" s="8">
+        <v>168</v>
+      </c>
+      <c r="C2814" s="3" t="s">
+        <v>8931</v>
+      </c>
+      <c r="D2814" s="3" t="s">
+        <v>8932</v>
+      </c>
+      <c r="E2814" s="3" t="s">
+        <v>8933</v>
+      </c>
+      <c r="F2814" s="3" t="s">
+        <v>8934</v>
+      </c>
+      <c r="G2814" s="4"/>
+    </row>
+    <row r="2815" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2815" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2815" s="8">
+        <v>169</v>
+      </c>
+      <c r="C2815" s="3" t="s">
+        <v>8935</v>
+      </c>
+      <c r="D2815" s="3" t="s">
+        <v>8936</v>
+      </c>
+      <c r="E2815" s="3" t="s">
+        <v>8937</v>
+      </c>
+      <c r="F2815" s="3" t="s">
+        <v>8938</v>
+      </c>
+      <c r="G2815" s="4"/>
+    </row>
+    <row r="2816" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2816" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2816" s="8">
+        <v>170</v>
+      </c>
+      <c r="C2816" s="3" t="s">
+        <v>8939</v>
+      </c>
+      <c r="D2816" s="3" t="s">
+        <v>8939</v>
+      </c>
+      <c r="E2816" s="3" t="s">
+        <v>8940</v>
+      </c>
+      <c r="F2816" s="3" t="s">
+        <v>8941</v>
+      </c>
+      <c r="G2816" s="4"/>
+    </row>
+    <row r="2817" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2817" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2817" s="8">
+        <v>171</v>
+      </c>
+      <c r="C2817" s="3" t="s">
+        <v>8942</v>
+      </c>
+      <c r="D2817" s="3" t="s">
+        <v>8942</v>
+      </c>
+      <c r="E2817" s="3" t="s">
+        <v>8943</v>
+      </c>
+      <c r="F2817" s="3" t="s">
+        <v>8944</v>
+      </c>
+      <c r="G2817" s="4" t="s">
+        <v>8945</v>
+      </c>
+    </row>
+    <row r="2818" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2818" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2818" s="8">
+        <v>172</v>
+      </c>
+      <c r="C2818" s="3" t="s">
+        <v>8946</v>
+      </c>
+      <c r="D2818" s="3" t="s">
+        <v>8946</v>
+      </c>
+      <c r="E2818" s="3" t="s">
+        <v>8947</v>
+      </c>
+      <c r="F2818" s="3" t="s">
+        <v>8948</v>
+      </c>
+      <c r="G2818" s="4"/>
+    </row>
+    <row r="2819" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2819" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2819" s="8">
+        <v>173</v>
+      </c>
+      <c r="C2819" s="3" t="s">
+        <v>8949</v>
+      </c>
+      <c r="D2819" s="3" t="s">
+        <v>8950</v>
+      </c>
+      <c r="E2819" s="3" t="s">
+        <v>8951</v>
+      </c>
+      <c r="F2819" s="3" t="s">
+        <v>8952</v>
+      </c>
+      <c r="G2819" s="4"/>
+    </row>
+    <row r="2820" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2820" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2820" s="8">
+        <v>174</v>
+      </c>
+      <c r="C2820" s="3" t="s">
+        <v>8953</v>
+      </c>
+      <c r="D2820" s="3" t="s">
+        <v>8953</v>
+      </c>
+      <c r="E2820" s="3" t="s">
+        <v>8954</v>
+      </c>
+      <c r="F2820" s="3" t="s">
+        <v>8955</v>
+      </c>
+      <c r="G2820" s="4"/>
+    </row>
+    <row r="2821" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2821" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2821" s="8">
+        <v>175</v>
+      </c>
+      <c r="C2821" s="3" t="s">
+        <v>8956</v>
+      </c>
+      <c r="D2821" s="3" t="s">
+        <v>8957</v>
+      </c>
+      <c r="E2821" s="3" t="s">
+        <v>8958</v>
+      </c>
+      <c r="F2821" s="3" t="s">
+        <v>8959</v>
+      </c>
+      <c r="G2821" s="4"/>
+    </row>
+    <row r="2822" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2822" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2822" s="8">
+        <v>176</v>
+      </c>
+      <c r="C2822" s="3" t="s">
+        <v>8960</v>
+      </c>
+      <c r="D2822" s="3" t="s">
+        <v>8960</v>
+      </c>
+      <c r="E2822" s="3" t="s">
+        <v>8961</v>
+      </c>
+      <c r="F2822" s="3" t="s">
+        <v>8962</v>
+      </c>
+      <c r="G2822" s="4"/>
+    </row>
+    <row r="2823" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2823" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2823" s="8">
+        <v>177</v>
+      </c>
+      <c r="C2823" s="3" t="s">
+        <v>8963</v>
+      </c>
+      <c r="D2823" s="3" t="s">
+        <v>8964</v>
+      </c>
+      <c r="E2823" s="3" t="s">
+        <v>8965</v>
+      </c>
+      <c r="F2823" s="3" t="s">
+        <v>8966</v>
+      </c>
+      <c r="G2823" s="4"/>
+    </row>
+    <row r="2824" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2824" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2824" s="8">
+        <v>178</v>
+      </c>
+      <c r="C2824" s="3" t="s">
+        <v>8967</v>
+      </c>
+      <c r="D2824" s="3" t="s">
+        <v>8968</v>
+      </c>
+      <c r="E2824" s="3" t="s">
+        <v>3452</v>
+      </c>
+      <c r="F2824" s="3" t="s">
+        <v>8969</v>
+      </c>
+      <c r="G2824" s="4"/>
+    </row>
+    <row r="2825" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2825" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2825" s="8">
+        <v>179</v>
+      </c>
+      <c r="C2825" s="3" t="s">
+        <v>8970</v>
+      </c>
+      <c r="D2825" s="3" t="s">
+        <v>8970</v>
+      </c>
+      <c r="E2825" s="3" t="s">
+        <v>8971</v>
+      </c>
+      <c r="F2825" s="3" t="s">
+        <v>8972</v>
+      </c>
+      <c r="G2825" s="4"/>
+    </row>
+    <row r="2826" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2826" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2826" s="8">
+        <v>180</v>
+      </c>
+      <c r="C2826" s="3" t="s">
+        <v>8973</v>
+      </c>
+      <c r="D2826" s="3" t="s">
+        <v>8973</v>
+      </c>
+      <c r="E2826" s="3" t="s">
+        <v>8974</v>
+      </c>
+      <c r="F2826" s="3" t="s">
+        <v>8975</v>
+      </c>
+      <c r="G2826" s="4"/>
+    </row>
+    <row r="2827" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2827" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2827" s="8">
+        <v>181</v>
+      </c>
+      <c r="C2827" s="3" t="s">
+        <v>8976</v>
+      </c>
+      <c r="D2827" s="3" t="s">
+        <v>8977</v>
+      </c>
+      <c r="E2827" s="3" t="s">
+        <v>8978</v>
+      </c>
+      <c r="F2827" s="3" t="s">
+        <v>8979</v>
+      </c>
+      <c r="G2827" s="4"/>
+    </row>
+    <row r="2828" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2828" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2828" s="8">
+        <v>182</v>
+      </c>
+      <c r="C2828" s="3" t="s">
+        <v>8980</v>
+      </c>
+      <c r="D2828" s="3" t="s">
+        <v>8981</v>
+      </c>
+      <c r="E2828" s="3" t="s">
+        <v>8982</v>
+      </c>
+      <c r="F2828" s="3" t="s">
+        <v>8983</v>
+      </c>
+      <c r="G2828" s="4" t="s">
+        <v>8984</v>
+      </c>
+    </row>
+    <row r="2829" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2829" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2829" s="8">
+        <v>183</v>
+      </c>
+      <c r="C2829" s="3" t="s">
+        <v>8985</v>
+      </c>
+      <c r="D2829" s="3" t="s">
+        <v>8985</v>
+      </c>
+      <c r="E2829" s="3" t="s">
+        <v>8986</v>
+      </c>
+      <c r="F2829" s="3" t="s">
+        <v>8987</v>
+      </c>
+      <c r="G2829" s="4"/>
+    </row>
+    <row r="2830" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2830" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2830" s="8">
+        <v>184</v>
+      </c>
+      <c r="C2830" s="3" t="s">
+        <v>8988</v>
+      </c>
+      <c r="D2830" s="3" t="s">
+        <v>8988</v>
+      </c>
+      <c r="E2830" s="3" t="s">
+        <v>8989</v>
+      </c>
+      <c r="F2830" s="3" t="s">
+        <v>8990</v>
+      </c>
+      <c r="G2830" s="4"/>
+    </row>
+    <row r="2831" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2831" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2831" s="8">
+        <v>185</v>
+      </c>
+      <c r="C2831" s="3" t="s">
+        <v>8991</v>
+      </c>
+      <c r="D2831" s="3" t="s">
+        <v>8992</v>
+      </c>
+      <c r="E2831" s="3" t="s">
+        <v>8993</v>
+      </c>
+      <c r="F2831" s="3" t="s">
+        <v>8994</v>
+      </c>
+      <c r="G2831" s="4"/>
+    </row>
+    <row r="2832" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2832" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2832" s="8">
+        <v>186</v>
+      </c>
+      <c r="C2832" s="3" t="s">
+        <v>8995</v>
+      </c>
+      <c r="D2832" s="3" t="s">
+        <v>8995</v>
+      </c>
+      <c r="E2832" s="3" t="s">
+        <v>8996</v>
+      </c>
+      <c r="F2832" s="3" t="s">
+        <v>8997</v>
+      </c>
+      <c r="G2832" s="4"/>
+    </row>
+    <row r="2833" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2833" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2833" s="8">
+        <v>187</v>
+      </c>
+      <c r="C2833" s="3" t="s">
+        <v>8998</v>
+      </c>
+      <c r="D2833" s="3" t="s">
+        <v>8998</v>
+      </c>
+      <c r="E2833" s="3" t="s">
+        <v>8999</v>
+      </c>
+      <c r="F2833" s="3" t="s">
+        <v>9000</v>
+      </c>
+      <c r="G2833" s="4"/>
+    </row>
+    <row r="2834" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2834" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2834" s="8">
+        <v>188</v>
+      </c>
+      <c r="C2834" s="3" t="s">
+        <v>9001</v>
+      </c>
+      <c r="D2834" s="3" t="s">
+        <v>9001</v>
+      </c>
+      <c r="E2834" s="3" t="s">
+        <v>9002</v>
+      </c>
+      <c r="F2834" s="3" t="s">
+        <v>9003</v>
+      </c>
+      <c r="G2834" s="4"/>
+    </row>
+    <row r="2835" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2835" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2835" s="8">
+        <v>189</v>
+      </c>
+      <c r="C2835" s="3" t="s">
+        <v>9004</v>
+      </c>
+      <c r="D2835" s="3" t="s">
+        <v>9004</v>
+      </c>
+      <c r="E2835" s="3" t="s">
+        <v>9005</v>
+      </c>
+      <c r="F2835" s="3" t="s">
+        <v>9006</v>
+      </c>
+      <c r="G2835" s="4"/>
+    </row>
+    <row r="2836" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2836" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2836" s="8">
+        <v>190</v>
+      </c>
+      <c r="C2836" s="3" t="s">
+        <v>9007</v>
+      </c>
+      <c r="D2836" s="3" t="s">
+        <v>9007</v>
+      </c>
+      <c r="E2836" s="3" t="s">
+        <v>9008</v>
+      </c>
+      <c r="F2836" s="3" t="s">
+        <v>9009</v>
+      </c>
+      <c r="G2836" s="4"/>
+    </row>
+    <row r="2837" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2837" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2837" s="8">
+        <v>191</v>
+      </c>
+      <c r="C2837" s="3" t="s">
+        <v>9010</v>
+      </c>
+      <c r="D2837" s="3" t="s">
+        <v>9011</v>
+      </c>
+      <c r="E2837" s="3" t="s">
+        <v>9012</v>
+      </c>
+      <c r="F2837" s="3" t="s">
+        <v>9013</v>
+      </c>
+      <c r="G2837" s="4"/>
+    </row>
+    <row r="2838" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2838" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2838" s="8">
+        <v>192</v>
+      </c>
+      <c r="C2838" s="3" t="s">
+        <v>9014</v>
+      </c>
+      <c r="D2838" s="3" t="s">
+        <v>9015</v>
+      </c>
+      <c r="E2838" s="3" t="s">
+        <v>9016</v>
+      </c>
+      <c r="F2838" s="3" t="s">
+        <v>9017</v>
+      </c>
+      <c r="G2838" s="4"/>
+    </row>
+    <row r="2839" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2839" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2839" s="8">
+        <v>193</v>
+      </c>
+      <c r="C2839" s="3" t="s">
+        <v>9018</v>
+      </c>
+      <c r="D2839" s="3" t="s">
+        <v>9018</v>
+      </c>
+      <c r="E2839" s="3" t="s">
+        <v>9019</v>
+      </c>
+      <c r="F2839" s="3" t="s">
+        <v>9020</v>
+      </c>
+      <c r="G2839" s="4"/>
+    </row>
+    <row r="2840" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2840" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2840" s="8">
+        <v>194</v>
+      </c>
+      <c r="C2840" s="3" t="s">
+        <v>9021</v>
+      </c>
+      <c r="D2840" s="3" t="s">
+        <v>9021</v>
+      </c>
+      <c r="E2840" s="3" t="s">
+        <v>9022</v>
+      </c>
+      <c r="F2840" s="3" t="s">
+        <v>9023</v>
+      </c>
+      <c r="G2840" s="4"/>
+    </row>
+    <row r="2841" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2841" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2841" s="8">
+        <v>195</v>
+      </c>
+      <c r="C2841" s="3" t="s">
+        <v>9024</v>
+      </c>
+      <c r="D2841" s="3" t="s">
+        <v>9024</v>
+      </c>
+      <c r="E2841" s="3" t="s">
+        <v>9025</v>
+      </c>
+      <c r="F2841" s="3" t="s">
+        <v>9026</v>
+      </c>
+      <c r="G2841" s="4"/>
+    </row>
+    <row r="2842" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2842" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2842" s="8">
+        <v>196</v>
+      </c>
+      <c r="C2842" s="3" t="s">
+        <v>9027</v>
+      </c>
+      <c r="D2842" s="3" t="s">
+        <v>9027</v>
+      </c>
+      <c r="E2842" s="3" t="s">
+        <v>8911</v>
+      </c>
+      <c r="F2842" s="3" t="s">
+        <v>9028</v>
+      </c>
+      <c r="G2842" s="4"/>
+    </row>
+    <row r="2843" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2843" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2843" s="8">
+        <v>197</v>
+      </c>
+      <c r="C2843" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D2843" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E2843" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F2843" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G2843" s="4"/>
+    </row>
+    <row r="2844" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2844" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2844" s="8">
+        <v>198</v>
+      </c>
+      <c r="C2844" s="3" t="s">
+        <v>9029</v>
+      </c>
+      <c r="D2844" s="3" t="s">
+        <v>9029</v>
+      </c>
+      <c r="E2844" s="3" t="s">
+        <v>9030</v>
+      </c>
+      <c r="F2844" s="3" t="s">
+        <v>9031</v>
+      </c>
+      <c r="G2844" s="4"/>
+    </row>
+    <row r="2845" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2845" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2845" s="8">
+        <v>199</v>
+      </c>
+      <c r="C2845" s="3" t="s">
+        <v>9032</v>
+      </c>
+      <c r="D2845" s="3" t="s">
+        <v>9032</v>
+      </c>
+      <c r="E2845" s="3" t="s">
+        <v>9033</v>
+      </c>
+      <c r="F2845" s="3" t="s">
+        <v>9034</v>
+      </c>
+      <c r="G2845" s="4"/>
+    </row>
+    <row r="2846" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2846" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2846" s="8">
+        <v>200</v>
+      </c>
+      <c r="C2846" s="3" t="s">
+        <v>9035</v>
+      </c>
+      <c r="D2846" s="3" t="s">
+        <v>9035</v>
+      </c>
+      <c r="E2846" s="3" t="s">
+        <v>9036</v>
+      </c>
+      <c r="F2846" s="3" t="s">
+        <v>9037</v>
+      </c>
+      <c r="G2846" s="4"/>
+    </row>
+    <row r="2847" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2847" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2847" s="8">
+        <v>201</v>
+      </c>
+      <c r="C2847" s="3" t="s">
+        <v>9038</v>
+      </c>
+      <c r="D2847" s="3" t="s">
+        <v>9038</v>
+      </c>
+      <c r="E2847" s="3" t="s">
+        <v>9039</v>
+      </c>
+      <c r="F2847" s="3" t="s">
+        <v>9040</v>
+      </c>
+      <c r="G2847" s="4"/>
+    </row>
+    <row r="2848" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2848" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2848" s="8">
+        <v>202</v>
+      </c>
+      <c r="C2848" s="3" t="s">
+        <v>9041</v>
+      </c>
+      <c r="D2848" s="3" t="s">
+        <v>9041</v>
+      </c>
+      <c r="E2848" s="3" t="s">
+        <v>9042</v>
+      </c>
+      <c r="F2848" s="3" t="s">
+        <v>9043</v>
+      </c>
+      <c r="G2848" s="4"/>
+    </row>
+    <row r="2849" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2849" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2849" s="8">
+        <v>203</v>
+      </c>
+      <c r="C2849" s="3" t="s">
+        <v>9044</v>
+      </c>
+      <c r="D2849" s="3" t="s">
+        <v>9045</v>
+      </c>
+      <c r="E2849" s="3" t="s">
+        <v>9046</v>
+      </c>
+      <c r="F2849" s="3" t="s">
+        <v>9047</v>
+      </c>
+      <c r="G2849" s="4"/>
+    </row>
+    <row r="2850" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2850" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2850" s="8">
+        <v>204</v>
+      </c>
+      <c r="C2850" s="3" t="s">
+        <v>9048</v>
+      </c>
+      <c r="D2850" s="3" t="s">
+        <v>9049</v>
+      </c>
+      <c r="E2850" s="3" t="s">
+        <v>9050</v>
+      </c>
+      <c r="F2850" s="3" t="s">
+        <v>9051</v>
+      </c>
+      <c r="G2850" s="4"/>
+    </row>
+    <row r="2851" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2851" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2851" s="8">
+        <v>205</v>
+      </c>
+      <c r="C2851" s="3" t="s">
+        <v>9052</v>
+      </c>
+      <c r="D2851" s="3" t="s">
+        <v>9053</v>
+      </c>
+      <c r="E2851" s="3" t="s">
+        <v>3642</v>
+      </c>
+      <c r="F2851" s="3" t="s">
+        <v>3643</v>
+      </c>
+      <c r="G2851" s="4"/>
+    </row>
+    <row r="2852" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2852" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2852" s="8">
+        <v>206</v>
+      </c>
+      <c r="C2852" s="3" t="s">
+        <v>3644</v>
+      </c>
+      <c r="D2852" s="3" t="s">
+        <v>3645</v>
+      </c>
+      <c r="E2852" s="3" t="s">
+        <v>3646</v>
+      </c>
+      <c r="F2852" s="3" t="s">
+        <v>3647</v>
+      </c>
+      <c r="G2852" s="4"/>
+    </row>
+    <row r="2853" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2853" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2853" s="8">
+        <v>207</v>
+      </c>
+      <c r="C2853" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D2853" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E2853" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F2853" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G2853" s="4"/>
+    </row>
+    <row r="2854" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2854" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2854" s="8">
+        <v>208</v>
+      </c>
+      <c r="C2854" s="3" t="s">
+        <v>9054</v>
+      </c>
+      <c r="D2854" s="3" t="s">
+        <v>9055</v>
+      </c>
+      <c r="E2854" s="3" t="s">
+        <v>9056</v>
+      </c>
+      <c r="F2854" s="3" t="s">
+        <v>9057</v>
+      </c>
+      <c r="G2854" s="4"/>
+    </row>
+    <row r="2855" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2855" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2855" s="8">
+        <v>209</v>
+      </c>
+      <c r="C2855" s="3" t="s">
+        <v>9058</v>
+      </c>
+      <c r="D2855" s="3" t="s">
+        <v>9059</v>
+      </c>
+      <c r="E2855" s="3" t="s">
+        <v>8372</v>
+      </c>
+      <c r="F2855" s="3" t="s">
+        <v>8373</v>
+      </c>
+      <c r="G2855" s="4"/>
+    </row>
+    <row r="2856" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2856" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2856" s="8">
+        <v>210</v>
+      </c>
+      <c r="C2856" s="3" t="s">
+        <v>9060</v>
+      </c>
+      <c r="D2856" s="3" t="s">
+        <v>9061</v>
+      </c>
+      <c r="E2856" s="3" t="s">
+        <v>8376</v>
+      </c>
+      <c r="F2856" s="3" t="s">
+        <v>8377</v>
+      </c>
+      <c r="G2856" s="4"/>
+    </row>
+    <row r="2857" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2857" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2857" s="8">
+        <v>211</v>
+      </c>
+      <c r="C2857" s="3" t="s">
+        <v>9062</v>
+      </c>
+      <c r="D2857" s="3" t="s">
+        <v>9063</v>
+      </c>
+      <c r="E2857" s="3" t="s">
+        <v>9064</v>
+      </c>
+      <c r="F2857" s="3" t="s">
+        <v>9065</v>
+      </c>
+      <c r="G2857" s="4"/>
+    </row>
+    <row r="2858" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2858" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2858" s="8">
+        <v>212</v>
+      </c>
+      <c r="C2858" s="3" t="s">
+        <v>9066</v>
+      </c>
+      <c r="D2858" s="3" t="s">
+        <v>9067</v>
+      </c>
+      <c r="E2858" s="3" t="s">
+        <v>2775</v>
+      </c>
+      <c r="F2858" s="3" t="s">
+        <v>9068</v>
+      </c>
+      <c r="G2858" s="4"/>
+    </row>
+    <row r="2859" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2859" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2859" s="8">
+        <v>213</v>
+      </c>
+      <c r="C2859" s="3" t="s">
+        <v>9069</v>
+      </c>
+      <c r="D2859" s="3" t="s">
+        <v>9069</v>
+      </c>
+      <c r="E2859" s="3" t="s">
+        <v>9070</v>
+      </c>
+      <c r="F2859" s="3" t="s">
+        <v>9071</v>
+      </c>
+      <c r="G2859" s="4"/>
+    </row>
+    <row r="2860" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2860" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2860" s="8">
+        <v>214</v>
+      </c>
+      <c r="C2860" s="3" t="s">
+        <v>9072</v>
+      </c>
+      <c r="D2860" s="3" t="s">
+        <v>9072</v>
+      </c>
+      <c r="E2860" s="3" t="s">
+        <v>9073</v>
+      </c>
+      <c r="F2860" s="3" t="s">
+        <v>9074</v>
+      </c>
+      <c r="G2860" s="4"/>
+    </row>
+    <row r="2861" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2861" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2861" s="8">
+        <v>215</v>
+      </c>
+      <c r="C2861" s="3" t="s">
+        <v>9075</v>
+      </c>
+      <c r="D2861" s="3" t="s">
+        <v>9075</v>
+      </c>
+      <c r="E2861" s="3" t="s">
+        <v>9076</v>
+      </c>
+      <c r="F2861" s="3" t="s">
+        <v>9077</v>
+      </c>
+      <c r="G2861" s="4"/>
+    </row>
+    <row r="2862" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2862" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2862" s="8">
+        <v>216</v>
+      </c>
+      <c r="C2862" s="3" t="s">
+        <v>9078</v>
+      </c>
+      <c r="D2862" s="3" t="s">
+        <v>9078</v>
+      </c>
+      <c r="E2862" s="3" t="s">
+        <v>9079</v>
+      </c>
+      <c r="F2862" s="3" t="s">
+        <v>9080</v>
+      </c>
+      <c r="G2862" s="4"/>
+    </row>
+    <row r="2863" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2863" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2863" s="8">
+        <v>217</v>
+      </c>
+      <c r="C2863" s="3" t="s">
+        <v>9081</v>
+      </c>
+      <c r="D2863" s="3" t="s">
+        <v>9082</v>
+      </c>
+      <c r="E2863" s="3" t="s">
+        <v>9083</v>
+      </c>
+      <c r="F2863" s="3" t="s">
+        <v>9084</v>
+      </c>
+      <c r="G2863" s="4"/>
+    </row>
+    <row r="2864" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2864" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2864" s="8">
+        <v>218</v>
+      </c>
+      <c r="C2864" s="3" t="s">
+        <v>9085</v>
+      </c>
+      <c r="D2864" s="3" t="s">
+        <v>9086</v>
+      </c>
+      <c r="E2864" s="3" t="s">
+        <v>9087</v>
+      </c>
+      <c r="F2864" s="3" t="s">
+        <v>9088</v>
+      </c>
+      <c r="G2864" s="4" t="s">
+        <v>9089</v>
+      </c>
+    </row>
+    <row r="2865" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2865" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2865" s="8">
+        <v>219</v>
+      </c>
+      <c r="C2865" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D2865" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E2865" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F2865" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G2865" s="4"/>
+    </row>
+    <row r="2866" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2866" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2866" s="8">
+        <v>220</v>
+      </c>
+      <c r="C2866" s="3" t="s">
+        <v>9090</v>
+      </c>
+      <c r="D2866" s="3" t="s">
+        <v>9091</v>
+      </c>
+      <c r="E2866" s="3" t="s">
+        <v>9092</v>
+      </c>
+      <c r="F2866" s="3" t="s">
+        <v>9093</v>
+      </c>
+      <c r="G2866" s="4"/>
+    </row>
+    <row r="2867" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2867" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2867" s="8">
+        <v>221</v>
+      </c>
+      <c r="C2867" s="3" t="s">
+        <v>9094</v>
+      </c>
+      <c r="D2867" s="3" t="s">
+        <v>9095</v>
+      </c>
+      <c r="E2867" s="3" t="s">
+        <v>9096</v>
+      </c>
+      <c r="F2867" s="3" t="s">
+        <v>9097</v>
+      </c>
+      <c r="G2867" s="4"/>
+    </row>
+    <row r="2868" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2868" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2868" s="8">
+        <v>222</v>
+      </c>
+      <c r="C2868" s="3" t="s">
+        <v>9098</v>
+      </c>
+      <c r="D2868" s="3" t="s">
+        <v>9099</v>
+      </c>
+      <c r="E2868" s="3" t="s">
+        <v>9100</v>
+      </c>
+      <c r="F2868" s="3" t="s">
+        <v>9101</v>
+      </c>
+      <c r="G2868" s="4"/>
+    </row>
+    <row r="2869" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2869" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2869" s="8">
+        <v>223</v>
+      </c>
+      <c r="C2869" s="3" t="s">
+        <v>9102</v>
+      </c>
+      <c r="D2869" s="3" t="s">
+        <v>9103</v>
+      </c>
+      <c r="E2869" s="3" t="s">
+        <v>9104</v>
+      </c>
+      <c r="F2869" s="3" t="s">
+        <v>9105</v>
+      </c>
+      <c r="G2869" s="4"/>
+    </row>
+    <row r="2870" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2870" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2870" s="8">
+        <v>224</v>
+      </c>
+      <c r="C2870" s="3" t="s">
+        <v>9106</v>
+      </c>
+      <c r="D2870" s="3" t="s">
+        <v>9107</v>
+      </c>
+      <c r="E2870" s="3" t="s">
+        <v>9108</v>
+      </c>
+      <c r="F2870" s="3" t="s">
+        <v>9109</v>
+      </c>
+      <c r="G2870" s="4"/>
+    </row>
+    <row r="2871" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2871" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2871" s="8">
+        <v>225</v>
+      </c>
+      <c r="C2871" s="3" t="s">
+        <v>9110</v>
+      </c>
+      <c r="D2871" s="3" t="s">
+        <v>9111</v>
+      </c>
+      <c r="E2871" s="3" t="s">
+        <v>9112</v>
+      </c>
+      <c r="F2871" s="3" t="s">
+        <v>9113</v>
+      </c>
+      <c r="G2871" s="4"/>
+    </row>
+    <row r="2872" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2872" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2872" s="8">
+        <v>226</v>
+      </c>
+      <c r="C2872" s="3" t="s">
+        <v>9114</v>
+      </c>
+      <c r="D2872" s="3" t="s">
+        <v>9115</v>
+      </c>
+      <c r="E2872" s="3" t="s">
+        <v>9116</v>
+      </c>
+      <c r="F2872" s="3" t="s">
+        <v>9117</v>
+      </c>
+      <c r="G2872" s="4"/>
+    </row>
+    <row r="2873" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2873" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2873" s="8">
+        <v>227</v>
+      </c>
+      <c r="C2873" s="3" t="s">
+        <v>9118</v>
+      </c>
+      <c r="D2873" s="3" t="s">
+        <v>9118</v>
+      </c>
+      <c r="E2873" s="3" t="s">
+        <v>9119</v>
+      </c>
+      <c r="F2873" s="3" t="s">
+        <v>9120</v>
+      </c>
+      <c r="G2873" s="4"/>
+    </row>
+    <row r="2874" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2874" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2874" s="8">
+        <v>228</v>
+      </c>
+      <c r="C2874" s="3" t="s">
+        <v>9121</v>
+      </c>
+      <c r="D2874" s="3" t="s">
+        <v>9121</v>
+      </c>
+      <c r="E2874" s="3" t="s">
+        <v>9122</v>
+      </c>
+      <c r="F2874" s="3" t="s">
+        <v>9123</v>
+      </c>
+      <c r="G2874" s="4"/>
+    </row>
+    <row r="2875" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2875" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2875" s="8">
+        <v>229</v>
+      </c>
+      <c r="C2875" s="3" t="s">
+        <v>9124</v>
+      </c>
+      <c r="D2875" s="3" t="s">
+        <v>9125</v>
+      </c>
+      <c r="E2875" s="3" t="s">
+        <v>8555</v>
+      </c>
+      <c r="F2875" s="3" t="s">
+        <v>8556</v>
+      </c>
+      <c r="G2875" s="4"/>
+    </row>
+    <row r="2876" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2876" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2876" s="8">
+        <v>230</v>
+      </c>
+      <c r="C2876" s="3" t="s">
+        <v>9126</v>
+      </c>
+      <c r="D2876" s="3" t="s">
+        <v>9126</v>
+      </c>
+      <c r="E2876" s="3" t="s">
+        <v>9127</v>
+      </c>
+      <c r="F2876" s="3" t="s">
+        <v>9128</v>
+      </c>
+      <c r="G2876" s="4"/>
+    </row>
+    <row r="2877" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2877" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2877" s="8">
+        <v>231</v>
+      </c>
+      <c r="C2877" s="3" t="s">
+        <v>9106</v>
+      </c>
+      <c r="D2877" s="3" t="s">
+        <v>9107</v>
+      </c>
+      <c r="E2877" s="3" t="s">
+        <v>9108</v>
+      </c>
+      <c r="F2877" s="3" t="s">
+        <v>9129</v>
+      </c>
+      <c r="G2877" s="4"/>
+    </row>
+    <row r="2878" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2878" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2878" s="8">
+        <v>232</v>
+      </c>
+      <c r="C2878" s="3" t="s">
+        <v>9110</v>
+      </c>
+      <c r="D2878" s="3" t="s">
+        <v>9111</v>
+      </c>
+      <c r="E2878" s="3" t="s">
+        <v>9112</v>
+      </c>
+      <c r="F2878" s="3" t="s">
+        <v>9130</v>
+      </c>
+      <c r="G2878" s="4"/>
+    </row>
+    <row r="2879" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2879" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2879" s="8">
+        <v>233</v>
+      </c>
+      <c r="C2879" s="3" t="s">
+        <v>9131</v>
+      </c>
+      <c r="D2879" s="3" t="s">
+        <v>9132</v>
+      </c>
+      <c r="E2879" s="3" t="s">
+        <v>9133</v>
+      </c>
+      <c r="F2879" s="3" t="s">
+        <v>9134</v>
+      </c>
+      <c r="G2879" s="4"/>
+    </row>
+    <row r="2880" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2880" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2880" s="8">
+        <v>234</v>
+      </c>
+      <c r="C2880" s="3" t="s">
+        <v>9135</v>
+      </c>
+      <c r="D2880" s="3" t="s">
+        <v>9136</v>
+      </c>
+      <c r="E2880" s="3" t="s">
+        <v>9116</v>
+      </c>
+      <c r="F2880" s="3" t="s">
+        <v>9137</v>
+      </c>
+      <c r="G2880" s="4"/>
+    </row>
+    <row r="2881" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2881" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2881" s="8">
+        <v>235</v>
+      </c>
+      <c r="C2881" s="3" t="s">
+        <v>9138</v>
+      </c>
+      <c r="D2881" s="3" t="s">
+        <v>9139</v>
+      </c>
+      <c r="E2881" s="3" t="s">
+        <v>9140</v>
+      </c>
+      <c r="F2881" s="3" t="s">
+        <v>9141</v>
+      </c>
+      <c r="G2881" s="4"/>
+    </row>
+    <row r="2882" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2882" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2882" s="8">
+        <v>236</v>
+      </c>
+      <c r="C2882" s="3" t="s">
+        <v>9142</v>
+      </c>
+      <c r="D2882" s="3" t="s">
+        <v>9143</v>
+      </c>
+      <c r="E2882" s="3" t="s">
+        <v>9144</v>
+      </c>
+      <c r="F2882" s="3" t="s">
+        <v>9145</v>
+      </c>
+      <c r="G2882" s="4"/>
+    </row>
+    <row r="2883" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2883" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2883" s="8">
+        <v>237</v>
+      </c>
+      <c r="C2883" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D2883" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E2883" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F2883" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G2883" s="4"/>
+    </row>
+    <row r="2884" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2884" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2884" s="8">
+        <v>238</v>
+      </c>
+      <c r="C2884" s="3" t="s">
+        <v>9146</v>
+      </c>
+      <c r="D2884" s="3" t="s">
+        <v>9146</v>
+      </c>
+      <c r="E2884" s="3" t="s">
+        <v>9070</v>
+      </c>
+      <c r="F2884" s="3" t="s">
+        <v>9071</v>
+      </c>
+      <c r="G2884" s="4"/>
+    </row>
+    <row r="2885" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2885" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2885" s="8">
+        <v>239</v>
+      </c>
+      <c r="C2885" s="3" t="s">
+        <v>9147</v>
+      </c>
+      <c r="D2885" s="3" t="s">
+        <v>9148</v>
+      </c>
+      <c r="E2885" s="3" t="s">
+        <v>2794</v>
+      </c>
+      <c r="F2885" s="3" t="s">
+        <v>2795</v>
+      </c>
+      <c r="G2885" s="4"/>
+    </row>
+    <row r="2886" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2886" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2886" s="8">
+        <v>240</v>
+      </c>
+      <c r="C2886" s="3" t="s">
+        <v>8490</v>
+      </c>
+      <c r="D2886" s="3" t="s">
+        <v>8491</v>
+      </c>
+      <c r="E2886" s="3" t="s">
+        <v>8492</v>
+      </c>
+      <c r="F2886" s="3" t="s">
+        <v>9149</v>
+      </c>
+      <c r="G2886" s="4"/>
+    </row>
+    <row r="2887" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2887" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2887" s="8">
+        <v>241</v>
+      </c>
+      <c r="C2887" s="3" t="s">
+        <v>9150</v>
+      </c>
+      <c r="D2887" s="3" t="s">
+        <v>9150</v>
+      </c>
+      <c r="E2887" s="3" t="s">
+        <v>9151</v>
+      </c>
+      <c r="F2887" s="3" t="s">
+        <v>9152</v>
+      </c>
+      <c r="G2887" s="4"/>
+    </row>
+    <row r="2888" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2888" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2888" s="8">
+        <v>242</v>
+      </c>
+      <c r="C2888" s="3" t="s">
+        <v>9153</v>
+      </c>
+      <c r="D2888" s="3" t="s">
+        <v>9154</v>
+      </c>
+      <c r="E2888" s="3" t="s">
+        <v>9155</v>
+      </c>
+      <c r="F2888" s="3" t="s">
+        <v>9156</v>
+      </c>
+      <c r="G2888" s="4"/>
+    </row>
+    <row r="2889" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2889" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2889" s="8">
+        <v>243</v>
+      </c>
+      <c r="C2889" s="3" t="s">
+        <v>9157</v>
+      </c>
+      <c r="D2889" s="3" t="s">
+        <v>9158</v>
+      </c>
+      <c r="E2889" s="3" t="s">
+        <v>9159</v>
+      </c>
+      <c r="F2889" s="3" t="s">
+        <v>9160</v>
+      </c>
+      <c r="G2889" s="4"/>
+    </row>
+    <row r="2890" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2890" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2890" s="8">
+        <v>244</v>
+      </c>
+      <c r="C2890" s="3" t="s">
+        <v>9161</v>
+      </c>
+      <c r="D2890" s="3" t="s">
+        <v>9162</v>
+      </c>
+      <c r="E2890" s="3" t="s">
+        <v>9163</v>
+      </c>
+      <c r="F2890" s="3" t="s">
+        <v>9164</v>
+      </c>
+      <c r="G2890" s="4"/>
+    </row>
+    <row r="2891" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2891" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2891" s="8">
+        <v>245</v>
+      </c>
+      <c r="C2891" s="3" t="s">
+        <v>9102</v>
+      </c>
+      <c r="D2891" s="3" t="s">
+        <v>9103</v>
+      </c>
+      <c r="E2891" s="3" t="s">
+        <v>9104</v>
+      </c>
+      <c r="F2891" s="3" t="s">
+        <v>9105</v>
+      </c>
+      <c r="G2891" s="4"/>
+    </row>
+    <row r="2892" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2892" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2892" s="8">
+        <v>246</v>
+      </c>
+      <c r="C2892" s="3" t="s">
+        <v>9106</v>
+      </c>
+      <c r="D2892" s="3" t="s">
+        <v>9107</v>
+      </c>
+      <c r="E2892" s="3" t="s">
+        <v>9108</v>
+      </c>
+      <c r="F2892" s="3" t="s">
+        <v>9129</v>
+      </c>
+      <c r="G2892" s="4"/>
+    </row>
+    <row r="2893" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2893" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2893" s="8">
+        <v>247</v>
+      </c>
+      <c r="C2893" s="3" t="s">
+        <v>9165</v>
+      </c>
+      <c r="D2893" s="3" t="s">
+        <v>9165</v>
+      </c>
+      <c r="E2893" s="3" t="s">
+        <v>9166</v>
+      </c>
+      <c r="F2893" s="3" t="s">
+        <v>9167</v>
+      </c>
+      <c r="G2893" s="4"/>
+    </row>
+    <row r="2894" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2894" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2894" s="8">
+        <v>248</v>
+      </c>
+      <c r="C2894" s="3" t="s">
+        <v>9168</v>
+      </c>
+      <c r="D2894" s="3" t="s">
+        <v>9169</v>
+      </c>
+      <c r="E2894" s="3" t="s">
+        <v>9170</v>
+      </c>
+      <c r="F2894" s="3" t="s">
+        <v>9171</v>
+      </c>
+      <c r="G2894" s="4"/>
+    </row>
+    <row r="2895" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2895" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2895" s="8">
+        <v>249</v>
+      </c>
+      <c r="C2895" s="3" t="s">
+        <v>9172</v>
+      </c>
+      <c r="D2895" s="3" t="s">
+        <v>9172</v>
+      </c>
+      <c r="E2895" s="3" t="s">
+        <v>9173</v>
+      </c>
+      <c r="F2895" s="3" t="s">
+        <v>9174</v>
+      </c>
+      <c r="G2895" s="4"/>
+    </row>
+    <row r="2896" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2896" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2896" s="8">
+        <v>250</v>
+      </c>
+      <c r="C2896" s="3" t="s">
+        <v>9175</v>
+      </c>
+      <c r="D2896" s="3" t="s">
+        <v>9175</v>
+      </c>
+      <c r="E2896" s="3" t="s">
+        <v>9176</v>
+      </c>
+      <c r="F2896" s="3" t="s">
+        <v>9177</v>
+      </c>
+      <c r="G2896" s="4"/>
+    </row>
+    <row r="2897" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2897" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2897" s="8">
+        <v>251</v>
+      </c>
+      <c r="C2897" s="3" t="s">
+        <v>9178</v>
+      </c>
+      <c r="D2897" s="3" t="s">
+        <v>9179</v>
+      </c>
+      <c r="E2897" s="3" t="s">
+        <v>9180</v>
+      </c>
+      <c r="F2897" s="3" t="s">
+        <v>9181</v>
+      </c>
+      <c r="G2897" s="4"/>
+    </row>
+    <row r="2898" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2898" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2898" s="8">
+        <v>252</v>
+      </c>
+      <c r="C2898" s="3" t="s">
+        <v>9182</v>
+      </c>
+      <c r="D2898" s="3" t="s">
+        <v>9183</v>
+      </c>
+      <c r="E2898" s="3" t="s">
+        <v>9184</v>
+      </c>
+      <c r="F2898" s="3" t="s">
+        <v>9185</v>
+      </c>
+      <c r="G2898" s="4"/>
+    </row>
+    <row r="2899" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2899" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2899" s="8">
+        <v>253</v>
+      </c>
+      <c r="C2899" s="3" t="s">
+        <v>9126</v>
+      </c>
+      <c r="D2899" s="3" t="s">
+        <v>9126</v>
+      </c>
+      <c r="E2899" s="3" t="s">
+        <v>9127</v>
+      </c>
+      <c r="F2899" s="3" t="s">
+        <v>9128</v>
+      </c>
+      <c r="G2899" s="4"/>
+    </row>
+    <row r="2900" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2900" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2900" s="8">
+        <v>254</v>
+      </c>
+      <c r="C2900" s="3" t="s">
+        <v>9106</v>
+      </c>
+      <c r="D2900" s="3" t="s">
+        <v>9107</v>
+      </c>
+      <c r="E2900" s="3" t="s">
+        <v>9108</v>
+      </c>
+      <c r="F2900" s="3" t="s">
+        <v>9186</v>
+      </c>
+      <c r="G2900" s="4"/>
+    </row>
+    <row r="2901" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2901" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2901" s="8">
+        <v>255</v>
+      </c>
+      <c r="C2901" s="3" t="s">
+        <v>9187</v>
+      </c>
+      <c r="D2901" s="3" t="s">
+        <v>9188</v>
+      </c>
+      <c r="E2901" s="3" t="s">
+        <v>9189</v>
+      </c>
+      <c r="F2901" s="3" t="s">
+        <v>9190</v>
+      </c>
+      <c r="G2901" s="4"/>
+    </row>
+    <row r="2902" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2902" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2902" s="8">
+        <v>256</v>
+      </c>
+      <c r="C2902" s="3" t="s">
+        <v>9191</v>
+      </c>
+      <c r="D2902" s="3" t="s">
+        <v>9192</v>
+      </c>
+      <c r="E2902" s="3" t="s">
+        <v>9133</v>
+      </c>
+      <c r="F2902" s="3" t="s">
+        <v>9134</v>
+      </c>
+      <c r="G2902" s="4"/>
+    </row>
+    <row r="2903" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2903" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2903" s="8">
+        <v>257</v>
+      </c>
+      <c r="C2903" s="3" t="s">
+        <v>9138</v>
+      </c>
+      <c r="D2903" s="3" t="s">
+        <v>9139</v>
+      </c>
+      <c r="E2903" s="3" t="s">
+        <v>9140</v>
+      </c>
+      <c r="F2903" s="3" t="s">
+        <v>9141</v>
+      </c>
+      <c r="G2903" s="4"/>
+    </row>
+    <row r="2904" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2904" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2904" s="8">
+        <v>258</v>
+      </c>
+      <c r="C2904" s="3" t="s">
+        <v>9142</v>
+      </c>
+      <c r="D2904" s="3" t="s">
+        <v>9143</v>
+      </c>
+      <c r="E2904" s="3" t="s">
+        <v>9144</v>
+      </c>
+      <c r="F2904" s="3" t="s">
+        <v>9145</v>
+      </c>
+      <c r="G2904" s="4"/>
+    </row>
+    <row r="2905" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2905" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2905" s="8">
+        <v>259</v>
+      </c>
+      <c r="C2905" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D2905" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E2905" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F2905" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G2905" s="4"/>
+    </row>
+    <row r="2906" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2906" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2906" s="8">
+        <v>260</v>
+      </c>
+      <c r="C2906" s="3" t="s">
+        <v>9146</v>
+      </c>
+      <c r="D2906" s="3" t="s">
+        <v>9146</v>
+      </c>
+      <c r="E2906" s="3" t="s">
+        <v>9070</v>
+      </c>
+      <c r="F2906" s="3" t="s">
+        <v>9071</v>
+      </c>
+      <c r="G2906" s="4"/>
+    </row>
+    <row r="2907" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2907" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2907" s="8">
+        <v>261</v>
+      </c>
+      <c r="C2907" s="3" t="s">
+        <v>9147</v>
+      </c>
+      <c r="D2907" s="3" t="s">
+        <v>9148</v>
+      </c>
+      <c r="E2907" s="3" t="s">
+        <v>2794</v>
+      </c>
+      <c r="F2907" s="3" t="s">
+        <v>2795</v>
+      </c>
+      <c r="G2907" s="4"/>
+    </row>
+    <row r="2908" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2908" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2908" s="8">
+        <v>262</v>
+      </c>
+      <c r="C2908" s="3" t="s">
+        <v>8490</v>
+      </c>
+      <c r="D2908" s="3" t="s">
+        <v>8491</v>
+      </c>
+      <c r="E2908" s="3" t="s">
+        <v>8492</v>
+      </c>
+      <c r="F2908" s="3" t="s">
+        <v>9149</v>
+      </c>
+      <c r="G2908" s="4"/>
+    </row>
+    <row r="2909" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2909" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2909" s="8">
+        <v>263</v>
+      </c>
+      <c r="C2909" s="3" t="s">
+        <v>9193</v>
+      </c>
+      <c r="D2909" s="3" t="s">
+        <v>9194</v>
+      </c>
+      <c r="E2909" s="3" t="s">
+        <v>9195</v>
+      </c>
+      <c r="F2909" s="3" t="s">
+        <v>9196</v>
+      </c>
+      <c r="G2909" s="4"/>
+    </row>
+    <row r="2910" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2910" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2910" s="8">
+        <v>264</v>
+      </c>
+      <c r="C2910" s="3" t="s">
+        <v>9197</v>
+      </c>
+      <c r="D2910" s="3" t="s">
+        <v>9198</v>
+      </c>
+      <c r="E2910" s="3" t="s">
+        <v>9199</v>
+      </c>
+      <c r="F2910" s="3" t="s">
+        <v>9200</v>
+      </c>
+      <c r="G2910" s="4"/>
+    </row>
+    <row r="2911" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2911" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2911" s="8">
+        <v>265</v>
+      </c>
+      <c r="C2911" s="3" t="s">
+        <v>9201</v>
+      </c>
+      <c r="D2911" s="3" t="s">
+        <v>9202</v>
+      </c>
+      <c r="E2911" s="3" t="s">
+        <v>9100</v>
+      </c>
+      <c r="F2911" s="3" t="s">
+        <v>9101</v>
+      </c>
+      <c r="G2911" s="4"/>
+    </row>
+    <row r="2912" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2912" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2912" s="8">
+        <v>266</v>
+      </c>
+      <c r="C2912" s="3" t="s">
+        <v>9203</v>
+      </c>
+      <c r="D2912" s="3" t="s">
+        <v>9204</v>
+      </c>
+      <c r="E2912" s="3" t="s">
+        <v>9205</v>
+      </c>
+      <c r="F2912" s="3" t="s">
+        <v>9206</v>
+      </c>
+      <c r="G2912" s="4"/>
+    </row>
+    <row r="2913" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2913" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2913" s="8">
+        <v>267</v>
+      </c>
+      <c r="C2913" s="3" t="s">
+        <v>9102</v>
+      </c>
+      <c r="D2913" s="3" t="s">
+        <v>9103</v>
+      </c>
+      <c r="E2913" s="3" t="s">
+        <v>9104</v>
+      </c>
+      <c r="F2913" s="3" t="s">
+        <v>9105</v>
+      </c>
+      <c r="G2913" s="4"/>
+    </row>
+    <row r="2914" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2914" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2914" s="8">
+        <v>268</v>
+      </c>
+      <c r="C2914" s="3" t="s">
+        <v>9106</v>
+      </c>
+      <c r="D2914" s="3" t="s">
+        <v>9107</v>
+      </c>
+      <c r="E2914" s="3" t="s">
+        <v>9108</v>
+      </c>
+      <c r="F2914" s="3" t="s">
+        <v>9129</v>
+      </c>
+      <c r="G2914" s="4"/>
+    </row>
+    <row r="2915" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2915" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2915" s="8">
+        <v>269</v>
+      </c>
+      <c r="C2915" s="3" t="s">
+        <v>9207</v>
+      </c>
+      <c r="D2915" s="3" t="s">
+        <v>9208</v>
+      </c>
+      <c r="E2915" s="3" t="s">
+        <v>9209</v>
+      </c>
+      <c r="F2915" s="3" t="s">
+        <v>9210</v>
+      </c>
+      <c r="G2915" s="4"/>
+    </row>
+    <row r="2916" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2916" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2916" s="8">
+        <v>270</v>
+      </c>
+      <c r="C2916" s="3" t="s">
+        <v>9211</v>
+      </c>
+      <c r="D2916" s="3" t="s">
+        <v>9212</v>
+      </c>
+      <c r="E2916" s="3" t="s">
+        <v>9213</v>
+      </c>
+      <c r="F2916" s="3" t="s">
+        <v>9214</v>
+      </c>
+      <c r="G2916" s="4"/>
+    </row>
+    <row r="2917" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2917" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2917" s="8">
+        <v>271</v>
+      </c>
+      <c r="C2917" s="3" t="s">
+        <v>9215</v>
+      </c>
+      <c r="D2917" s="3" t="s">
+        <v>9215</v>
+      </c>
+      <c r="E2917" s="3" t="s">
+        <v>9216</v>
+      </c>
+      <c r="F2917" s="3" t="s">
+        <v>9217</v>
+      </c>
+      <c r="G2917" s="4"/>
+    </row>
+    <row r="2918" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2918" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2918" s="8">
+        <v>272</v>
+      </c>
+      <c r="C2918" s="3" t="s">
+        <v>9218</v>
+      </c>
+      <c r="D2918" s="3" t="s">
+        <v>9218</v>
+      </c>
+      <c r="E2918" s="3" t="s">
+        <v>9219</v>
+      </c>
+      <c r="F2918" s="3" t="s">
+        <v>9220</v>
+      </c>
+      <c r="G2918" s="4"/>
+    </row>
+    <row r="2919" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2919" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2919" s="8">
+        <v>273</v>
+      </c>
+      <c r="C2919" s="3" t="s">
+        <v>9221</v>
+      </c>
+      <c r="D2919" s="3" t="s">
+        <v>9221</v>
+      </c>
+      <c r="E2919" s="3" t="s">
+        <v>9222</v>
+      </c>
+      <c r="F2919" s="3" t="s">
+        <v>9223</v>
+      </c>
+      <c r="G2919" s="4"/>
+    </row>
+    <row r="2920" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2920" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2920" s="8">
+        <v>274</v>
+      </c>
+      <c r="C2920" s="3" t="s">
+        <v>9224</v>
+      </c>
+      <c r="D2920" s="3" t="s">
+        <v>9224</v>
+      </c>
+      <c r="E2920" s="3" t="s">
+        <v>9225</v>
+      </c>
+      <c r="F2920" s="3" t="s">
+        <v>9226</v>
+      </c>
+      <c r="G2920" s="4"/>
+    </row>
+    <row r="2921" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A2921" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2921" s="8">
+        <v>275</v>
+      </c>
+      <c r="C2921" s="3" t="s">
+        <v>9227</v>
+      </c>
+      <c r="D2921" s="3" t="s">
+        <v>9228</v>
+      </c>
+      <c r="E2921" s="3" t="s">
+        <v>9229</v>
+      </c>
+      <c r="F2921" s="3" t="s">
+        <v>9230</v>
+      </c>
+      <c r="G2921" s="4" t="s">
+        <v>9231</v>
+      </c>
+    </row>
+    <row r="2922" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2922" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2922" s="8">
+        <v>276</v>
+      </c>
+      <c r="C2922" s="3" t="s">
+        <v>9232</v>
+      </c>
+      <c r="D2922" s="3" t="s">
+        <v>9233</v>
+      </c>
+      <c r="E2922" s="3" t="s">
+        <v>9234</v>
+      </c>
+      <c r="F2922" s="3" t="s">
+        <v>9235</v>
+      </c>
+      <c r="G2922" s="4"/>
+    </row>
+    <row r="2923" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2923" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2923" s="8">
+        <v>277</v>
+      </c>
+      <c r="C2923" s="3" t="s">
+        <v>9236</v>
+      </c>
+      <c r="D2923" s="3" t="s">
+        <v>9236</v>
+      </c>
+      <c r="E2923" s="3" t="s">
+        <v>9237</v>
+      </c>
+      <c r="F2923" s="3" t="s">
+        <v>9238</v>
+      </c>
+      <c r="G2923" s="4"/>
+    </row>
+    <row r="2924" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2924" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2924" s="8">
+        <v>278</v>
+      </c>
+      <c r="C2924" s="3" t="s">
+        <v>9239</v>
+      </c>
+      <c r="D2924" s="3" t="s">
+        <v>9239</v>
+      </c>
+      <c r="E2924" s="3" t="s">
+        <v>9240</v>
+      </c>
+      <c r="F2924" s="3" t="s">
+        <v>9241</v>
+      </c>
+      <c r="G2924" s="4"/>
+    </row>
+    <row r="2925" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2925" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2925" s="8">
+        <v>279</v>
+      </c>
+      <c r="C2925" s="3" t="s">
+        <v>9242</v>
+      </c>
+      <c r="D2925" s="3" t="s">
+        <v>9242</v>
+      </c>
+      <c r="E2925" s="3" t="s">
+        <v>9243</v>
+      </c>
+      <c r="F2925" s="3" t="s">
+        <v>9244</v>
+      </c>
+      <c r="G2925" s="4"/>
+    </row>
+    <row r="2926" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2926" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2926" s="8">
+        <v>280</v>
+      </c>
+      <c r="C2926" s="3" t="s">
+        <v>9245</v>
+      </c>
+      <c r="D2926" s="3" t="s">
+        <v>9245</v>
+      </c>
+      <c r="E2926" s="3" t="s">
+        <v>9246</v>
+      </c>
+      <c r="F2926" s="3" t="s">
+        <v>9247</v>
+      </c>
+      <c r="G2926" s="4"/>
+    </row>
+    <row r="2927" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2927" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2927" s="8">
+        <v>281</v>
+      </c>
+      <c r="C2927" s="3" t="s">
+        <v>9248</v>
+      </c>
+      <c r="D2927" s="3" t="s">
+        <v>9248</v>
+      </c>
+      <c r="E2927" s="3" t="s">
+        <v>9249</v>
+      </c>
+      <c r="F2927" s="3" t="s">
+        <v>9250</v>
+      </c>
+      <c r="G2927" s="4"/>
+    </row>
+    <row r="2928" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2928" s="8">
+        <v>8</v>
+      </c>
+      <c r="B2928" s="8">
+        <v>282</v>
+      </c>
+      <c r="C2928" s="5" t="s">
+        <v>9251</v>
+      </c>
+      <c r="D2928" s="5" t="s">
+        <v>9252</v>
+      </c>
+      <c r="E2928" s="5" t="s">
+        <v>9253</v>
+      </c>
+      <c r="F2928" s="5" t="s">
+        <v>9254</v>
+      </c>
+      <c r="G2928" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
